--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\grades-portal\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khangv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE882BB-2797-4815-B159-C5E1A84B3225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D76234-032C-4B97-8DF7-B78EB1F08579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -2590,7 +2590,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2770,7 +2770,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3087,16 +3087,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E62F6F0-A60C-46AE-A379-677AAC706EA5}">
   <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="15" max="15" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4007,16 +4007,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B7CE8A-3709-4982-8530-4B128DCF5EDD}">
   <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14.265625" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="15" max="15" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -4407,11 +4407,14 @@
       <c r="H13">
         <v>10</v>
       </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
       <c r="O13">
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -4440,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -4469,7 +4472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -4498,7 +4501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -4527,7 +4530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -4550,13 +4553,16 @@
         <v>534</v>
       </c>
       <c r="H18">
-        <v>9.8000000000000007</v>
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>9.5</v>
       </c>
       <c r="O18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -4585,7 +4591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -4614,7 +4620,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -4643,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -4672,7 +4678,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -4701,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -4730,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4759,7 +4765,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -4788,7 +4794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -4817,7 +4823,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -4846,7 +4852,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -4875,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4915,16 +4921,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31AEED-D516-49B6-A6FF-F6CDC6895127}">
   <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" customWidth="1"/>
+    <col min="6" max="6" width="11.59765625" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4968,7 +4974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4997,7 +5003,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5023,7 +5029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5049,7 +5055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5075,7 +5081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5101,7 +5107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5125,7 +5131,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -5154,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5180,7 +5186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -5206,7 +5212,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -5235,7 +5241,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -5261,7 +5267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -5287,7 +5293,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -5316,7 +5322,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -5342,7 +5348,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -5368,7 +5374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5394,7 +5400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5420,7 +5426,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -5472,7 +5478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -5501,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -5527,7 +5533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -5553,7 +5559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -5579,7 +5585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -5605,7 +5611,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -5631,7 +5637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -5660,7 +5666,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -5689,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -5715,7 +5721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -5741,7 +5747,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -5778,16 +5784,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4EC707-71B4-4E8F-AC0E-96DAFCEEB03D}">
   <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="6" max="6" width="35.3984375" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5831,7 +5837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5857,7 +5863,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5883,7 +5889,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5909,7 +5915,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5938,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5967,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5996,7 +6002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -6025,7 +6031,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6051,7 +6057,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -6103,7 +6109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -6129,7 +6135,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -6155,7 +6161,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -6184,7 +6190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -6210,7 +6216,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -6239,7 +6245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -6268,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6294,7 +6300,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -6323,7 +6329,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -6349,7 +6355,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -6375,7 +6381,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -6401,7 +6407,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -6430,7 +6436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -6459,7 +6465,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -6485,7 +6491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -6511,7 +6517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -6537,7 +6543,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -6563,7 +6569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -6589,7 +6595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -6615,7 +6621,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -6652,16 +6658,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195B8901-376D-4489-8560-7242E57D3B44}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="16.73046875" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6705,7 +6711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6731,7 +6737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -6760,7 +6766,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -6789,7 +6795,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -6815,7 +6821,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -6844,7 +6850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6931,7 +6937,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -6960,7 +6966,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -6986,7 +6992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -7015,7 +7021,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -7041,7 +7047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -7070,7 +7076,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -7099,7 +7105,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -7125,7 +7131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -7151,7 +7157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -7180,7 +7186,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -7206,7 +7212,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -7232,7 +7238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -7261,7 +7267,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -7342,7 +7348,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -7368,7 +7374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -7397,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -7426,7 +7432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -7452,7 +7458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -7481,7 +7487,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -7518,16 +7524,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC312E2-BFEE-413B-B1C1-039BACF14471}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="14" max="14" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7571,7 +7577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7600,7 +7606,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -7626,7 +7632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -7652,7 +7658,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -7678,7 +7684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -7704,7 +7710,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -7730,7 +7736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -7756,7 +7762,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -7785,7 +7791,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -7811,7 +7817,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -7837,7 +7843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -7863,7 +7869,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -7889,7 +7895,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -7918,7 +7924,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -7944,7 +7950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -7970,7 +7976,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -7999,7 +8005,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -8025,7 +8031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -8054,7 +8060,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -8083,7 +8089,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -8138,7 +8144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -8164,7 +8170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -8190,7 +8196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -8216,7 +8222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -8245,7 +8251,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -8271,7 +8277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -8295,7 +8301,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -8332,15 +8338,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD567BBF-FA45-4BB7-A2DB-AA426EC5E0BA}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="2" max="3" width="9.73046875" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="15" max="15" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -8410,7 +8416,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -8433,7 +8439,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -8456,7 +8462,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -8479,7 +8485,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -8502,7 +8508,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -8525,7 +8531,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -8548,7 +8554,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -8571,7 +8577,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -8594,7 +8600,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -8617,7 +8623,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -8640,7 +8646,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -8663,7 +8669,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -8686,7 +8692,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -8709,7 +8715,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -8732,7 +8738,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -8755,7 +8761,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -8778,7 +8784,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -8801,7 +8807,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -8824,7 +8830,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -8847,7 +8853,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -8870,7 +8876,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -8893,7 +8899,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -8916,7 +8922,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -8939,7 +8945,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -8962,7 +8968,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -8985,7 +8991,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -9018,6 +9024,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -9256,24 +9279,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9290,29 +9321,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khangv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D76234-032C-4B97-8DF7-B78EB1F08579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26B3770-ED8A-46F7-ADBA-87D0839C8E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -3166,10 +3166,10 @@
         <v>463</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="O2">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
@@ -3198,7 +3198,7 @@
         <v>10</v>
       </c>
       <c r="O3">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
@@ -3430,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
@@ -3485,7 +3485,7 @@
         <v>474</v>
       </c>
       <c r="H13">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>475</v>
       </c>
       <c r="H14">
-        <v>9.3000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3604,7 +3604,7 @@
         <v>478</v>
       </c>
       <c r="H17">
-        <v>8.8000000000000007</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3662,10 +3662,10 @@
         <v>479</v>
       </c>
       <c r="H19">
-        <v>9.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="O19">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.45">
@@ -3781,7 +3781,7 @@
         <v>483</v>
       </c>
       <c r="H23">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>486</v>
       </c>
       <c r="H28">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="O3">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
@@ -4202,7 +4202,7 @@
         <v>523</v>
       </c>
       <c r="H6">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>524</v>
       </c>
       <c r="H7">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>525</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v>526</v>
       </c>
       <c r="H9">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -6734,7 +6734,10 @@
         <v>182</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -6763,7 +6766,7 @@
         <v>10</v>
       </c>
       <c r="N3">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
@@ -6792,7 +6795,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
@@ -6818,7 +6821,10 @@
         <v>251</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
@@ -6844,10 +6850,10 @@
         <v>252</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
@@ -6873,10 +6879,10 @@
         <v>253</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
@@ -6931,10 +6937,10 @@
         <v>255</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
@@ -6960,10 +6966,10 @@
         <v>256</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
@@ -6991,6 +6997,9 @@
       <c r="H11">
         <v>10</v>
       </c>
+      <c r="N11">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -7015,10 +7024,10 @@
         <v>83</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N12">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
@@ -7044,7 +7053,10 @@
         <v>258</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>9.5</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
@@ -7070,10 +7082,10 @@
         <v>259</v>
       </c>
       <c r="H14">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N14">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
@@ -7102,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
@@ -7128,7 +7140,10 @@
         <v>254</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>9.5</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
@@ -7156,6 +7171,9 @@
       <c r="H17">
         <v>10</v>
       </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
@@ -7183,7 +7201,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
@@ -7209,7 +7227,10 @@
         <v>263</v>
       </c>
       <c r="H19">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
@@ -7237,6 +7258,9 @@
       <c r="H20">
         <v>10</v>
       </c>
+      <c r="N20">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
@@ -7261,10 +7285,10 @@
         <v>265</v>
       </c>
       <c r="H21">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N21">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
@@ -7290,7 +7314,10 @@
         <v>171</v>
       </c>
       <c r="H22">
-        <v>8</v>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
@@ -7316,7 +7343,10 @@
         <v>266</v>
       </c>
       <c r="H23">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
@@ -7345,7 +7375,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
@@ -7373,6 +7403,9 @@
       <c r="H25">
         <v>10</v>
       </c>
+      <c r="N25">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -7455,7 +7488,10 @@
         <v>261</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
@@ -7484,7 +7520,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
@@ -7510,7 +7546,10 @@
         <v>268</v>
       </c>
       <c r="H30">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -7600,10 +7639,10 @@
         <v>327</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="N2">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -7631,6 +7670,9 @@
       <c r="H3">
         <v>10</v>
       </c>
+      <c r="N3">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -7655,7 +7697,10 @@
         <v>328</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
@@ -7683,6 +7728,9 @@
       <c r="H5">
         <v>10</v>
       </c>
+      <c r="N5">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -7707,7 +7755,10 @@
         <v>329</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
@@ -7735,6 +7786,9 @@
       <c r="H7">
         <v>10</v>
       </c>
+      <c r="N7">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -7788,7 +7842,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
@@ -7842,6 +7896,9 @@
       <c r="H11">
         <v>10</v>
       </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -7894,6 +7951,9 @@
       <c r="H13">
         <v>10</v>
       </c>
+      <c r="N13">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -7921,7 +7981,7 @@
         <v>9.5</v>
       </c>
       <c r="N14">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
@@ -8002,7 +8062,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
@@ -8028,7 +8088,10 @@
         <v>177</v>
       </c>
       <c r="H18">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
@@ -8057,7 +8120,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
@@ -8086,7 +8149,7 @@
         <v>9.5</v>
       </c>
       <c r="N20">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
@@ -8112,10 +8175,10 @@
         <v>342</v>
       </c>
       <c r="H21">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="N21">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
@@ -8143,6 +8206,9 @@
       <c r="H22">
         <v>10</v>
       </c>
+      <c r="N22">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
@@ -8169,6 +8235,9 @@
       <c r="H23">
         <v>10</v>
       </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
@@ -8221,6 +8290,9 @@
       <c r="H25">
         <v>10</v>
       </c>
+      <c r="N25">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -8248,7 +8320,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
@@ -8325,6 +8397,9 @@
       </c>
       <c r="H29">
         <v>10</v>
+      </c>
+      <c r="N29">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
@@ -9024,23 +9099,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -9279,32 +9337,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9321,4 +9371,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khangv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26B3770-ED8A-46F7-ADBA-87D0839C8E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57520756-4A4C-4B3F-8742-C53F60E488FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -4925,7 +4925,7 @@
   <cols>
     <col min="2" max="2" width="9.73046875" customWidth="1"/>
     <col min="3" max="3" width="14.3984375" customWidth="1"/>
-    <col min="6" max="6" width="11.59765625" customWidth="1"/>
+    <col min="6" max="6" width="24.265625" customWidth="1"/>
     <col min="7" max="7" width="11.86328125" customWidth="1"/>
     <col min="14" max="14" width="16.1328125" customWidth="1"/>
   </cols>
@@ -5000,7 +5000,7 @@
         <v>10</v>
       </c>
       <c r="N2">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -5028,6 +5028,9 @@
       <c r="H3">
         <v>10</v>
       </c>
+      <c r="N3">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -5054,6 +5057,9 @@
       <c r="H4">
         <v>10</v>
       </c>
+      <c r="N4">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -5078,7 +5084,10 @@
         <v>167</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
@@ -5106,6 +5115,9 @@
       <c r="H6">
         <v>10</v>
       </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -5154,7 +5166,7 @@
         <v>170</v>
       </c>
       <c r="H8">
-        <v>8.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -5185,6 +5197,9 @@
       <c r="H9">
         <v>10</v>
       </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -5209,7 +5224,10 @@
         <v>172</v>
       </c>
       <c r="H10">
-        <v>8.5</v>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
@@ -5238,7 +5256,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
@@ -5266,6 +5284,9 @@
       <c r="H12">
         <v>10</v>
       </c>
+      <c r="N12">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -5290,7 +5311,10 @@
         <v>175</v>
       </c>
       <c r="H13">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
@@ -5319,7 +5343,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
@@ -5345,7 +5369,10 @@
         <v>176</v>
       </c>
       <c r="H15">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
@@ -5371,7 +5398,10 @@
         <v>177</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>8.5</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
@@ -5399,6 +5429,9 @@
       <c r="H17">
         <v>10</v>
       </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
@@ -5423,7 +5456,10 @@
         <v>179</v>
       </c>
       <c r="H18">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
@@ -5451,6 +5487,9 @@
       <c r="H19">
         <v>10</v>
       </c>
+      <c r="N19">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
@@ -5475,7 +5514,10 @@
         <v>181</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N20">
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
@@ -5501,10 +5543,10 @@
         <v>182</v>
       </c>
       <c r="H21">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
@@ -5530,7 +5572,10 @@
         <v>183</v>
       </c>
       <c r="H22">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0.75</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
@@ -5556,7 +5601,10 @@
         <v>165</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
@@ -5584,6 +5632,9 @@
       <c r="H24">
         <v>9</v>
       </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -5608,7 +5659,10 @@
         <v>184</v>
       </c>
       <c r="H25">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
@@ -5634,7 +5688,10 @@
         <v>92</v>
       </c>
       <c r="H26">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N26">
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
@@ -5663,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
@@ -5689,7 +5746,7 @@
         <v>186</v>
       </c>
       <c r="H28">
-        <v>9.3000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5720,6 +5777,9 @@
       <c r="H29">
         <v>10</v>
       </c>
+      <c r="N29">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
@@ -5744,7 +5804,10 @@
         <v>187</v>
       </c>
       <c r="H30">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.45">
@@ -5770,7 +5833,10 @@
         <v>188</v>
       </c>
       <c r="H31">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N31">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -5860,7 +5926,10 @@
         <v>72</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -5886,7 +5955,10 @@
         <v>73</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
@@ -5912,7 +5984,10 @@
         <v>74</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
@@ -5938,7 +6013,7 @@
         <v>75</v>
       </c>
       <c r="H5">
-        <v>8.8000000000000007</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -5967,7 +6042,7 @@
         <v>76</v>
       </c>
       <c r="H6">
-        <v>8.3000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -5996,10 +6071,10 @@
         <v>77</v>
       </c>
       <c r="H7">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
@@ -6028,7 +6103,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
@@ -6054,7 +6129,10 @@
         <v>79</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
@@ -6082,6 +6160,9 @@
       <c r="H10">
         <v>10</v>
       </c>
+      <c r="N10">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -6108,6 +6189,9 @@
       <c r="H11">
         <v>10</v>
       </c>
+      <c r="N11">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -6134,6 +6218,9 @@
       <c r="H12">
         <v>10</v>
       </c>
+      <c r="N12">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -6158,7 +6245,10 @@
         <v>82</v>
       </c>
       <c r="H13">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
@@ -6184,10 +6274,10 @@
         <v>83</v>
       </c>
       <c r="H14">
-        <v>8.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
@@ -6213,7 +6303,10 @@
         <v>84</v>
       </c>
       <c r="H15">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
@@ -6239,10 +6332,10 @@
         <v>85</v>
       </c>
       <c r="H16">
-        <v>9.3000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
@@ -6268,10 +6361,10 @@
         <v>86</v>
       </c>
       <c r="H17">
-        <v>9.3000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
@@ -6297,7 +6390,10 @@
         <v>87</v>
       </c>
       <c r="H18">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
@@ -6326,7 +6422,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
@@ -6352,7 +6448,10 @@
         <v>89</v>
       </c>
       <c r="H20">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
@@ -6378,7 +6477,10 @@
         <v>90</v>
       </c>
       <c r="H21">
-        <v>7.5</v>
+        <v>8</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
@@ -6404,7 +6506,10 @@
         <v>91</v>
       </c>
       <c r="H22">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
@@ -6430,10 +6535,10 @@
         <v>92</v>
       </c>
       <c r="H23">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
@@ -6462,7 +6567,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
@@ -6490,6 +6595,9 @@
       <c r="H25">
         <v>10</v>
       </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -6516,6 +6624,9 @@
       <c r="H26">
         <v>10</v>
       </c>
+      <c r="N26">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -6540,7 +6651,10 @@
         <v>96</v>
       </c>
       <c r="H27">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
@@ -6566,7 +6680,10 @@
         <v>97</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="N28">
+        <v>0.25</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
@@ -6592,7 +6709,10 @@
         <v>98</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>9.5</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
@@ -6618,7 +6738,10 @@
         <v>99</v>
       </c>
       <c r="H30">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.45">
@@ -6644,7 +6767,10 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>6.5</v>
+        <v>7</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7815,6 +7941,9 @@
       <c r="H8">
         <v>9.5</v>
       </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -7870,6 +7999,9 @@
       <c r="H10">
         <v>9.5</v>
       </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -7925,6 +8057,9 @@
       <c r="H12">
         <v>9.5</v>
       </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -8009,6 +8144,9 @@
       <c r="H15">
         <v>10</v>
       </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -8035,6 +8173,9 @@
       <c r="H16">
         <v>9.5</v>
       </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
@@ -8264,6 +8405,9 @@
       <c r="H24">
         <v>10</v>
       </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -8348,6 +8492,9 @@
       <c r="H27">
         <v>8</v>
       </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
@@ -8372,6 +8519,9 @@
         <v>345</v>
       </c>
       <c r="H28" s="1"/>
+      <c r="N28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
@@ -8490,6 +8640,9 @@
       <c r="G2" t="s">
         <v>406</v>
       </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -8513,6 +8666,9 @@
       <c r="G3" t="s">
         <v>407</v>
       </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -8536,6 +8692,9 @@
       <c r="G4" t="s">
         <v>408</v>
       </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -8559,6 +8718,9 @@
       <c r="G5" t="s">
         <v>409</v>
       </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -8582,6 +8744,9 @@
       <c r="G6" t="s">
         <v>410</v>
       </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -8605,6 +8770,9 @@
       <c r="G7" t="s">
         <v>411</v>
       </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -8628,6 +8796,9 @@
       <c r="G8" t="s">
         <v>412</v>
       </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -8651,6 +8822,9 @@
       <c r="G9" t="s">
         <v>413</v>
       </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -8674,6 +8848,9 @@
       <c r="G10" t="s">
         <v>414</v>
       </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -8697,6 +8874,9 @@
       <c r="G11" t="s">
         <v>415</v>
       </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -8720,6 +8900,9 @@
       <c r="G12" t="s">
         <v>416</v>
       </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -8743,6 +8926,9 @@
       <c r="G13" t="s">
         <v>417</v>
       </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -8766,6 +8952,9 @@
       <c r="G14" t="s">
         <v>418</v>
       </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -8789,6 +8978,9 @@
       <c r="G15" t="s">
         <v>419</v>
       </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -8812,8 +9004,11 @@
       <c r="G16" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -8835,8 +9030,11 @@
       <c r="G17" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -8858,8 +9056,11 @@
       <c r="G18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -8881,8 +9082,11 @@
       <c r="G19" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -8904,8 +9108,11 @@
       <c r="G20" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -8927,8 +9134,11 @@
       <c r="G21" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -8950,8 +9160,11 @@
       <c r="G22" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -8973,8 +9186,11 @@
       <c r="G23" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -8996,8 +9212,11 @@
       <c r="G24" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -9019,8 +9238,11 @@
       <c r="G25" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -9042,8 +9264,11 @@
       <c r="G26" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -9065,8 +9290,11 @@
       <c r="G27" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -9087,6 +9315,9 @@
       </c>
       <c r="G28" t="s">
         <v>432</v>
+      </c>
+      <c r="H28">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9099,6 +9330,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -9337,15 +9577,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9355,6 +9586,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9369,14 +9608,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinhthienly-my.sharepoint.com/personal/ict_khangv_lsts_edu_vn/Documents/01. PD/2025 - 2026/SỔ ĐIỂM HK2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="13_ncr:1_{863424D0-A828-47E1-ADF0-1DE921A707F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC081C49-6B1A-4180-93DE-D0B3D6E824B6}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{9C38F584-4819-487B-ADF8-F9572E133DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB2ECF6-12B8-43FA-A4D1-5DACDB3B1B66}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="831">
   <si>
     <t>STT</t>
   </si>
@@ -2490,9 +2490,6 @@
   </si>
   <si>
     <t>22/02/2010</t>
-  </si>
-  <si>
-    <t>7951465925</t>
   </si>
   <si>
     <t>2106219@lsts.edu.vn</t>
@@ -2559,7 +2556,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2569,6 +2566,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2585,13 +2588,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2604,6 +2608,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3178,7 +3186,8 @@
         <v>4</v>
       </c>
       <c r="O2">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3219,7 +3228,8 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -3260,7 +3270,8 @@
         <v>4</v>
       </c>
       <c r="O4">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -3301,7 +3312,8 @@
         <v>4</v>
       </c>
       <c r="O5">
-        <v>0.75</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -3342,7 +3354,8 @@
         <v>4</v>
       </c>
       <c r="O6">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -3383,7 +3396,8 @@
         <v>4</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -3424,7 +3438,8 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -3465,7 +3480,8 @@
         <v>4</v>
       </c>
       <c r="O9">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -3506,7 +3522,8 @@
         <v>4</v>
       </c>
       <c r="O10">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -3547,7 +3564,8 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -3588,7 +3606,8 @@
         <v>4</v>
       </c>
       <c r="O12">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -3629,7 +3648,8 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -3670,7 +3690,8 @@
         <v>4</v>
       </c>
       <c r="O14">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -3711,7 +3732,8 @@
         <v>4</v>
       </c>
       <c r="O15">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -3752,7 +3774,8 @@
         <v>4</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>2.25</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -3796,7 +3819,8 @@
         <v>4</v>
       </c>
       <c r="O17">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -3837,7 +3861,8 @@
         <v>4</v>
       </c>
       <c r="O18">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3878,7 +3903,8 @@
         <v>4</v>
       </c>
       <c r="O19">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3919,7 +3945,8 @@
         <v>4</v>
       </c>
       <c r="O20">
-        <v>0.75</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3960,7 +3987,8 @@
         <v>4</v>
       </c>
       <c r="O21">
-        <v>0.75</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.75</v>
       </c>
       <c r="P21">
         <v>10</v>
@@ -4004,7 +4032,8 @@
         <v>4</v>
       </c>
       <c r="O22">
-        <v>0.75</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -4045,7 +4074,8 @@
         <v>4</v>
       </c>
       <c r="O23">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -4086,7 +4116,8 @@
         <v>4</v>
       </c>
       <c r="O24">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -4127,7 +4158,8 @@
         <v>4</v>
       </c>
       <c r="O25">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
       <c r="P25">
         <v>9.3000000000000007</v>
@@ -4171,7 +4203,8 @@
         <v>4</v>
       </c>
       <c r="O26">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -4212,7 +4245,8 @@
         <v>4</v>
       </c>
       <c r="O27">
-        <v>0.75</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -4253,7 +4287,8 @@
         <v>4</v>
       </c>
       <c r="O28">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -4294,7 +4329,8 @@
         <v>4</v>
       </c>
       <c r="O29">
-        <v>0.5</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -4335,7 +4371,8 @@
         <v>4</v>
       </c>
       <c r="O30">
-        <v>0.25</v>
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -4446,8 +4483,7 @@
         <v>4</v>
       </c>
       <c r="O2">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4488,8 +4524,7 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -4530,8 +4565,7 @@
         <v>4</v>
       </c>
       <c r="O4">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -4572,8 +4606,7 @@
         <v>4</v>
       </c>
       <c r="O5">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -4614,8 +4647,7 @@
         <v>4</v>
       </c>
       <c r="O6">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -4656,8 +4688,7 @@
         <v>4</v>
       </c>
       <c r="O7">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4698,8 +4729,7 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4740,8 +4770,7 @@
         <v>4</v>
       </c>
       <c r="O9">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4782,8 +4811,7 @@
         <v>4</v>
       </c>
       <c r="O10">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4824,8 +4852,7 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -4866,8 +4893,7 @@
         <v>4</v>
       </c>
       <c r="O12">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4908,8 +4934,7 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -4953,8 +4978,7 @@
         <v>4</v>
       </c>
       <c r="O14">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4995,8 +5019,7 @@
         <v>4</v>
       </c>
       <c r="O15">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -5037,8 +5060,7 @@
         <v>4</v>
       </c>
       <c r="O16">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -5079,8 +5101,7 @@
         <v>4</v>
       </c>
       <c r="O17">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -5121,8 +5142,7 @@
         <v>4</v>
       </c>
       <c r="O18">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="P18">
         <v>9.5</v>
@@ -5166,8 +5186,7 @@
         <v>4</v>
       </c>
       <c r="O19">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -5208,8 +5227,7 @@
         <v>4</v>
       </c>
       <c r="O20">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -5250,8 +5268,7 @@
         <v>4</v>
       </c>
       <c r="O21">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -5292,8 +5309,7 @@
         <v>4</v>
       </c>
       <c r="O22">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -5334,8 +5350,7 @@
         <v>4</v>
       </c>
       <c r="O23">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -5376,8 +5391,7 @@
         <v>4</v>
       </c>
       <c r="O24">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -5418,8 +5432,7 @@
         <v>4</v>
       </c>
       <c r="O25">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -5460,8 +5473,7 @@
         <v>4</v>
       </c>
       <c r="O26">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -5502,8 +5514,7 @@
         <v>4</v>
       </c>
       <c r="O27">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -5544,8 +5555,7 @@
         <v>4</v>
       </c>
       <c r="O28">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -5586,8 +5596,7 @@
         <v>4</v>
       </c>
       <c r="O29">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -5628,8 +5637,7 @@
         <v>4</v>
       </c>
       <c r="O30">
-        <f ca="1">Table1345678[[#This Row],[Điểm cộng/trừ]]+0.25</f>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -5719,7 +5727,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -5748,7 +5756,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -5777,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -5806,7 +5814,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -5835,7 +5843,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -5863,6 +5871,9 @@
       <c r="H7" s="1">
         <v>8</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -5890,7 +5901,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -5919,7 +5930,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -5948,7 +5959,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -5977,7 +5988,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -6006,7 +6017,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -6035,7 +6046,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -6064,7 +6075,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -6093,7 +6104,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -6122,7 +6133,7 @@
         <v>8.5</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -6151,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -6180,7 +6191,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -6209,7 +6220,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -6238,7 +6249,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -6267,7 +6278,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -6296,7 +6307,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -6325,7 +6336,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -6354,7 +6365,7 @@
         <v>9.5</v>
       </c>
       <c r="M24">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -6383,7 +6394,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -6412,7 +6423,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -6441,7 +6452,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -6470,7 +6481,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -6499,7 +6510,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -6528,7 +6539,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -6557,7 +6568,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -6647,7 +6658,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -6676,7 +6687,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -6705,7 +6716,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -6734,7 +6745,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -6763,7 +6774,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -6792,7 +6803,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -6821,7 +6832,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -6850,7 +6861,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -6879,7 +6890,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -6908,7 +6919,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -6937,7 +6948,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -6966,7 +6977,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -6995,7 +7006,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -7024,7 +7035,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -7053,7 +7064,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -7082,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="M17">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -7111,7 +7122,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -7140,7 +7151,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -7169,7 +7180,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -7198,7 +7209,7 @@
         <v>8</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -7227,7 +7238,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -7256,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -7285,7 +7296,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -7314,7 +7325,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -7343,7 +7354,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -7372,7 +7383,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -7401,7 +7412,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -7430,7 +7441,7 @@
         <v>9.5</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -7459,7 +7470,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -7488,7 +7499,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7587,7 +7598,8 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2">
-        <v>0.25</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7622,7 +7634,7 @@
         <v>9.5</v>
       </c>
       <c r="M3">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7657,7 +7669,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7692,7 +7704,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7727,7 +7739,7 @@
         <v>9.25</v>
       </c>
       <c r="M6">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -7762,7 +7774,7 @@
         <v>8.25</v>
       </c>
       <c r="M7">
-        <v>-0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7797,7 +7809,7 @@
         <v>9.25</v>
       </c>
       <c r="M8">
-        <v>-1.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -7832,7 +7844,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-0.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -7867,7 +7879,8 @@
         <v>6.5</v>
       </c>
       <c r="M10">
-        <v>-0.5</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -7902,7 +7915,7 @@
         <v>9.5</v>
       </c>
       <c r="M11">
-        <v>1.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -7937,7 +7950,8 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -7972,7 +7986,7 @@
         <v>9.75</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8007,7 +8021,7 @@
         <v>8.5</v>
       </c>
       <c r="M14">
-        <v>-0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8042,7 +8056,7 @@
         <v>9.5</v>
       </c>
       <c r="M15">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8077,7 +8091,8 @@
         <v>8.5</v>
       </c>
       <c r="M16">
-        <v>-0.75</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8112,7 +8127,8 @@
         <v>8.75</v>
       </c>
       <c r="M17">
-        <v>-1.75</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -8147,7 +8163,8 @@
         <v>9.75</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8182,7 +8199,7 @@
         <v>9.5</v>
       </c>
       <c r="M19">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -8217,7 +8234,8 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>1.75</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>2.75</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -8252,7 +8270,7 @@
         <v>9.25</v>
       </c>
       <c r="M21">
-        <v>-2.75</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -8287,7 +8305,8 @@
         <v>9.75</v>
       </c>
       <c r="M22">
-        <v>-1.25</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -8322,7 +8341,7 @@
         <v>9.75</v>
       </c>
       <c r="M23">
-        <v>-1.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -8357,7 +8376,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>0.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -8392,7 +8411,8 @@
         <v>9.5</v>
       </c>
       <c r="M25">
-        <v>1.25</v>
+        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -8427,7 +8447,7 @@
         <v>8.5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -8462,7 +8482,7 @@
         <v>9.5</v>
       </c>
       <c r="M27">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -8497,7 +8517,7 @@
         <v>8.75</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -8532,7 +8552,7 @@
         <v>9.25</v>
       </c>
       <c r="M29">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -8567,7 +8587,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
@@ -8659,9 +8679,12 @@
       <c r="I2">
         <v>10</v>
       </c>
+      <c r="J2">
+        <v>8.25</v>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -8692,8 +8715,11 @@
       <c r="I3">
         <v>10</v>
       </c>
+      <c r="J3">
+        <v>9.75</v>
+      </c>
       <c r="M3">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -8724,6 +8750,9 @@
       <c r="I4">
         <v>10</v>
       </c>
+      <c r="J4">
+        <v>9.75</v>
+      </c>
       <c r="M4">
         <v>0</v>
       </c>
@@ -8756,8 +8785,11 @@
       <c r="I5">
         <v>10</v>
       </c>
+      <c r="J5">
+        <v>9.75</v>
+      </c>
       <c r="M5">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -8788,8 +8820,11 @@
       <c r="I6">
         <v>10</v>
       </c>
+      <c r="J6">
+        <v>9.25</v>
+      </c>
       <c r="M6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -8820,8 +8855,11 @@
       <c r="I7">
         <v>10</v>
       </c>
+      <c r="J7">
+        <v>9.75</v>
+      </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -8852,8 +8890,11 @@
       <c r="I8">
         <v>10</v>
       </c>
+      <c r="J8">
+        <v>9.25</v>
+      </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8884,8 +8925,11 @@
       <c r="I9">
         <v>10</v>
       </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
       <c r="M9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8916,8 +8960,11 @@
       <c r="I10">
         <v>10</v>
       </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
       <c r="M10">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8948,8 +8995,11 @@
       <c r="I11">
         <v>10</v>
       </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
       <c r="M11">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8980,8 +9030,11 @@
       <c r="I12">
         <v>10</v>
       </c>
+      <c r="J12">
+        <v>9.5</v>
+      </c>
       <c r="M12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -9012,6 +9065,9 @@
       <c r="I13">
         <v>10</v>
       </c>
+      <c r="J13">
+        <v>9.5</v>
+      </c>
       <c r="M13">
         <v>0.5</v>
       </c>
@@ -9044,8 +9100,11 @@
       <c r="I14">
         <v>10</v>
       </c>
+      <c r="J14">
+        <v>9.75</v>
+      </c>
       <c r="M14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -9076,8 +9135,11 @@
       <c r="I15">
         <v>10</v>
       </c>
+      <c r="J15">
+        <v>9</v>
+      </c>
       <c r="M15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -9108,8 +9170,11 @@
       <c r="I16">
         <v>10</v>
       </c>
+      <c r="J16">
+        <v>9.5</v>
+      </c>
       <c r="M16">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -9140,8 +9205,11 @@
       <c r="I17">
         <v>10</v>
       </c>
+      <c r="J17">
+        <v>7.75</v>
+      </c>
       <c r="M17">
-        <v>0</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -9172,8 +9240,11 @@
       <c r="I18">
         <v>10</v>
       </c>
+      <c r="J18">
+        <v>8.25</v>
+      </c>
       <c r="M18">
-        <v>0.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9204,8 +9275,11 @@
       <c r="I19">
         <v>10</v>
       </c>
+      <c r="J19">
+        <v>9.75</v>
+      </c>
       <c r="M19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -9236,6 +9310,9 @@
       <c r="I20">
         <v>10</v>
       </c>
+      <c r="J20">
+        <v>8.75</v>
+      </c>
       <c r="M20">
         <v>0</v>
       </c>
@@ -9268,8 +9345,11 @@
       <c r="I21">
         <v>10</v>
       </c>
+      <c r="J21">
+        <v>8.5</v>
+      </c>
       <c r="M21">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -9300,8 +9380,11 @@
       <c r="I22">
         <v>10</v>
       </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
       <c r="M22">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -9332,8 +9415,11 @@
       <c r="I23">
         <v>10</v>
       </c>
+      <c r="J23">
+        <v>9.25</v>
+      </c>
       <c r="M23">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -9364,8 +9450,11 @@
       <c r="I24">
         <v>10</v>
       </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9396,8 +9485,11 @@
       <c r="I25">
         <v>10</v>
       </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
       <c r="M25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -9428,8 +9520,11 @@
       <c r="I26">
         <v>10</v>
       </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
       <c r="M26">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -9461,7 +9556,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -9492,6 +9587,9 @@
       <c r="I28">
         <v>10</v>
       </c>
+      <c r="J28">
+        <v>8.75</v>
+      </c>
       <c r="M28">
         <v>0</v>
       </c>
@@ -9524,8 +9622,11 @@
       <c r="I29">
         <v>10</v>
       </c>
+      <c r="J29">
+        <v>9.5</v>
+      </c>
       <c r="M29">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
@@ -9541,7 +9642,8 @@
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="11" max="12" width="9.140625" customWidth="1"/>
@@ -9629,11 +9731,11 @@
       <c r="K2">
         <v>6</v>
       </c>
-      <c r="L2">
-        <v>3.6</v>
+      <c r="L2" s="3">
+        <v>3.8</v>
       </c>
       <c r="O2">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -9665,16 +9767,16 @@
         <v>10</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>5.7</v>
       </c>
-      <c r="L3">
-        <v>2.8</v>
+      <c r="L3" s="3">
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -9702,8 +9804,8 @@
       <c r="H4">
         <v>10</v>
       </c>
-      <c r="I4">
-        <v>5</v>
+      <c r="I4" s="3">
+        <v>8</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -9711,11 +9813,11 @@
       <c r="K4">
         <v>5.7</v>
       </c>
-      <c r="L4">
-        <v>3.6</v>
+      <c r="L4" s="3">
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -9743,8 +9845,8 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5">
-        <v>4</v>
+      <c r="I5" s="3">
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -9752,11 +9854,11 @@
       <c r="K5">
         <v>6</v>
       </c>
-      <c r="L5">
-        <v>3.2</v>
+      <c r="L5" s="3">
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -9793,11 +9895,11 @@
       <c r="K6">
         <v>5.3</v>
       </c>
-      <c r="L6">
-        <v>2.8</v>
+      <c r="L6" s="3">
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -9834,11 +9936,11 @@
       <c r="K7">
         <v>5.7</v>
       </c>
-      <c r="L7">
-        <v>3.6</v>
+      <c r="L7" s="3">
+        <v>3.8</v>
       </c>
       <c r="O7">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -9875,11 +9977,11 @@
       <c r="K8">
         <v>6</v>
       </c>
-      <c r="L8">
-        <v>3.6</v>
+      <c r="L8" s="3">
+        <v>3.8</v>
       </c>
       <c r="O8">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -9907,20 +10009,20 @@
       <c r="H9">
         <v>10</v>
       </c>
-      <c r="I9">
-        <v>5</v>
+      <c r="I9" s="3">
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="3">
         <v>3.2</v>
       </c>
       <c r="O9">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -9948,20 +10050,20 @@
       <c r="H10">
         <v>10</v>
       </c>
-      <c r="I10">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>5.4</v>
       </c>
-      <c r="L10">
-        <v>2.8</v>
+      <c r="L10" s="3">
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -9989,8 +10091,8 @@
       <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11">
-        <v>5</v>
+      <c r="I11" s="3">
+        <v>8</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -9998,11 +10100,11 @@
       <c r="K11">
         <v>5.5</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="3">
         <v>3.2</v>
       </c>
       <c r="O11">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -10030,8 +10132,8 @@
       <c r="H12">
         <v>10</v>
       </c>
-      <c r="I12">
-        <v>5</v>
+      <c r="I12" s="3">
+        <v>8</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -10039,11 +10141,11 @@
       <c r="K12">
         <v>5.7</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <v>3.2</v>
       </c>
       <c r="O12">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -10071,8 +10173,8 @@
       <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13">
-        <v>5</v>
+      <c r="I13" s="3">
+        <v>8</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -10080,11 +10182,11 @@
       <c r="K13">
         <v>5.7</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <v>3.2</v>
       </c>
       <c r="O13">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -10112,8 +10214,8 @@
       <c r="H14">
         <v>10</v>
       </c>
-      <c r="I14">
-        <v>5</v>
+      <c r="I14" s="3">
+        <v>8</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -10121,11 +10223,11 @@
       <c r="K14">
         <v>5.9</v>
       </c>
-      <c r="L14">
-        <v>3.6</v>
+      <c r="L14" s="3">
+        <v>3.8</v>
       </c>
       <c r="O14">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -10153,8 +10255,8 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15">
-        <v>4</v>
+      <c r="I15" s="3">
+        <v>8</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -10162,11 +10264,11 @@
       <c r="K15">
         <v>5.7</v>
       </c>
-      <c r="L15">
-        <v>3.2</v>
+      <c r="L15" s="3">
+        <v>3.6</v>
       </c>
       <c r="O15">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -10194,8 +10296,8 @@
       <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16">
-        <v>5</v>
+      <c r="I16" s="3">
+        <v>8</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -10203,11 +10305,11 @@
       <c r="K16">
         <v>5.6</v>
       </c>
-      <c r="L16">
-        <v>3.6</v>
+      <c r="L16" s="3">
+        <v>3.8</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -10235,20 +10337,20 @@
       <c r="H17">
         <v>10</v>
       </c>
-      <c r="I17">
-        <v>5</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
+      <c r="I17" s="3">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
+        <v>8</v>
       </c>
       <c r="K17">
         <v>5.6</v>
       </c>
-      <c r="L17">
-        <v>2.8</v>
+      <c r="L17" s="3">
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -10276,20 +10378,20 @@
       <c r="H18">
         <v>10</v>
       </c>
-      <c r="I18">
-        <v>4</v>
+      <c r="I18" s="3">
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>5.9</v>
       </c>
-      <c r="L18">
-        <v>3.6</v>
+      <c r="L18" s="3">
+        <v>3.8</v>
       </c>
       <c r="O18">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -10317,20 +10419,20 @@
       <c r="H19">
         <v>10</v>
       </c>
-      <c r="I19">
-        <v>5</v>
+      <c r="I19" s="3">
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>5.8</v>
       </c>
-      <c r="L19">
-        <v>3.6</v>
+      <c r="L19" s="3">
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -10358,20 +10460,20 @@
       <c r="H20">
         <v>10</v>
       </c>
-      <c r="I20">
-        <v>5</v>
+      <c r="I20" s="3">
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>5.9</v>
       </c>
-      <c r="L20">
-        <v>3.2</v>
+      <c r="L20" s="3">
+        <v>3.6</v>
       </c>
       <c r="O20">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -10399,20 +10501,20 @@
       <c r="H21">
         <v>10</v>
       </c>
-      <c r="I21">
-        <v>4</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
+      <c r="I21" s="3">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3">
+        <v>8</v>
       </c>
       <c r="K21">
         <v>5.7</v>
       </c>
-      <c r="L21">
-        <v>2.8</v>
+      <c r="L21" s="3">
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -10444,16 +10546,16 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>2.8</v>
+        <v>10</v>
+      </c>
+      <c r="K22" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="L22" s="3">
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -10481,8 +10583,8 @@
       <c r="H23">
         <v>10</v>
       </c>
-      <c r="I23">
-        <v>5</v>
+      <c r="I23" s="3">
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -10490,11 +10592,11 @@
       <c r="K23">
         <v>6</v>
       </c>
-      <c r="L23">
-        <v>2.8</v>
+      <c r="L23" s="3">
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -10531,11 +10633,11 @@
       <c r="K24">
         <v>6</v>
       </c>
-      <c r="L24">
-        <v>3.6</v>
+      <c r="L24" s="3">
+        <v>3.8</v>
       </c>
       <c r="O24">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -10545,38 +10647,38 @@
       <c r="B25" t="s">
         <v>746</v>
       </c>
-      <c r="C25" t="s">
-        <v>816</v>
+      <c r="C25">
+        <v>7951465925</v>
       </c>
       <c r="D25">
         <v>2106219</v>
       </c>
       <c r="E25" t="s">
+        <v>816</v>
+      </c>
+      <c r="F25" t="s">
         <v>817</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>818</v>
       </c>
-      <c r="G25" t="s">
-        <v>819</v>
-      </c>
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="3">
         <v>9</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>5.6</v>
       </c>
-      <c r="L25">
-        <v>3.6</v>
+      <c r="L25" s="3">
+        <v>3.8</v>
       </c>
       <c r="O25">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -10587,19 +10689,19 @@
         <v>771</v>
       </c>
       <c r="C26" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D26">
         <v>2110032</v>
       </c>
       <c r="E26" t="s">
+        <v>820</v>
+      </c>
+      <c r="F26" t="s">
         <v>821</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>822</v>
-      </c>
-      <c r="G26" t="s">
-        <v>823</v>
       </c>
       <c r="H26">
         <v>10</v>
@@ -10613,11 +10715,11 @@
       <c r="K26">
         <v>5.6</v>
       </c>
-      <c r="L26">
-        <v>2.8</v>
+      <c r="L26" s="3">
+        <v>3</v>
       </c>
       <c r="O26">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -10628,25 +10730,25 @@
         <v>733</v>
       </c>
       <c r="C27" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D27">
         <v>2106099</v>
       </c>
       <c r="E27" t="s">
+        <v>824</v>
+      </c>
+      <c r="F27" t="s">
         <v>825</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>826</v>
       </c>
-      <c r="G27" t="s">
-        <v>827</v>
-      </c>
       <c r="H27">
         <v>10</v>
       </c>
-      <c r="I27">
-        <v>4</v>
+      <c r="I27" s="3">
+        <v>8</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -10654,11 +10756,11 @@
       <c r="K27">
         <v>6</v>
       </c>
-      <c r="L27">
-        <v>3.2</v>
+      <c r="L27" s="3">
+        <v>3.6</v>
       </c>
       <c r="O27">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -10669,37 +10771,37 @@
         <v>746</v>
       </c>
       <c r="C28" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D28">
         <v>2107049</v>
       </c>
       <c r="E28" t="s">
+        <v>828</v>
+      </c>
+      <c r="F28" t="s">
         <v>829</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>830</v>
       </c>
-      <c r="G28" t="s">
-        <v>831</v>
-      </c>
       <c r="H28">
         <v>10</v>
       </c>
-      <c r="I28">
-        <v>4</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
+      <c r="I28" s="3">
+        <v>8</v>
+      </c>
+      <c r="J28" s="3">
+        <v>8</v>
       </c>
       <c r="K28">
         <v>5.7</v>
       </c>
-      <c r="L28">
-        <v>2.8</v>
+      <c r="L28" s="3">
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -10712,20 +10814,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10968,26 +11070,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinhthienly-my.sharepoint.com/personal/ict_khangv_lsts_edu_vn/Documents/01. PD/2025 - 2026/SỔ ĐIỂM HK2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{9C38F584-4819-487B-ADF8-F9572E133DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB2ECF6-12B8-43FA-A4D1-5DACDB3B1B66}"/>
+  <xr:revisionPtr revIDLastSave="1481" documentId="13_ncr:1_{9C38F584-4819-487B-ADF8-F9572E133DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B4EA72-7195-48F4-AB79-BA43E9A97B95}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="75" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="6" activeTab="6" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="9H07" sheetId="4" r:id="rId6"/>
     <sheet name="MUL10L3" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191028" calcCompleted="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2541,7 +2541,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2556,7 +2559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2575,6 +2578,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2588,16 +2609,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2608,10 +2760,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2625,14 +2773,14 @@
     <tableColumn id="4" xr3:uid="{8A570531-1F2E-496F-81CB-604F321E21CA}" name="Email"/>
     <tableColumn id="5" xr3:uid="{A02E2B85-AB61-40A1-9F4B-D979CAC0B617}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{2FFEAA5A-8746-4BD9-98AB-DBD4E8A4A25E}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{73647768-883D-4881-AC08-329C42F7CAF5}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{73647768-883D-4881-AC08-329C42F7CAF5}" name="TX1" dataDxfId="17"/>
     <tableColumn id="8" xr3:uid="{F07CAD0F-FE6E-43E3-A5F3-7B413864403F}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{5AFF0A24-6235-4A06-8319-FC8208F8B70E}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{EE5EFA3E-6E5D-4CC4-AF4D-352CC7E2323A}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{C094DE6A-6F36-4C2C-9BA8-FC6279DB205D}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{6A74C0A7-2690-4619-8688-B10403D4B1A9}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{32C992A3-1937-4FAD-93D0-760AAC028DCA}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{D56AE305-8846-4965-9E4A-4C7CCC2ED78A}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{D56AE305-8846-4965-9E4A-4C7CCC2ED78A}" name="Điểm cộng/trừ" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2649,14 +2797,14 @@
     <tableColumn id="4" xr3:uid="{C5D3CFB0-FAF6-4D1E-A475-E7FA9D71AB5D}" name="Email"/>
     <tableColumn id="5" xr3:uid="{91C2DDE5-F074-4EAC-88F7-79EA00D266CC}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{226EBCCE-5C9A-4CBC-8056-733B010D8131}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{F73C8D4B-448F-461E-BE91-2ED211DEF252}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{F73C8D4B-448F-461E-BE91-2ED211DEF252}" name="TX1" dataDxfId="15"/>
     <tableColumn id="8" xr3:uid="{A1579224-363E-453E-9563-D540AA688406}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{6F87760A-1A5B-4020-811F-F2DFA92559E8}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{7460001B-4B51-4627-B19E-56E68A476EC5}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{CE0203A2-6C00-4623-82AD-1BFF8ACD360C}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{7428E339-3333-4B74-963C-C009887E1C5C}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{9A8E2EAA-0067-4189-AB09-0CB66607B45E}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{390C5CFE-3A6A-4638-9BBF-A4E808C34019}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{390C5CFE-3A6A-4638-9BBF-A4E808C34019}" name="Điểm cộng/trừ" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2673,12 +2821,12 @@
     <tableColumn id="4" xr3:uid="{B5A5A35E-BF57-4756-93A5-E4D8D57AE3DD}" name="Email"/>
     <tableColumn id="5" xr3:uid="{BD257335-0296-4F83-9582-74FB6D54FFEE}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{149A88A9-EBA0-4DEF-ABEF-87BA920B076E}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{412235EE-C3D7-41E5-8934-3084314078B0}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{412235EE-C3D7-41E5-8934-3084314078B0}" name="TX1" dataDxfId="13"/>
     <tableColumn id="8" xr3:uid="{B4ED72BD-9228-4E83-8EE4-091B112C2B0C}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{727F5E71-DAB5-4D3F-9759-8BC266A4ED52}" name="GKTN"/>
-    <tableColumn id="11" xr3:uid="{333B9655-FE71-4ED7-82A0-F0641FE0FC1D}" name="CKTN"/>
+    <tableColumn id="9" xr3:uid="{727F5E71-DAB5-4D3F-9759-8BC266A4ED52}" name="GKTN" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{333B9655-FE71-4ED7-82A0-F0641FE0FC1D}" name="CKTN" dataDxfId="11"/>
     <tableColumn id="12" xr3:uid="{12F75C8C-BA02-41AF-B140-AE5EF3BD99A4}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{C94634BB-4F5D-4330-99F0-51186DAB60DE}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{C94634BB-4F5D-4330-99F0-51186DAB60DE}" name="Điểm cộng/trừ" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2695,12 +2843,12 @@
     <tableColumn id="4" xr3:uid="{22F7231F-C7A0-447F-A36F-DF32328BE83E}" name="Email"/>
     <tableColumn id="5" xr3:uid="{CB4BA5A7-E295-4634-B8D5-79CED684DA84}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{9E09BF74-FA06-4E53-B295-9B096B431E71}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{77131993-30B1-49AE-BCE9-38F5EDF29692}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{77131993-30B1-49AE-BCE9-38F5EDF29692}" name="TX1" dataDxfId="9"/>
     <tableColumn id="8" xr3:uid="{EA41B88E-A7D1-49D3-AAA3-D3FD83B5F818}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{CA4BAF3B-3E9D-4F31-A984-1BBC57B1761E}" name="GKTN"/>
-    <tableColumn id="11" xr3:uid="{8E43F492-DA8D-4B36-992F-8FF2ED3BA73B}" name="CKTN"/>
+    <tableColumn id="9" xr3:uid="{CA4BAF3B-3E9D-4F31-A984-1BBC57B1761E}" name="GKTN" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{8E43F492-DA8D-4B36-992F-8FF2ED3BA73B}" name="CKTN" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{F54748B3-D956-40BA-B6D0-AC2C18A939C2}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{E68010E6-7545-4825-8A30-E7739A1C4C4A}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{E68010E6-7545-4825-8A30-E7739A1C4C4A}" name="Điểm cộng/trừ" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2717,12 +2865,12 @@
     <tableColumn id="4" xr3:uid="{7BD37775-2BE4-42D5-836D-E721DAE8F028}" name="Email"/>
     <tableColumn id="5" xr3:uid="{31926365-1D24-4CFE-BA60-8DB775984C5D}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{977019B1-D09A-42A2-BB7E-87A52F4F5FC5}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{83E63E51-16A0-4F7B-AD5B-954C67C5604E}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{83E63E51-16A0-4F7B-AD5B-954C67C5604E}" name="TX1" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{E12E76F6-5CAD-4D93-B39B-BEF9F29047D1}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{B9EA5CAD-C0AD-4602-B18F-77FA277F8DB7}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{8B0F90C0-A200-4C39-B887-17FF3D23FB8C}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{C3D25CAA-BDF5-4FE0-82DF-D8A37B9D0D87}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{1F6CE7C5-9460-4818-BE04-86FDB1B4A51B}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{1F6CE7C5-9460-4818-BE04-86FDB1B4A51B}" name="Điểm cộng/trừ" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2739,12 +2887,12 @@
     <tableColumn id="4" xr3:uid="{C834A720-51FC-4C56-8876-916F6364A386}" name="Email"/>
     <tableColumn id="5" xr3:uid="{6FB130F4-A05E-4FDC-B2DA-22E94D5D3B81}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{60B78D02-D560-431E-8870-83F119B73156}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{C3793044-9978-49A7-9D3A-45059A554ABC}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{C3793044-9978-49A7-9D3A-45059A554ABC}" name="TX1" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{E363DFF6-1A16-48AE-B1F0-2A19DD4C324E}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{F678A0CD-2F7B-4590-82F6-896BD825BC54}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{FBC07A04-980A-40A1-B291-5F4C36722B6A}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{1E86EEE0-3C4E-441A-AF40-2F0A70054A22}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{7F492110-3F4E-4B88-9286-10B4D422DBF3}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{7F492110-3F4E-4B88-9286-10B4D422DBF3}" name="Điểm cộng/trừ" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2761,14 +2909,14 @@
     <tableColumn id="4" xr3:uid="{06BB6758-BB6D-4290-B77F-4E8EEA74F35D}" name="Email"/>
     <tableColumn id="5" xr3:uid="{33C0ABE3-FAC4-4D07-BF8A-BBC8667CC653}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{860FF401-193A-4CEF-A318-711475F896D5}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{9DB0F73A-AF64-4B12-A1B2-292C31ABAD85}" name="TX1"/>
+    <tableColumn id="7" xr3:uid="{9DB0F73A-AF64-4B12-A1B2-292C31ABAD85}" name="TX1" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{B2D8B9D4-A9A6-4707-9FE9-196AB7FAD70B}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{CC905B07-3171-4DB1-8DE4-D4812DC9F8D9}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{6B9636A9-2F54-4EDD-AA38-33B1287A1DFA}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{25C5BFA4-7959-4B67-AAFA-4499322AA35A}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{4794BE50-1508-4F5D-BDA5-0D795E511169}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{20B8C87E-B4C2-46B2-A1EE-45C5B13A49F5}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{0E49A624-F415-4FEC-A84F-1976E399D991}" name="Điểm cộng/trừ"/>
+    <tableColumn id="13" xr3:uid="{0E49A624-F415-4FEC-A84F-1976E399D991}" name="Điểm cộng/trừ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3092,16 +3240,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E62F6F0-A60C-46AE-A379-677AAC706EA5}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3123,7 +3272,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -3144,11 +3293,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3170,7 +3319,7 @@
       <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>9.3000000000000007</v>
       </c>
       <c r="I2">
@@ -3185,12 +3334,15 @@
       <c r="L2">
         <v>4</v>
       </c>
-      <c r="O2">
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="O2" s="9">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3212,14 +3364,14 @@
       <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -3227,1029 +3379,1084 @@
       <c r="L3">
         <v>4</v>
       </c>
-      <c r="O3">
+      <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>1906042</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="O4" s="9">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>1906042</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <v>6</v>
-      </c>
-      <c r="L4">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>1906045</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
         <v>4</v>
       </c>
-      <c r="O4">
+      <c r="M5" s="6">
+        <v>6</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>1906054</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="O6" s="9">
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>1906056</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="5">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" s="6">
+        <v>6</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>1906064</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="5">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8" s="6">
+        <v>6</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>1906085</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="5">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+      <c r="M9" s="6">
+        <v>6</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>1906091</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10" s="6">
+        <v>6</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <v>1906104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11" s="6">
+        <v>6</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12">
+        <v>1906106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="5">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>6</v>
+      </c>
+      <c r="L12">
+        <v>4</v>
+      </c>
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13">
+        <v>1906111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="5">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>10</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14">
+        <v>1906123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="I14">
+        <v>8.5</v>
+      </c>
+      <c r="J14">
+        <v>9.5</v>
+      </c>
+      <c r="K14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14" s="6">
+        <v>4.95</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15">
+        <v>1911004</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="5">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>9.5</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>5.7</v>
+      </c>
+      <c r="L15">
+        <v>4</v>
+      </c>
+      <c r="M15">
+        <v>5.7</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16">
+        <v>1908001</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="5">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
+      <c r="M16">
+        <v>6</v>
+      </c>
+      <c r="O16" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="3" customFormat="1">
+      <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1906139</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="5">
+        <v>9</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="L17" s="3">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18">
+        <v>1906141</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="5">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <v>4</v>
+      </c>
+      <c r="M18">
+        <v>6</v>
+      </c>
+      <c r="O18" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19">
+        <v>1906142</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
+      <c r="M19">
+        <v>6</v>
+      </c>
+      <c r="O19" s="9">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5">
-        <v>1906045</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20">
+        <v>1906153</v>
+      </c>
+      <c r="E20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="5">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K20">
+        <v>5.4</v>
+      </c>
+      <c r="L20">
+        <v>4</v>
+      </c>
+      <c r="M20" s="6">
+        <v>4.95</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21">
+        <v>1906160</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="5">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="K21">
+        <v>6</v>
+      </c>
+      <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
+        <v>6</v>
+      </c>
+      <c r="O21" s="9">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22">
+        <v>1906173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="5">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>6</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22" s="6">
+        <v>6</v>
+      </c>
+      <c r="O22" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23">
+        <v>1906182</v>
+      </c>
+      <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="5">
+        <v>8</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23">
         <v>5.7</v>
       </c>
-      <c r="L5">
+      <c r="L23">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="M23">
+        <v>5.4</v>
+      </c>
+      <c r="O23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24">
+        <v>1906197</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="5">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24">
+        <v>4</v>
+      </c>
+      <c r="M24" s="6">
+        <v>6</v>
+      </c>
+      <c r="O24" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25">
+        <v>1910010</v>
+      </c>
+      <c r="E25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5">
+        <v>10</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>6</v>
+      </c>
+      <c r="O25" s="9">
+        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
+        <v>1.25</v>
+      </c>
+      <c r="P25">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26">
+        <v>1909014</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="5">
+        <v>10</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26">
+        <v>6</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26" s="6">
+        <v>6</v>
+      </c>
+      <c r="O26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27">
+        <v>1907001</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="5">
+        <v>10</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27">
+        <v>6</v>
+      </c>
+      <c r="L27">
+        <v>4</v>
+      </c>
+      <c r="M27">
+        <v>6</v>
+      </c>
+      <c r="O27" s="9">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>1906054</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="O6">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>1906056</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>5.7</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="O7">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8">
-        <v>1906064</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>6</v>
-      </c>
-      <c r="L8">
-        <v>4</v>
-      </c>
-      <c r="O8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9">
-        <v>1906085</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>10</v>
-      </c>
-      <c r="K9">
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
-      <c r="O9">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>1906091</v>
-      </c>
-      <c r="E10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>10</v>
-      </c>
-      <c r="K10">
-        <v>5.7</v>
-      </c>
-      <c r="L10">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11">
-        <v>1906104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>4</v>
-      </c>
-      <c r="O11">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12">
-        <v>1906106</v>
-      </c>
-      <c r="E12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>5.7</v>
-      </c>
-      <c r="L12">
-        <v>4</v>
-      </c>
-      <c r="O12">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13">
-        <v>1906111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13">
-        <v>10</v>
-      </c>
-      <c r="K13">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>4</v>
-      </c>
-      <c r="O13">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14">
-        <v>1906123</v>
-      </c>
-      <c r="E14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14">
-        <v>9.5</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-      <c r="J14">
-        <v>9.5</v>
-      </c>
-      <c r="K14">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L14">
-        <v>4</v>
-      </c>
-      <c r="O14">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15">
-        <v>1911004</v>
-      </c>
-      <c r="E15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15">
-        <v>8</v>
-      </c>
-      <c r="J15">
-        <v>10</v>
-      </c>
-      <c r="K15">
-        <v>5.7</v>
-      </c>
-      <c r="L15">
-        <v>4</v>
-      </c>
-      <c r="O15">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16">
-        <v>1908001</v>
-      </c>
-      <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16">
-        <v>10</v>
-      </c>
-      <c r="K16">
-        <v>6</v>
-      </c>
-      <c r="L16">
-        <v>4</v>
-      </c>
-      <c r="O16">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>2.25</v>
-      </c>
-      <c r="P16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17">
-        <v>1906139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17">
-        <v>9</v>
-      </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <v>10</v>
-      </c>
-      <c r="K17">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L17">
-        <v>4</v>
-      </c>
-      <c r="O17">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18">
-        <v>1906141</v>
-      </c>
-      <c r="E18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18">
-        <v>10</v>
-      </c>
-      <c r="K18">
-        <v>6</v>
-      </c>
-      <c r="L18">
-        <v>4</v>
-      </c>
-      <c r="O18">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19">
-        <v>1906142</v>
-      </c>
-      <c r="E19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I19">
-        <v>10</v>
-      </c>
-      <c r="J19">
-        <v>10</v>
-      </c>
-      <c r="K19">
-        <v>6</v>
-      </c>
-      <c r="L19">
-        <v>4</v>
-      </c>
-      <c r="O19">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20">
-        <v>1906153</v>
-      </c>
-      <c r="E20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20">
-        <v>10</v>
-      </c>
-      <c r="I20">
-        <v>10</v>
-      </c>
-      <c r="J20">
-        <v>7</v>
-      </c>
-      <c r="K20">
-        <v>5.4</v>
-      </c>
-      <c r="L20">
-        <v>4</v>
-      </c>
-      <c r="O20">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21">
-        <v>1906160</v>
-      </c>
-      <c r="E21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21">
-        <v>10</v>
-      </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>10</v>
-      </c>
-      <c r="K21">
-        <v>6</v>
-      </c>
-      <c r="L21">
-        <v>4</v>
-      </c>
-      <c r="O21">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.75</v>
-      </c>
-      <c r="P21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22">
-        <v>1906173</v>
-      </c>
-      <c r="E22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22">
-        <v>10</v>
-      </c>
-      <c r="K22">
-        <v>6</v>
-      </c>
-      <c r="L22">
-        <v>4</v>
-      </c>
-      <c r="O22">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23">
-        <v>1906182</v>
-      </c>
-      <c r="E23" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23">
-        <v>8</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>10</v>
-      </c>
-      <c r="K23">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L23">
-        <v>4</v>
-      </c>
-      <c r="O23">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24">
-        <v>1906197</v>
-      </c>
-      <c r="E24" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24">
-        <v>10</v>
-      </c>
-      <c r="I24">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>10</v>
-      </c>
-      <c r="K24">
-        <v>6</v>
-      </c>
-      <c r="L24">
-        <v>4</v>
-      </c>
-      <c r="O24">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25">
-        <v>1910010</v>
-      </c>
-      <c r="E25" t="s">
-        <v>132</v>
-      </c>
-      <c r="F25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>10</v>
-      </c>
-      <c r="K25">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>4</v>
-      </c>
-      <c r="O25">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-      <c r="P25">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26">
-        <v>1909014</v>
-      </c>
-      <c r="E26" t="s">
-        <v>136</v>
-      </c>
-      <c r="F26" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26">
-        <v>10</v>
-      </c>
-      <c r="J26">
-        <v>10</v>
-      </c>
-      <c r="K26">
-        <v>6</v>
-      </c>
-      <c r="L26">
-        <v>4</v>
-      </c>
-      <c r="O26">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>139</v>
-      </c>
-      <c r="D27">
-        <v>1907001</v>
-      </c>
-      <c r="E27" t="s">
-        <v>140</v>
-      </c>
-      <c r="F27" t="s">
-        <v>141</v>
-      </c>
-      <c r="G27" t="s">
-        <v>142</v>
-      </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-      <c r="I27">
-        <v>10</v>
-      </c>
-      <c r="J27">
-        <v>10</v>
-      </c>
-      <c r="K27">
-        <v>6</v>
-      </c>
-      <c r="L27">
-        <v>4</v>
-      </c>
-      <c r="O27">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4271,7 +4478,7 @@
       <c r="G28" t="s">
         <v>147</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>10</v>
       </c>
       <c r="I28">
@@ -4281,17 +4488,19 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>4</v>
       </c>
-      <c r="O28">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M28" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="O28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -4313,7 +4522,7 @@
       <c r="G29" t="s">
         <v>152</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>10</v>
       </c>
       <c r="I29">
@@ -4328,12 +4537,14 @@
       <c r="L29">
         <v>4</v>
       </c>
-      <c r="O29">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M29" s="6">
+        <v>6</v>
+      </c>
+      <c r="O29" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -4355,7 +4566,7 @@
       <c r="G30" t="s">
         <v>157</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <v>10</v>
       </c>
       <c r="I30">
@@ -4370,7 +4581,10 @@
       <c r="L30">
         <v>4</v>
       </c>
-      <c r="O30">
+      <c r="M30">
+        <v>6</v>
+      </c>
+      <c r="O30" s="9">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
@@ -4389,16 +4603,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B7CE8A-3709-4982-8530-4B128DCF5EDD}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4420,7 +4635,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4441,11 +4656,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4467,7 +4682,7 @@
       <c r="G2" t="s">
         <v>162</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>10</v>
       </c>
       <c r="I2">
@@ -4482,11 +4697,14 @@
       <c r="L2">
         <v>4</v>
       </c>
-      <c r="O2">
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="O2" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4508,14 +4726,14 @@
       <c r="G3" t="s">
         <v>166</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>5.0999999999999996</v>
@@ -4523,11 +4741,14 @@
       <c r="L3">
         <v>4</v>
       </c>
-      <c r="O3">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>5.4</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -4549,7 +4770,7 @@
       <c r="G4" t="s">
         <v>170</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
       <c r="I4">
@@ -4564,11 +4785,14 @@
       <c r="L4">
         <v>4</v>
       </c>
-      <c r="O4">
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="O4" s="9">
         <v>2.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4590,7 +4814,7 @@
       <c r="G5" t="s">
         <v>174</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>10</v>
       </c>
       <c r="I5">
@@ -4605,11 +4829,14 @@
       <c r="L5">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="O5" s="9">
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4631,11 +4858,11 @@
       <c r="G6" t="s">
         <v>178</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>8.5</v>
       </c>
       <c r="I6">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -4646,11 +4873,14 @@
       <c r="L6">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4672,7 +4902,7 @@
       <c r="G7" t="s">
         <v>182</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>10</v>
       </c>
       <c r="I7">
@@ -4682,16 +4912,19 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="L7">
         <v>4</v>
       </c>
-      <c r="O7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>5.7</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4713,13 +4946,13 @@
       <c r="G8" t="s">
         <v>186</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>9.5</v>
       </c>
       <c r="I8">
-        <v>8.5</v>
-      </c>
-      <c r="J8">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J8" s="4">
         <v>0</v>
       </c>
       <c r="K8">
@@ -4728,11 +4961,14 @@
       <c r="L8">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -4754,7 +4990,7 @@
       <c r="G9" t="s">
         <v>190</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>10</v>
       </c>
       <c r="I9">
@@ -4769,52 +5005,56 @@
       <c r="L9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="M9">
+        <v>6</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1">
+      <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>1910003</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>6.5</v>
-      </c>
-      <c r="J10">
-        <v>10</v>
-      </c>
-      <c r="K10">
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="J10" s="3">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3">
         <v>5.4</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="3">
         <v>4</v>
       </c>
-      <c r="O10">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M10" s="4"/>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -4836,7 +5076,7 @@
       <c r="G11" t="s">
         <v>170</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>10</v>
       </c>
       <c r="I11">
@@ -4851,11 +5091,14 @@
       <c r="L11">
         <v>4</v>
       </c>
-      <c r="O11">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>6</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -4877,7 +5120,7 @@
       <c r="G12" t="s">
         <v>201</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>10</v>
       </c>
       <c r="I12">
@@ -4892,11 +5135,14 @@
       <c r="L12">
         <v>4</v>
       </c>
-      <c r="O12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="O12" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -4918,7 +5164,7 @@
       <c r="G13" t="s">
         <v>205</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>10</v>
       </c>
       <c r="I13">
@@ -4933,14 +5179,17 @@
       <c r="L13">
         <v>4</v>
       </c>
-      <c r="O13">
-        <v>2</v>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="O13" s="9">
+        <v>1.25</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -4962,7 +5211,7 @@
       <c r="G14" t="s">
         <v>209</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>10</v>
       </c>
       <c r="I14">
@@ -4977,11 +5226,14 @@
       <c r="L14">
         <v>4</v>
       </c>
-      <c r="O14">
+      <c r="M14">
+        <v>6</v>
+      </c>
+      <c r="O14" s="9">
         <v>1.25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -5003,7 +5255,7 @@
       <c r="G15" t="s">
         <v>213</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>10</v>
       </c>
       <c r="I15">
@@ -5018,11 +5270,14 @@
       <c r="L15">
         <v>4</v>
       </c>
-      <c r="O15">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M15">
+        <v>6</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -5044,7 +5299,7 @@
       <c r="G16" t="s">
         <v>217</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>10</v>
       </c>
       <c r="I16">
@@ -5054,16 +5309,19 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>4</v>
       </c>
-      <c r="O16">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>6</v>
+      </c>
+      <c r="O16" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -5085,7 +5343,7 @@
       <c r="G17" t="s">
         <v>221</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>10</v>
       </c>
       <c r="I17">
@@ -5100,11 +5358,14 @@
       <c r="L17">
         <v>4</v>
       </c>
-      <c r="O17">
+      <c r="M17">
+        <v>6</v>
+      </c>
+      <c r="O17" s="9">
         <v>2.25</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -5126,7 +5387,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>10</v>
       </c>
       <c r="I18">
@@ -5141,14 +5402,17 @@
       <c r="L18">
         <v>4</v>
       </c>
-      <c r="O18">
+      <c r="M18">
+        <v>6</v>
+      </c>
+      <c r="O18" s="9">
         <v>1.5</v>
       </c>
       <c r="P18">
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5170,7 +5434,7 @@
       <c r="G19" t="s">
         <v>229</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>10</v>
       </c>
       <c r="I19">
@@ -5185,11 +5449,14 @@
       <c r="L19">
         <v>4</v>
       </c>
-      <c r="O19">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>6</v>
+      </c>
+      <c r="O19" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -5211,7 +5478,7 @@
       <c r="G20" t="s">
         <v>233</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>10</v>
       </c>
       <c r="I20">
@@ -5226,11 +5493,14 @@
       <c r="L20">
         <v>4</v>
       </c>
-      <c r="O20">
+      <c r="M20">
+        <v>6</v>
+      </c>
+      <c r="O20" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5252,7 +5522,7 @@
       <c r="G21" t="s">
         <v>237</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>9.5</v>
       </c>
       <c r="I21">
@@ -5262,16 +5532,19 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
-      <c r="O21">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>5.8</v>
+      </c>
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -5293,14 +5566,14 @@
       <c r="G22" t="s">
         <v>241</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
       <c r="J22">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -5308,11 +5581,14 @@
       <c r="L22">
         <v>4</v>
       </c>
-      <c r="O22">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M22">
+        <v>5.8</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -5334,14 +5610,14 @@
       <c r="G23" t="s">
         <v>245</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -5349,11 +5625,14 @@
       <c r="L23">
         <v>4</v>
       </c>
-      <c r="O23">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M23">
+        <v>5.6</v>
+      </c>
+      <c r="O23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5375,7 +5654,7 @@
       <c r="G24" t="s">
         <v>249</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>9.5</v>
       </c>
       <c r="I24">
@@ -5390,11 +5669,14 @@
       <c r="L24">
         <v>4</v>
       </c>
-      <c r="O24">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="O24" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -5416,7 +5698,7 @@
       <c r="G25" t="s">
         <v>253</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>10</v>
       </c>
       <c r="I25">
@@ -5431,11 +5713,14 @@
       <c r="L25">
         <v>4</v>
       </c>
-      <c r="O25">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M25">
+        <v>6</v>
+      </c>
+      <c r="O25" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -5457,11 +5742,11 @@
       <c r="G26" t="s">
         <v>249</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>10</v>
       </c>
       <c r="I26">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>10</v>
@@ -5472,11 +5757,14 @@
       <c r="L26">
         <v>4</v>
       </c>
-      <c r="O26">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M26">
+        <v>5.9</v>
+      </c>
+      <c r="O26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -5498,7 +5786,7 @@
       <c r="G27" t="s">
         <v>225</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>10</v>
       </c>
       <c r="I27">
@@ -5513,11 +5801,14 @@
       <c r="L27">
         <v>4</v>
       </c>
-      <c r="O27">
+      <c r="M27">
+        <v>6</v>
+      </c>
+      <c r="O27" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -5539,7 +5830,7 @@
       <c r="G28" t="s">
         <v>263</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>10</v>
       </c>
       <c r="I28">
@@ -5554,11 +5845,14 @@
       <c r="L28">
         <v>4</v>
       </c>
-      <c r="O28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M28">
+        <v>5.5</v>
+      </c>
+      <c r="O28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -5580,7 +5874,7 @@
       <c r="G29" t="s">
         <v>217</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>10</v>
       </c>
       <c r="I29">
@@ -5595,11 +5889,14 @@
       <c r="L29">
         <v>4</v>
       </c>
-      <c r="O29">
+      <c r="M29">
+        <v>6</v>
+      </c>
+      <c r="O29" s="9">
         <v>1.25</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5621,7 +5918,7 @@
       <c r="G30" t="s">
         <v>270</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <v>10</v>
       </c>
       <c r="I30">
@@ -5631,13 +5928,16 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>4</v>
       </c>
-      <c r="O30">
-        <v>1.25</v>
+      <c r="M30">
+        <v>6</v>
+      </c>
+      <c r="O30" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5651,16 +5951,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31AEED-D516-49B6-A6FF-F6CDC6895127}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5682,7 +5983,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -5697,11 +5998,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -5723,14 +6024,23 @@
       <c r="G2" t="s">
         <v>275</v>
       </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="6">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -5752,14 +6062,23 @@
       <c r="G3" t="s">
         <v>279</v>
       </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="M3">
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3" s="6">
+        <v>10</v>
+      </c>
+      <c r="K3" s="6">
+        <v>6</v>
+      </c>
+      <c r="M3" s="9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -5781,14 +6100,23 @@
       <c r="G4" t="s">
         <v>283</v>
       </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="M4">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6">
+        <v>6</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -5810,14 +6138,23 @@
       <c r="G5" t="s">
         <v>287</v>
       </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="M5">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5" s="6">
+        <v>10</v>
+      </c>
+      <c r="K5" s="6">
+        <v>6</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -5839,43 +6176,57 @@
       <c r="G6" t="s">
         <v>291</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="3" customFormat="1">
+      <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>2006111</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="5">
         <v>8</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I7" s="4"/>
+      <c r="J7" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -5897,14 +6248,23 @@
       <c r="G8" t="s">
         <v>299</v>
       </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H8" s="5">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8" s="6">
+        <v>10</v>
+      </c>
+      <c r="K8" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -5926,14 +6286,23 @@
       <c r="G9" t="s">
         <v>303</v>
       </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="M9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H9" s="5">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9" s="6">
+        <v>10</v>
+      </c>
+      <c r="K9" s="6">
+        <v>6</v>
+      </c>
+      <c r="M9" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -5955,14 +6324,23 @@
       <c r="G10" t="s">
         <v>307</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>9.3000000000000007</v>
       </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>9.5</v>
+      </c>
+      <c r="J10" s="6">
+        <v>9.75</v>
+      </c>
+      <c r="K10" s="6">
+        <v>6</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -5984,14 +6362,23 @@
       <c r="G11" t="s">
         <v>311</v>
       </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" s="6">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -6013,14 +6400,23 @@
       <c r="G12" t="s">
         <v>315</v>
       </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="M12">
+      <c r="H12" s="5">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" s="6">
+        <v>10</v>
+      </c>
+      <c r="K12" s="6">
+        <v>6</v>
+      </c>
+      <c r="M12" s="9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -6042,14 +6438,23 @@
       <c r="G13" t="s">
         <v>319</v>
       </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H13" s="5">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13" s="6">
+        <v>10</v>
+      </c>
+      <c r="K13" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -6071,14 +6476,23 @@
       <c r="G14" t="s">
         <v>323</v>
       </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="M14">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H14" s="5">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14" s="6">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -6100,14 +6514,23 @@
       <c r="G15" t="s">
         <v>327</v>
       </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H15" s="5">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K15" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -6129,14 +6552,23 @@
       <c r="G16" t="s">
         <v>331</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>8.5</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I16" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="J16" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="K16" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -6158,14 +6590,23 @@
       <c r="G17" t="s">
         <v>335</v>
       </c>
-      <c r="H17">
-        <v>10</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17" s="6">
+        <v>10</v>
+      </c>
+      <c r="K17" s="6">
+        <v>6</v>
+      </c>
+      <c r="M17" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -6187,14 +6628,23 @@
       <c r="G18" t="s">
         <v>339</v>
       </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="M18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H18" s="5">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18" s="6">
+        <v>10</v>
+      </c>
+      <c r="K18" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -6216,14 +6666,23 @@
       <c r="G19" t="s">
         <v>343</v>
       </c>
-      <c r="H19">
-        <v>10</v>
-      </c>
-      <c r="M19">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H19" s="5">
+        <v>10</v>
+      </c>
+      <c r="I19" s="4">
+        <v>6.25</v>
+      </c>
+      <c r="J19" s="6">
+        <v>9.75</v>
+      </c>
+      <c r="K19" s="6">
+        <v>6</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -6245,14 +6704,23 @@
       <c r="G20" t="s">
         <v>347</v>
       </c>
-      <c r="H20">
-        <v>10</v>
-      </c>
-      <c r="M20">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H20" s="5">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K20" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6274,14 +6742,23 @@
       <c r="G21" t="s">
         <v>351</v>
       </c>
-      <c r="H21">
-        <v>10</v>
-      </c>
-      <c r="M21">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H21" s="5">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="K21" s="6">
+        <v>6</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -6303,14 +6780,23 @@
       <c r="G22" t="s">
         <v>355</v>
       </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="M22">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H22" s="5">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22" s="6">
+        <v>10</v>
+      </c>
+      <c r="K22" s="6">
+        <v>6</v>
+      </c>
+      <c r="M22" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -6332,14 +6818,23 @@
       <c r="G23" t="s">
         <v>279</v>
       </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="M23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H23" s="5">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23" s="6">
+        <v>10</v>
+      </c>
+      <c r="K23" s="6">
+        <v>6</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -6361,14 +6856,23 @@
       <c r="G24" t="s">
         <v>362</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>9.5</v>
       </c>
-      <c r="M24">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I24" s="4">
+        <v>6.25</v>
+      </c>
+      <c r="J24" s="6">
+        <v>9.25</v>
+      </c>
+      <c r="K24" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -6390,14 +6894,23 @@
       <c r="G25" t="s">
         <v>366</v>
       </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="M25">
+      <c r="H25" s="5">
+        <v>10</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25" s="6">
+        <v>10</v>
+      </c>
+      <c r="K25" s="6">
+        <v>6</v>
+      </c>
+      <c r="M25" s="9">
         <v>1.75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -6419,14 +6932,23 @@
       <c r="G26" t="s">
         <v>370</v>
       </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H26" s="5">
+        <v>10</v>
+      </c>
+      <c r="I26" s="4">
+        <v>7</v>
+      </c>
+      <c r="J26" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="K26" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -6448,14 +6970,23 @@
       <c r="G27" t="s">
         <v>374</v>
       </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-      <c r="M27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H27" s="5">
+        <v>10</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27" s="6">
+        <v>10</v>
+      </c>
+      <c r="K27" s="6">
+        <v>6</v>
+      </c>
+      <c r="M27" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -6477,14 +7008,23 @@
       <c r="G28" t="s">
         <v>378</v>
       </c>
-      <c r="H28">
-        <v>10</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H28" s="5">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="K28" s="6">
+        <v>5</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -6506,14 +7046,23 @@
       <c r="G29" t="s">
         <v>382</v>
       </c>
-      <c r="H29">
-        <v>10</v>
-      </c>
-      <c r="M29">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H29" s="5">
+        <v>10</v>
+      </c>
+      <c r="I29" s="4">
+        <v>5.75</v>
+      </c>
+      <c r="J29" s="6">
+        <v>10</v>
+      </c>
+      <c r="K29" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -6535,14 +7084,23 @@
       <c r="G30" t="s">
         <v>386</v>
       </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-      <c r="M30">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H30" s="5">
+        <v>10</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30" s="6">
+        <v>10</v>
+      </c>
+      <c r="K30" s="6">
+        <v>6</v>
+      </c>
+      <c r="M30" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -6564,11 +7122,20 @@
       <c r="G31" t="s">
         <v>391</v>
       </c>
-      <c r="H31">
-        <v>10</v>
-      </c>
-      <c r="M31">
-        <v>1.25</v>
+      <c r="H31" s="5">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31" s="6">
+        <v>10</v>
+      </c>
+      <c r="K31" s="6">
+        <v>6</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6582,16 +7149,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4EC707-71B4-4E8F-AC0E-96DAFCEEB03D}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="35.42578125" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6613,7 +7181,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -6628,11 +7196,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -6654,14 +7222,23 @@
       <c r="G2" t="s">
         <v>396</v>
       </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="6">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6">
+        <v>6</v>
+      </c>
+      <c r="M2" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -6683,14 +7260,23 @@
       <c r="G3" t="s">
         <v>400</v>
       </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="M3">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="K3" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -6712,14 +7298,23 @@
       <c r="G4" t="s">
         <v>404</v>
       </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6741,14 +7336,23 @@
       <c r="G5" t="s">
         <v>408</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I5" s="4">
+        <v>6</v>
+      </c>
+      <c r="J5" s="6">
+        <v>7.75</v>
+      </c>
+      <c r="K5" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -6770,14 +7374,23 @@
       <c r="G6" t="s">
         <v>412</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -6799,14 +7412,23 @@
       <c r="G7" t="s">
         <v>416</v>
       </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H7" s="5">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7" s="6">
+        <v>10</v>
+      </c>
+      <c r="K7" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -6828,14 +7450,23 @@
       <c r="G8" t="s">
         <v>420</v>
       </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H8" s="5">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8" s="6">
+        <v>10</v>
+      </c>
+      <c r="K8" s="6">
+        <v>6</v>
+      </c>
+      <c r="M8" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -6857,14 +7488,23 @@
       <c r="G9" t="s">
         <v>424</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>9</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9" s="6">
+        <v>8.75</v>
+      </c>
+      <c r="K9" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -6886,14 +7526,23 @@
       <c r="G10" t="s">
         <v>428</v>
       </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10" s="6">
+        <v>10</v>
+      </c>
+      <c r="K10" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -6915,14 +7564,23 @@
       <c r="G11" t="s">
         <v>323</v>
       </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="M11">
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" s="6">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -6944,14 +7602,23 @@
       <c r="G12" t="s">
         <v>435</v>
       </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="M12">
+      <c r="H12" s="5">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" s="6">
+        <v>10</v>
+      </c>
+      <c r="K12" s="6">
+        <v>6</v>
+      </c>
+      <c r="M12" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -6973,14 +7640,23 @@
       <c r="G13" t="s">
         <v>435</v>
       </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="M13">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H13" s="5">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13" s="6">
+        <v>10</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7002,14 +7678,23 @@
       <c r="G14" t="s">
         <v>442</v>
       </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="M14">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H14" s="5">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="K14" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -7031,14 +7716,23 @@
       <c r="G15" t="s">
         <v>446</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>9</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I15" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="J15" s="6">
+        <v>8</v>
+      </c>
+      <c r="K15" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -7060,14 +7754,23 @@
       <c r="G16" t="s">
         <v>362</v>
       </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="M16">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H16" s="5">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="K16" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -7089,14 +7792,23 @@
       <c r="G17" t="s">
         <v>453</v>
       </c>
-      <c r="H17">
-        <v>10</v>
-      </c>
-      <c r="M17">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17" s="6">
+        <v>10</v>
+      </c>
+      <c r="K17" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -7118,14 +7830,23 @@
       <c r="G18" t="s">
         <v>457</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>9</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I18" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="J18" s="6">
+        <v>9.25</v>
+      </c>
+      <c r="K18" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -7147,14 +7868,23 @@
       <c r="G19" t="s">
         <v>461</v>
       </c>
-      <c r="H19">
-        <v>10</v>
-      </c>
-      <c r="M19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H19" s="5">
+        <v>10</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19" s="6">
+        <v>10</v>
+      </c>
+      <c r="K19" s="6">
+        <v>6</v>
+      </c>
+      <c r="M19" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -7176,14 +7906,23 @@
       <c r="G20" t="s">
         <v>382</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>9</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20" s="6">
+        <v>9</v>
+      </c>
+      <c r="K20" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -7205,14 +7944,23 @@
       <c r="G21" t="s">
         <v>468</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>8</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I21" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J21" s="6">
+        <v>6.75</v>
+      </c>
+      <c r="K21" s="6">
+        <v>3.75</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -7234,14 +7982,23 @@
       <c r="G22" t="s">
         <v>472</v>
       </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H22" s="5">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22" s="6">
+        <v>10</v>
+      </c>
+      <c r="K22" s="6">
+        <v>6</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -7263,14 +8020,23 @@
       <c r="G23" t="s">
         <v>370</v>
       </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="M23">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H23" s="5">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23" s="6">
+        <v>10</v>
+      </c>
+      <c r="K23" s="6">
+        <v>6</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -7292,14 +8058,23 @@
       <c r="G24" t="s">
         <v>479</v>
       </c>
-      <c r="H24">
-        <v>10</v>
-      </c>
-      <c r="M24">
+      <c r="H24" s="5">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24" s="6">
+        <v>10</v>
+      </c>
+      <c r="K24" s="6">
+        <v>6</v>
+      </c>
+      <c r="M24" s="9">
         <v>3.75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -7321,14 +8096,23 @@
       <c r="G25" t="s">
         <v>483</v>
       </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="M25">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H25" s="5">
+        <v>10</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25" s="6">
+        <v>10</v>
+      </c>
+      <c r="K25" s="6">
+        <v>6</v>
+      </c>
+      <c r="M25" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -7350,14 +8134,23 @@
       <c r="G26" t="s">
         <v>487</v>
       </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="M26">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H26" s="5">
+        <v>10</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26" s="6">
+        <v>10</v>
+      </c>
+      <c r="K26" s="6">
+        <v>6</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -7379,14 +8172,23 @@
       <c r="G27" t="s">
         <v>491</v>
       </c>
-      <c r="H27">
-        <v>10</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H27" s="5">
+        <v>10</v>
+      </c>
+      <c r="I27" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="J27" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K27" s="6">
+        <v>5</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -7408,14 +8210,23 @@
       <c r="G28" t="s">
         <v>495</v>
       </c>
-      <c r="H28">
-        <v>10</v>
-      </c>
-      <c r="M28">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H28" s="5">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28" s="6">
+        <v>10</v>
+      </c>
+      <c r="K28" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -7437,14 +8248,23 @@
       <c r="G29" t="s">
         <v>499</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>9.5</v>
       </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29" s="6">
+        <v>10</v>
+      </c>
+      <c r="K29" s="6">
+        <v>6</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -7466,14 +8286,23 @@
       <c r="G30" t="s">
         <v>503</v>
       </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-      <c r="M30">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H30" s="5">
+        <v>10</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30" s="6">
+        <v>10</v>
+      </c>
+      <c r="K30" s="6">
+        <v>6</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -7495,11 +8324,20 @@
       <c r="G31" t="s">
         <v>507</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="5">
         <v>7</v>
       </c>
-      <c r="M31">
-        <v>1</v>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K31" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7513,18 +8351,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195B8901-376D-4489-8560-7242E57D3B44}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="8" max="8" width="8" style="5" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7546,7 +8384,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -7561,11 +8399,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -7587,22 +8425,24 @@
       <c r="G2" t="s">
         <v>351</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2">
-        <v>9.5</v>
+      <c r="J2" s="6">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6">
+        <v>5.6</v>
       </c>
       <c r="L2" s="2"/>
-      <c r="M2">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -7624,20 +8464,23 @@
       <c r="G3" t="s">
         <v>515</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3">
-        <v>9.5</v>
-      </c>
-      <c r="M3">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J3" s="6">
+        <v>10</v>
+      </c>
+      <c r="K3" s="6">
+        <v>6</v>
+      </c>
+      <c r="M3" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -7659,20 +8502,23 @@
       <c r="G4" t="s">
         <v>519</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-      <c r="M4">
+      <c r="J4" s="6">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6">
+        <v>6</v>
+      </c>
+      <c r="M4" s="9">
         <v>2.75</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -7694,20 +8540,23 @@
       <c r="G5" t="s">
         <v>523</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="6">
         <v>9</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K5" s="6">
+        <v>6</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -7729,20 +8578,23 @@
       <c r="G6" t="s">
         <v>527</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6">
-        <v>9.25</v>
-      </c>
-      <c r="M6">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J6" s="6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6">
+        <v>5</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -7764,20 +8616,23 @@
       <c r="G7" t="s">
         <v>531</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>8</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7">
-        <v>8.25</v>
-      </c>
-      <c r="M7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J7" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="K7" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -7799,20 +8654,23 @@
       <c r="G8" t="s">
         <v>535</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>9.3000000000000007</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8">
-        <v>9.25</v>
-      </c>
-      <c r="M8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="6">
+        <v>9.4</v>
+      </c>
+      <c r="K8" s="6">
+        <v>5</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -7834,20 +8692,23 @@
       <c r="G9" t="s">
         <v>539</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>9</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-      <c r="M9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J9" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="K9" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -7869,21 +8730,23 @@
       <c r="G10" t="s">
         <v>543</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>10</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10">
-        <v>6.5</v>
-      </c>
-      <c r="M10">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J10" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="K10" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -7905,20 +8768,23 @@
       <c r="G11" t="s">
         <v>547</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11">
-        <v>9.5</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="6">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -7940,21 +8806,23 @@
       <c r="G12" t="s">
         <v>442</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>8.5</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12">
-        <v>9</v>
-      </c>
-      <c r="M12">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K12" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -7976,20 +8844,23 @@
       <c r="G13" t="s">
         <v>554</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>9.5</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13">
-        <v>9.75</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="6">
+        <v>10</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -8011,20 +8882,23 @@
       <c r="G14" t="s">
         <v>558</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>8.5</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14">
-        <v>8.5</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="6">
+        <v>9</v>
+      </c>
+      <c r="K14" s="6">
+        <v>6</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -8046,20 +8920,23 @@
       <c r="G15" t="s">
         <v>562</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="6">
         <v>9.5</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K15" s="6">
+        <v>6</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -8081,21 +8958,23 @@
       <c r="G16" t="s">
         <v>535</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>9.5</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
-      <c r="J16">
-        <v>8.5</v>
-      </c>
-      <c r="M16">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J16" s="6">
+        <v>8.6</v>
+      </c>
+      <c r="K16" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -8117,21 +8996,23 @@
       <c r="G17" t="s">
         <v>569</v>
       </c>
-      <c r="H17">
-        <v>10</v>
-      </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4">
+        <v>9.25</v>
+      </c>
+      <c r="J17" s="6">
         <v>8.75</v>
       </c>
-      <c r="M17">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K17" s="6">
+        <v>5</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -8153,21 +9034,23 @@
       <c r="G18" t="s">
         <v>573</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>10</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18">
-        <v>9.75</v>
-      </c>
-      <c r="M18">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J18" s="6">
+        <v>10</v>
+      </c>
+      <c r="K18" s="6">
+        <v>6</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -8189,20 +9072,23 @@
       <c r="G19" t="s">
         <v>577</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
-      <c r="J19">
-        <v>9.5</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J19" s="6">
+        <v>10</v>
+      </c>
+      <c r="K19" s="6">
+        <v>5</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -8224,21 +9110,24 @@
       <c r="G20" t="s">
         <v>581</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
-      <c r="J20">
-        <v>10</v>
-      </c>
-      <c r="M20">
+      <c r="J20" s="6">
+        <v>10</v>
+      </c>
+      <c r="K20" s="6">
+        <v>6</v>
+      </c>
+      <c r="M20" s="9">
         <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>2.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8260,20 +9149,23 @@
       <c r="G21" t="s">
         <v>585</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>9.5</v>
       </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
+      <c r="I21" s="4">
+        <v>8.75</v>
+      </c>
+      <c r="J21" s="6">
         <v>9.25</v>
       </c>
-      <c r="M21">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K21" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -8295,21 +9187,23 @@
       <c r="G22" t="s">
         <v>303</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22">
+      <c r="I22" s="4">
         <v>9.75</v>
       </c>
-      <c r="M22">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J22" s="6">
+        <v>9.75</v>
+      </c>
+      <c r="K22" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -8331,20 +9225,23 @@
       <c r="G23" t="s">
         <v>592</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>9</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23">
-        <v>9.75</v>
-      </c>
-      <c r="M23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J23" s="6">
+        <v>10</v>
+      </c>
+      <c r="K23" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -8366,20 +9263,23 @@
       <c r="G24" t="s">
         <v>366</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24">
-        <v>10</v>
-      </c>
-      <c r="M24">
+      <c r="J24" s="6">
+        <v>10</v>
+      </c>
+      <c r="K24" s="6">
+        <v>6</v>
+      </c>
+      <c r="M24" s="9">
         <v>2.75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8401,21 +9301,23 @@
       <c r="G25" t="s">
         <v>424</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25">
-        <v>9.5</v>
-      </c>
-      <c r="M25">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J25" s="6">
+        <v>10</v>
+      </c>
+      <c r="K25" s="6">
+        <v>6</v>
+      </c>
+      <c r="M25" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -8437,20 +9339,23 @@
       <c r="G26" t="s">
         <v>446</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>9.8000000000000007</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
-      <c r="J26">
-        <v>8.5</v>
-      </c>
-      <c r="M26">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J26" s="6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K26" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -8472,20 +9377,23 @@
       <c r="G27" t="s">
         <v>605</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>9</v>
       </c>
-      <c r="I27">
-        <v>10</v>
-      </c>
-      <c r="J27">
+      <c r="I27" s="4">
         <v>9.5</v>
       </c>
-      <c r="M27">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J27" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K27" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -8507,20 +9415,23 @@
       <c r="G28" t="s">
         <v>569</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
-      <c r="J28">
-        <v>8.75</v>
-      </c>
-      <c r="M28">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J28" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K28" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -8542,20 +9453,23 @@
       <c r="G29" t="s">
         <v>378</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
-      <c r="J29">
-        <v>9.25</v>
-      </c>
-      <c r="M29">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J29" s="6">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K29" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -8577,17 +9491,20 @@
       <c r="G30" t="s">
         <v>615</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <v>10</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
-      <c r="J30">
-        <v>9</v>
-      </c>
-      <c r="M30">
-        <v>2.25</v>
+      <c r="J30" s="6">
+        <v>10</v>
+      </c>
+      <c r="K30" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8601,16 +9518,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC312E2-BFEE-413B-B1C1-039BACF14471}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
+    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8632,7 +9550,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -8647,11 +9565,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -8673,21 +9591,24 @@
       <c r="G2" t="s">
         <v>620</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>9.3000000000000007</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2">
-        <v>8.25</v>
+      <c r="J2" s="6">
+        <v>9</v>
+      </c>
+      <c r="K2" s="6">
+        <v>5.25</v>
       </c>
       <c r="L2" s="2"/>
-      <c r="M2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -8709,20 +9630,23 @@
       <c r="G3" t="s">
         <v>355</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3">
-        <v>9.75</v>
-      </c>
-      <c r="M3">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J3" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="K3" s="6">
+        <v>6</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -8744,20 +9668,23 @@
       <c r="G4" t="s">
         <v>627</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="6">
         <v>9.75</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K4" s="6">
+        <v>6</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -8779,20 +9706,23 @@
       <c r="G5" t="s">
         <v>382</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5">
-        <v>9.75</v>
-      </c>
-      <c r="M5">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J5" s="6">
+        <v>10</v>
+      </c>
+      <c r="K5" s="6">
+        <v>6</v>
+      </c>
+      <c r="M5" s="9">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -8814,20 +9744,23 @@
       <c r="G6" t="s">
         <v>634</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6">
-        <v>9.25</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J6" s="6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6">
+        <v>6</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -8849,20 +9782,23 @@
       <c r="G7" t="s">
         <v>638</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>10</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7">
-        <v>9.75</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J7" s="6">
+        <v>10</v>
+      </c>
+      <c r="K7" s="6">
+        <v>6</v>
+      </c>
+      <c r="M7" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -8884,20 +9820,23 @@
       <c r="G8" t="s">
         <v>642</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>9.5</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8">
-        <v>9.25</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="K8" s="6">
+        <v>5.25</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -8919,20 +9858,23 @@
       <c r="G9" t="s">
         <v>646</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>10</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9">
-        <v>10</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J9" s="6">
+        <v>10</v>
+      </c>
+      <c r="K9" s="6">
+        <v>6</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -8954,20 +9896,23 @@
       <c r="G10" t="s">
         <v>650</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>9.5</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10">
-        <v>9</v>
-      </c>
-      <c r="M10">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J10" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="K10" s="6">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -8989,20 +9934,23 @@
       <c r="G11" t="s">
         <v>654</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="6">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -9024,20 +9972,23 @@
       <c r="G12" t="s">
         <v>658</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>9.5</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12">
-        <v>9.5</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="6">
+        <v>10</v>
+      </c>
+      <c r="K12" s="6">
+        <v>5</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -9059,20 +10010,23 @@
       <c r="G13" t="s">
         <v>662</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>10</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13">
-        <v>9.5</v>
-      </c>
-      <c r="M13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -9094,20 +10048,23 @@
       <c r="G14" t="s">
         <v>666</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>9.5</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14">
-        <v>9.75</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="6">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
+        <v>6</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -9129,20 +10086,23 @@
       <c r="G15" t="s">
         <v>491</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15">
-        <v>9</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J15" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K15" s="6">
+        <v>6</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -9164,20 +10124,23 @@
       <c r="G16" t="s">
         <v>673</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>9.5</v>
       </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16">
+      <c r="I16" s="4">
         <v>9.5</v>
       </c>
-      <c r="M16">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J16" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="K16" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -9199,20 +10162,23 @@
       <c r="G17" t="s">
         <v>677</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>9</v>
       </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
+      <c r="I17" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J17" s="6">
         <v>7.75</v>
       </c>
-      <c r="M17">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K17" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -9234,20 +10200,23 @@
       <c r="G18" t="s">
         <v>331</v>
       </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18">
+      <c r="H18" s="5">
+        <v>10</v>
+      </c>
+      <c r="I18" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="J18" s="6">
         <v>8.25</v>
       </c>
-      <c r="M18">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K18" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -9269,20 +10238,23 @@
       <c r="G19" t="s">
         <v>684</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
-      <c r="J19">
-        <v>9.75</v>
-      </c>
-      <c r="M19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J19" s="6">
+        <v>10</v>
+      </c>
+      <c r="K19" s="6">
+        <v>6</v>
+      </c>
+      <c r="M19" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -9304,20 +10276,23 @@
       <c r="G20" t="s">
         <v>688</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>9.5</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="6">
         <v>8.75</v>
       </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K20" s="6">
+        <v>5</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9339,20 +10314,23 @@
       <c r="G21" t="s">
         <v>692</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>9.5</v>
       </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
+      <c r="I21" s="4">
+        <v>8</v>
+      </c>
+      <c r="J21" s="6">
         <v>8.5</v>
       </c>
-      <c r="M21">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K21" s="6">
+        <v>4</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -9374,20 +10352,23 @@
       <c r="G22" t="s">
         <v>627</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
-      <c r="J22">
-        <v>10</v>
-      </c>
-      <c r="M22">
+      <c r="J22" s="6">
+        <v>10</v>
+      </c>
+      <c r="K22" s="6">
+        <v>6</v>
+      </c>
+      <c r="M22" s="9">
         <v>3.25</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -9409,20 +10390,23 @@
       <c r="G23" t="s">
         <v>491</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23">
-        <v>9.25</v>
-      </c>
-      <c r="M23">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J23" s="6">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K23" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -9444,20 +10428,23 @@
       <c r="G24" t="s">
         <v>702</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24">
-        <v>10</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J24" s="6">
+        <v>10</v>
+      </c>
+      <c r="K24" s="6">
+        <v>6</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -9479,20 +10466,23 @@
       <c r="G25" t="s">
         <v>706</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25">
-        <v>10</v>
-      </c>
-      <c r="M25">
+      <c r="J25" s="6">
+        <v>10</v>
+      </c>
+      <c r="K25" s="6">
+        <v>6</v>
+      </c>
+      <c r="M25" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -9514,87 +10504,91 @@
       <c r="G26" t="s">
         <v>573</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>10</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
-      <c r="J26">
-        <v>10</v>
-      </c>
-      <c r="M26">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="J26" s="6">
+        <v>10</v>
+      </c>
+      <c r="K26" s="6">
+        <v>6</v>
+      </c>
+      <c r="M26" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="4" customFormat="1">
+      <c r="A27" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>2206254</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>8</v>
       </c>
-      <c r="I27">
-        <v>10</v>
-      </c>
-      <c r="M27">
+      <c r="I27" s="4">
+        <v>10</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="M27" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:13" s="3" customFormat="1">
+      <c r="A28" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="3">
         <v>2206058</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28">
-        <v>10</v>
-      </c>
-      <c r="J28">
+      <c r="H28" s="5">
+        <v>10</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="8">
         <v>8.75</v>
       </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K28" s="7"/>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -9616,17 +10610,20 @@
       <c r="G29" t="s">
         <v>446</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <v>10</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
-      <c r="J29">
-        <v>9.5</v>
-      </c>
-      <c r="M29">
-        <v>3.25</v>
+      <c r="J29" s="6">
+        <v>10</v>
+      </c>
+      <c r="K29" s="6">
+        <v>6</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -9640,17 +10637,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD567BBF-FA45-4BB7-A2DB-AA426EC5E0BA}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="5"/>
     <col min="11" max="12" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9672,7 +10670,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -9693,11 +10691,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9719,7 +10717,7 @@
       <c r="G2" t="s">
         <v>724</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>10</v>
       </c>
       <c r="I2">
@@ -9732,13 +10730,16 @@
         <v>6</v>
       </c>
       <c r="L2" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="O2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="O2" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -9760,7 +10761,7 @@
       <c r="G3" t="s">
         <v>728</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>10</v>
       </c>
       <c r="I3">
@@ -9770,16 +10771,19 @@
         <v>10</v>
       </c>
       <c r="K3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L3" s="3">
-        <v>3</v>
-      </c>
-      <c r="O3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>5.9</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -9801,26 +10805,29 @@
       <c r="G4" t="s">
         <v>732</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>10</v>
       </c>
       <c r="I4" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
       <c r="K4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L4" s="3">
         <v>3.8</v>
       </c>
-      <c r="O4">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>5.9</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -9842,11 +10849,11 @@
       <c r="G5" t="s">
         <v>737</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>10</v>
       </c>
       <c r="I5" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -9855,13 +10862,16 @@
         <v>6</v>
       </c>
       <c r="L5" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="O5">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -9883,7 +10893,7 @@
       <c r="G6" t="s">
         <v>741</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>10</v>
       </c>
       <c r="I6">
@@ -9893,16 +10903,19 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L6" s="3">
-        <v>3</v>
-      </c>
-      <c r="O6">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>5.6</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -9924,7 +10937,7 @@
       <c r="G7" t="s">
         <v>745</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>10</v>
       </c>
       <c r="I7">
@@ -9934,16 +10947,19 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="O7">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+      <c r="O7" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -9965,7 +10981,7 @@
       <c r="G8" t="s">
         <v>750</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>10</v>
       </c>
       <c r="I8">
@@ -9978,13 +10994,16 @@
         <v>6</v>
       </c>
       <c r="L8" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="O8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+      <c r="O8" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -10006,11 +11025,11 @@
       <c r="G9" t="s">
         <v>754</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>10</v>
       </c>
       <c r="I9" s="3">
-        <v>8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -10021,11 +11040,14 @@
       <c r="L9" s="3">
         <v>3.2</v>
       </c>
-      <c r="O9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>5.7</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -10047,11 +11069,11 @@
       <c r="G10" t="s">
         <v>758</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>10</v>
       </c>
       <c r="I10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -10060,13 +11082,16 @@
         <v>5.4</v>
       </c>
       <c r="L10" s="3">
-        <v>3</v>
-      </c>
-      <c r="O10">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3.3</v>
+      </c>
+      <c r="M10">
+        <v>5.6</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -10088,11 +11113,11 @@
       <c r="G11" t="s">
         <v>762</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>10</v>
       </c>
       <c r="I11" s="3">
-        <v>8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -10103,11 +11128,14 @@
       <c r="L11" s="3">
         <v>3.2</v>
       </c>
-      <c r="O11">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>5.7</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -10129,11 +11157,11 @@
       <c r="G12" t="s">
         <v>766</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>10</v>
       </c>
       <c r="I12" s="3">
-        <v>8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -10144,11 +11172,14 @@
       <c r="L12" s="3">
         <v>3.2</v>
       </c>
-      <c r="O12">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -10170,11 +11201,11 @@
       <c r="G13" t="s">
         <v>770</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>10</v>
       </c>
       <c r="I13" s="3">
-        <v>8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -10185,11 +11216,14 @@
       <c r="L13" s="3">
         <v>3.2</v>
       </c>
-      <c r="O13">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M13">
+        <v>5.7</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -10211,26 +11245,29 @@
       <c r="G14" t="s">
         <v>775</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>10</v>
       </c>
       <c r="I14" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
       <c r="K14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L14" s="3">
         <v>3.8</v>
       </c>
-      <c r="O14">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>6</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -10252,26 +11289,29 @@
       <c r="G15" t="s">
         <v>779</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>10</v>
       </c>
       <c r="I15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>10</v>
       </c>
       <c r="K15">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="M15">
         <v>5.7</v>
       </c>
-      <c r="L15" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="O15">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -10293,26 +11333,29 @@
       <c r="G16" t="s">
         <v>783</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>10</v>
       </c>
       <c r="I16" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>10</v>
       </c>
       <c r="K16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L16" s="3">
         <v>3.8</v>
       </c>
-      <c r="O16">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>5.8</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -10334,14 +11377,14 @@
       <c r="G17" t="s">
         <v>787</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>10</v>
       </c>
       <c r="I17" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K17">
         <v>5.6</v>
@@ -10349,11 +11392,14 @@
       <c r="L17" s="3">
         <v>3</v>
       </c>
-      <c r="O17">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <v>5.8</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -10375,26 +11421,29 @@
       <c r="G18" t="s">
         <v>791</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>10</v>
       </c>
       <c r="I18" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
       </c>
       <c r="K18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3">
         <v>3.8</v>
       </c>
-      <c r="O18">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M18">
+        <v>5.6</v>
+      </c>
+      <c r="O18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -10416,26 +11465,29 @@
       <c r="G19" t="s">
         <v>795</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>10</v>
       </c>
       <c r="I19" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>10</v>
       </c>
       <c r="K19">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L19" s="3">
         <v>3.8</v>
       </c>
-      <c r="O19">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>5.9</v>
+      </c>
+      <c r="O19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -10457,26 +11509,29 @@
       <c r="G20" t="s">
         <v>799</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>10</v>
       </c>
       <c r="I20" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
       <c r="K20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L20" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="O20">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3.8</v>
+      </c>
+      <c r="M20">
+        <v>6</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -10498,14 +11553,14 @@
       <c r="G21" t="s">
         <v>803</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>10</v>
       </c>
       <c r="I21" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J21" s="3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K21">
         <v>5.7</v>
@@ -10513,11 +11568,14 @@
       <c r="L21" s="3">
         <v>3</v>
       </c>
-      <c r="O21">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>5.5</v>
+      </c>
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -10539,11 +11597,11 @@
       <c r="G22" t="s">
         <v>807</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -10552,13 +11610,16 @@
         <v>5.6</v>
       </c>
       <c r="L22" s="3">
-        <v>3</v>
-      </c>
-      <c r="O22">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3.9</v>
+      </c>
+      <c r="M22">
+        <v>5.6</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -10580,11 +11641,11 @@
       <c r="G23" t="s">
         <v>811</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>10</v>
       </c>
       <c r="I23" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -10593,13 +11654,16 @@
         <v>6</v>
       </c>
       <c r="L23" s="3">
-        <v>3</v>
-      </c>
-      <c r="O23">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3.3</v>
+      </c>
+      <c r="M23">
+        <v>5.7</v>
+      </c>
+      <c r="O23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -10621,7 +11685,7 @@
       <c r="G24" t="s">
         <v>815</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>10</v>
       </c>
       <c r="I24">
@@ -10634,13 +11698,16 @@
         <v>6</v>
       </c>
       <c r="L24" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="O24">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="O24" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -10662,26 +11729,29 @@
       <c r="G25" t="s">
         <v>818</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>10</v>
       </c>
       <c r="I25" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>10</v>
       </c>
       <c r="K25">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L25" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="O25">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>5.8</v>
+      </c>
+      <c r="O25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -10703,7 +11773,7 @@
       <c r="G26" t="s">
         <v>822</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>10</v>
       </c>
       <c r="I26">
@@ -10713,16 +11783,19 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L26" s="3">
-        <v>3</v>
-      </c>
-      <c r="O26">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>6</v>
+      </c>
+      <c r="O26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -10744,11 +11817,11 @@
       <c r="G27" t="s">
         <v>826</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>10</v>
       </c>
       <c r="I27" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>10</v>
@@ -10757,13 +11830,16 @@
         <v>6</v>
       </c>
       <c r="L27" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="O27">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="M27">
+        <v>6</v>
+      </c>
+      <c r="O27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -10785,14 +11861,14 @@
       <c r="G28" t="s">
         <v>830</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <v>10</v>
       </c>
       <c r="I28" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K28">
         <v>5.7</v>
@@ -10800,8 +11876,11 @@
       <c r="L28" s="3">
         <v>3</v>
       </c>
-      <c r="O28">
-        <v>2.5</v>
+      <c r="M28">
+        <v>5.6</v>
+      </c>
+      <c r="O28" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10814,23 +11893,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -11069,46 +12131,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}"/>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinhthienly-my.sharepoint.com/personal/ict_khangv_lsts_edu_vn/Documents/01. PD/2025 - 2026/SỔ ĐIỂM HK2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANKHANG MEDIA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1481" documentId="13_ncr:1_{9C38F584-4819-487B-ADF8-F9572E133DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B4EA72-7195-48F4-AB79-BA43E9A97B95}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="6" activeTab="6" xr2:uid="{1EF14012-7694-4211-A43A-BA5E23E1AA9F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="9H07" sheetId="4" r:id="rId6"/>
     <sheet name="MUL10L3" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="162913" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2540,7 +2539,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2622,7 +2621,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -2763,160 +2762,160 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D8CAEABF-E66E-4EA0-B5F0-45BB7B7C8283}" name="Table134567" displayName="Table134567" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table134567" displayName="Table134567" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{87738BB3-F223-40DE-A3F1-6495839DEA66}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{11264E93-FA91-4F59-BD4B-C1C037FAA83D}" name="Tên lớp"/>
-    <tableColumn id="15" xr3:uid="{663E2F38-52E7-4DEC-8BF6-EC09A6ED999C}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{6244EDF7-7044-4E20-8F14-297F251103AC}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{8A570531-1F2E-496F-81CB-604F321E21CA}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{A02E2B85-AB61-40A1-9F4B-D979CAC0B617}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{2FFEAA5A-8746-4BD9-98AB-DBD4E8A4A25E}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{73647768-883D-4881-AC08-329C42F7CAF5}" name="TX1" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{F07CAD0F-FE6E-43E3-A5F3-7B413864403F}" name="TX2"/>
-    <tableColumn id="14" xr3:uid="{5AFF0A24-6235-4A06-8319-FC8208F8B70E}" name="TX3"/>
-    <tableColumn id="9" xr3:uid="{EE5EFA3E-6E5D-4CC4-AF4D-352CC7E2323A}" name="GKTN"/>
-    <tableColumn id="10" xr3:uid="{C094DE6A-6F36-4C2C-9BA8-FC6279DB205D}" name="GKTH"/>
-    <tableColumn id="11" xr3:uid="{6A74C0A7-2690-4619-8688-B10403D4B1A9}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{32C992A3-1937-4FAD-93D0-760AAC028DCA}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{D56AE305-8846-4965-9E4A-4C7CCC2ED78A}" name="Điểm cộng/trừ" dataDxfId="16"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="15" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="17"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="14" name="TX3"/>
+    <tableColumn id="9" name="GKTN"/>
+    <tableColumn id="10" name="GKTH"/>
+    <tableColumn id="11" name="CKTN"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5053C834-5E03-4C8A-8CA8-EB4B0CD7BAD8}" name="Table1345678" displayName="Table1345678" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1345678" displayName="Table1345678" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{380F80C6-CB38-4814-82CB-2252208DAA8B}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{F366DE0B-A4F5-4E70-BA9A-24B56B9D0D35}" name="Tên lớp"/>
-    <tableColumn id="15" xr3:uid="{F546ED14-29B4-41AC-BEC9-4BD5F9F39F22}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{81AF2768-B1A6-422C-8284-4DAA0BC48AAE}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{C5D3CFB0-FAF6-4D1E-A475-E7FA9D71AB5D}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{91C2DDE5-F074-4EAC-88F7-79EA00D266CC}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{226EBCCE-5C9A-4CBC-8056-733B010D8131}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{F73C8D4B-448F-461E-BE91-2ED211DEF252}" name="TX1" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{A1579224-363E-453E-9563-D540AA688406}" name="TX2"/>
-    <tableColumn id="14" xr3:uid="{6F87760A-1A5B-4020-811F-F2DFA92559E8}" name="TX3"/>
-    <tableColumn id="9" xr3:uid="{7460001B-4B51-4627-B19E-56E68A476EC5}" name="GKTN"/>
-    <tableColumn id="10" xr3:uid="{CE0203A2-6C00-4623-82AD-1BFF8ACD360C}" name="GKTH"/>
-    <tableColumn id="11" xr3:uid="{7428E339-3333-4B74-963C-C009887E1C5C}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{9A8E2EAA-0067-4189-AB09-0CB66607B45E}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{390C5CFE-3A6A-4638-9BBF-A4E808C34019}" name="Điểm cộng/trừ" dataDxfId="14"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="15" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="15"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="14" name="TX3"/>
+    <tableColumn id="9" name="GKTN"/>
+    <tableColumn id="10" name="GKTH"/>
+    <tableColumn id="11" name="CKTN"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{893C0C13-C0BF-41D2-B116-40DD21EF758A}" name="Table13" displayName="Table13" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{6E2116B6-8A6D-4061-8A21-74A7A7DC0A3F}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{6087A31C-093B-4F4E-B714-B12FB26CB1EB}" name="Tên lớp"/>
-    <tableColumn id="14" xr3:uid="{CA55B5F2-E1FD-481E-AE5C-E2565281A450}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{7A4A34B7-E2DB-4FE4-91C8-4E2B52ABDE65}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{B5A5A35E-BF57-4756-93A5-E4D8D57AE3DD}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{BD257335-0296-4F83-9582-74FB6D54FFEE}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{149A88A9-EBA0-4DEF-ABEF-87BA920B076E}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{412235EE-C3D7-41E5-8934-3084314078B0}" name="TX1" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{B4ED72BD-9228-4E83-8EE4-091B112C2B0C}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{727F5E71-DAB5-4D3F-9759-8BC266A4ED52}" name="GKTN" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{333B9655-FE71-4ED7-82A0-F0641FE0FC1D}" name="CKTN" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{12F75C8C-BA02-41AF-B140-AE5EF3BD99A4}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{C94634BB-4F5D-4330-99F0-51186DAB60DE}" name="Điểm cộng/trừ" dataDxfId="10"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="14" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="13"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="9" name="GKTN" dataDxfId="12"/>
+    <tableColumn id="11" name="CKTN" dataDxfId="11"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}" name="Table1" displayName="Table1" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{AEF25B17-4DF2-4D0E-9AE0-20FBC325DD6E}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{6A81BFF8-ED78-497C-9FBA-9E62170F7033}" name="Tên lớp"/>
-    <tableColumn id="14" xr3:uid="{5814C0D9-5FBA-4E09-888A-9B5D322FC7C3}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{7A5ECB8C-691A-46D4-84BB-9C820767C3DD}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{22F7231F-C7A0-447F-A36F-DF32328BE83E}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{CB4BA5A7-E295-4634-B8D5-79CED684DA84}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{9E09BF74-FA06-4E53-B295-9B096B431E71}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{77131993-30B1-49AE-BCE9-38F5EDF29692}" name="TX1" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{EA41B88E-A7D1-49D3-AAA3-D3FD83B5F818}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{CA4BAF3B-3E9D-4F31-A984-1BBC57B1761E}" name="GKTN" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{8E43F492-DA8D-4B36-992F-8FF2ED3BA73B}" name="CKTN" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{F54748B3-D956-40BA-B6D0-AC2C18A939C2}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{E68010E6-7545-4825-8A30-E7739A1C4C4A}" name="Điểm cộng/trừ" dataDxfId="6"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="14" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="9"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="9" name="GKTN" dataDxfId="8"/>
+    <tableColumn id="11" name="CKTN" dataDxfId="7"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4A3C666D-3C00-4905-B391-C83C5806B13E}" name="Table134" displayName="Table134" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table134" displayName="Table134" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{77EDE383-0924-4964-974B-4CBD42294757}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{1ED1936A-8E22-4C4E-ABF8-B2558213F9F1}" name="Tên lớp"/>
-    <tableColumn id="14" xr3:uid="{2EE42409-3D0E-408F-92A5-24635CA413AD}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{C2E0EF6F-E6CD-4622-87B5-D18C4C15CA78}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{7BD37775-2BE4-42D5-836D-E721DAE8F028}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{31926365-1D24-4CFE-BA60-8DB775984C5D}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{977019B1-D09A-42A2-BB7E-87A52F4F5FC5}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{83E63E51-16A0-4F7B-AD5B-954C67C5604E}" name="TX1" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{E12E76F6-5CAD-4D93-B39B-BEF9F29047D1}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{B9EA5CAD-C0AD-4602-B18F-77FA277F8DB7}" name="GKTN"/>
-    <tableColumn id="11" xr3:uid="{8B0F90C0-A200-4C39-B887-17FF3D23FB8C}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{C3D25CAA-BDF5-4FE0-82DF-D8A37B9D0D87}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{1F6CE7C5-9460-4818-BE04-86FDB1B4A51B}" name="Điểm cộng/trừ" dataDxfId="4"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="14" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="5"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="9" name="GKTN"/>
+    <tableColumn id="11" name="CKTN"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F82842B2-CFEE-4177-8C90-BCA51289E516}" name="Table1345" displayName="Table1345" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1345" displayName="Table1345" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{906712F0-7C83-4780-B789-61AD25B59BAC}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{AD518F16-22C3-491A-9625-22487E46C714}" name="Tên lớp"/>
-    <tableColumn id="14" xr3:uid="{7B884FA7-03C8-4866-BA9C-7F795FF87E7A}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{41E885D5-A632-43B9-A6ED-1E90C6AC2F84}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{C834A720-51FC-4C56-8876-916F6364A386}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{6FB130F4-A05E-4FDC-B2DA-22E94D5D3B81}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{60B78D02-D560-431E-8870-83F119B73156}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{C3793044-9978-49A7-9D3A-45059A554ABC}" name="TX1" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{E363DFF6-1A16-48AE-B1F0-2A19DD4C324E}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{F678A0CD-2F7B-4590-82F6-896BD825BC54}" name="GKTN"/>
-    <tableColumn id="11" xr3:uid="{FBC07A04-980A-40A1-B291-5F4C36722B6A}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{1E86EEE0-3C4E-441A-AF40-2F0A70054A22}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{7F492110-3F4E-4B88-9286-10B4D422DBF3}" name="Điểm cộng/trừ" dataDxfId="2"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="14" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="3"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="9" name="GKTN"/>
+    <tableColumn id="11" name="CKTN"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9853F517-198C-434C-89D9-1F4027A2BF6C}" name="Table13456" displayName="Table13456" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31" xr:uid="{87B4C68E-52B0-44CE-94D4-AC3C5E059EEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table13456" displayName="Table13456" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{FC843D9B-BB86-419E-9700-1C92F706BC83}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{9C544FF2-C870-49A1-B6CA-2EBF6EDE934C}" name="Tên lớp"/>
-    <tableColumn id="15" xr3:uid="{3C8C74FA-23DD-49D1-8C57-559308A35F3C}" name="Mã định danh"/>
-    <tableColumn id="3" xr3:uid="{DF87C69E-E838-4F85-B03C-5E4BE96FD101}" name="MSHS"/>
-    <tableColumn id="4" xr3:uid="{06BB6758-BB6D-4290-B77F-4E8EEA74F35D}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{33C0ABE3-FAC4-4D07-BF8A-BBC8667CC653}" name="Họ và tên"/>
-    <tableColumn id="6" xr3:uid="{860FF401-193A-4CEF-A318-711475F896D5}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{9DB0F73A-AF64-4B12-A1B2-292C31ABAD85}" name="TX1" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{B2D8B9D4-A9A6-4707-9FE9-196AB7FAD70B}" name="TX2"/>
-    <tableColumn id="14" xr3:uid="{CC905B07-3171-4DB1-8DE4-D4812DC9F8D9}" name="TX3"/>
-    <tableColumn id="9" xr3:uid="{6B9636A9-2F54-4EDD-AA38-33B1287A1DFA}" name="GKTN"/>
-    <tableColumn id="10" xr3:uid="{25C5BFA4-7959-4B67-AAFA-4499322AA35A}" name="GKTH"/>
-    <tableColumn id="11" xr3:uid="{4794BE50-1508-4F5D-BDA5-0D795E511169}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{20B8C87E-B4C2-46B2-A1EE-45C5B13A49F5}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{0E49A624-F415-4FEC-A84F-1976E399D991}" name="Điểm cộng/trừ" dataDxfId="0"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Tên lớp"/>
+    <tableColumn id="15" name="Mã định danh"/>
+    <tableColumn id="3" name="MSHS"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Họ và tên"/>
+    <tableColumn id="6" name="Ngày sinh"/>
+    <tableColumn id="7" name="TX1" dataDxfId="1"/>
+    <tableColumn id="8" name="TX2"/>
+    <tableColumn id="14" name="TX3"/>
+    <tableColumn id="9" name="GKTN"/>
+    <tableColumn id="10" name="GKTH"/>
+    <tableColumn id="11" name="CKTN"/>
+    <tableColumn id="12" name="CKTH"/>
+    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3238,16 +3237,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E62F6F0-A60C-46AE-A379-677AAC706EA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4601,16 +4600,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B7CE8A-3709-4982-8530-4B128DCF5EDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5949,16 +5948,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31AEED-D516-49B6-A6FF-F6CDC6895127}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="24.25" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -6036,6 +6035,9 @@
       <c r="K2" s="6">
         <v>5.7</v>
       </c>
+      <c r="L2">
+        <v>2.5</v>
+      </c>
       <c r="M2" s="9">
         <v>0</v>
       </c>
@@ -6074,6 +6076,9 @@
       <c r="K3" s="6">
         <v>6</v>
       </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
       <c r="M3" s="9">
         <v>2.5</v>
       </c>
@@ -6112,6 +6117,9 @@
       <c r="K4" s="6">
         <v>6</v>
       </c>
+      <c r="L4">
+        <v>3.5</v>
+      </c>
       <c r="M4" s="9">
         <v>0</v>
       </c>
@@ -6150,6 +6158,9 @@
       <c r="K5" s="6">
         <v>6</v>
       </c>
+      <c r="L5">
+        <v>3.5</v>
+      </c>
       <c r="M5" s="9">
         <v>0.25</v>
       </c>
@@ -6188,6 +6199,9 @@
       <c r="K6" s="6">
         <v>5.7</v>
       </c>
+      <c r="L6">
+        <v>2.5</v>
+      </c>
       <c r="M6" s="9">
         <v>0</v>
       </c>
@@ -6217,11 +6231,18 @@
       <c r="H7" s="5">
         <v>8</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="4">
+        <v>5</v>
+      </c>
       <c r="J7" s="8">
         <v>8.5</v>
       </c>
-      <c r="K7" s="7"/>
+      <c r="K7" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3</v>
+      </c>
       <c r="M7" s="9">
         <v>0</v>
       </c>
@@ -6260,6 +6281,9 @@
       <c r="K8" s="6">
         <v>5.2</v>
       </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
       <c r="M8" s="9">
         <v>0</v>
       </c>
@@ -6298,6 +6322,9 @@
       <c r="K9" s="6">
         <v>6</v>
       </c>
+      <c r="L9">
+        <v>3.5</v>
+      </c>
       <c r="M9" s="9">
         <v>2</v>
       </c>
@@ -6336,6 +6363,9 @@
       <c r="K10" s="6">
         <v>6</v>
       </c>
+      <c r="L10">
+        <v>3.8</v>
+      </c>
       <c r="M10" s="9">
         <v>0</v>
       </c>
@@ -6374,6 +6404,9 @@
       <c r="K11" s="6">
         <v>6</v>
       </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
       <c r="M11" s="9">
         <v>2.75</v>
       </c>
@@ -6412,6 +6445,9 @@
       <c r="K12" s="6">
         <v>6</v>
       </c>
+      <c r="L12">
+        <v>3.3</v>
+      </c>
       <c r="M12" s="9">
         <v>2.5</v>
       </c>
@@ -6450,6 +6486,9 @@
       <c r="K13" s="6">
         <v>5.5</v>
       </c>
+      <c r="L13">
+        <v>3.9</v>
+      </c>
       <c r="M13" s="9">
         <v>0</v>
       </c>
@@ -6488,6 +6527,9 @@
       <c r="K14" s="6">
         <v>5.5</v>
       </c>
+      <c r="L14">
+        <v>3.8</v>
+      </c>
       <c r="M14" s="9">
         <v>0</v>
       </c>
@@ -6526,6 +6568,9 @@
       <c r="K15" s="6">
         <v>4.75</v>
       </c>
+      <c r="L15">
+        <v>1.5</v>
+      </c>
       <c r="M15" s="9">
         <v>0</v>
       </c>
@@ -6564,6 +6609,9 @@
       <c r="K16" s="6">
         <v>4.5</v>
       </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
       <c r="M16" s="9">
         <v>0</v>
       </c>
@@ -6602,6 +6650,9 @@
       <c r="K17" s="6">
         <v>6</v>
       </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
       <c r="M17" s="9">
         <v>1</v>
       </c>
@@ -6640,6 +6691,9 @@
       <c r="K18" s="6">
         <v>5.5</v>
       </c>
+      <c r="L18">
+        <v>3.5</v>
+      </c>
       <c r="M18" s="9">
         <v>0</v>
       </c>
@@ -6678,6 +6732,9 @@
       <c r="K19" s="6">
         <v>6</v>
       </c>
+      <c r="L19">
+        <v>3.9</v>
+      </c>
       <c r="M19" s="9">
         <v>0</v>
       </c>
@@ -6716,6 +6773,9 @@
       <c r="K20" s="6">
         <v>5.5</v>
       </c>
+      <c r="L20">
+        <v>3.8</v>
+      </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
@@ -6754,6 +6814,9 @@
       <c r="K21" s="6">
         <v>6</v>
       </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
       <c r="M21" s="9">
         <v>0</v>
       </c>
@@ -6792,6 +6855,9 @@
       <c r="K22" s="6">
         <v>6</v>
       </c>
+      <c r="L22">
+        <v>3.8</v>
+      </c>
       <c r="M22" s="9">
         <v>1.25</v>
       </c>
@@ -6830,6 +6896,9 @@
       <c r="K23" s="6">
         <v>6</v>
       </c>
+      <c r="L23">
+        <v>3.9</v>
+      </c>
       <c r="M23" s="9">
         <v>0.25</v>
       </c>
@@ -6868,6 +6937,9 @@
       <c r="K24" s="6">
         <v>5.5</v>
       </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
       <c r="M24" s="9">
         <v>0</v>
       </c>
@@ -6906,6 +6978,9 @@
       <c r="K25" s="6">
         <v>6</v>
       </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
       <c r="M25" s="9">
         <v>1.75</v>
       </c>
@@ -6944,6 +7019,9 @@
       <c r="K26" s="6">
         <v>5.75</v>
       </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
       <c r="M26" s="9">
         <v>0</v>
       </c>
@@ -6982,6 +7060,9 @@
       <c r="K27" s="6">
         <v>6</v>
       </c>
+      <c r="L27">
+        <v>3.9</v>
+      </c>
       <c r="M27" s="9">
         <v>1.5</v>
       </c>
@@ -7020,6 +7101,9 @@
       <c r="K28" s="6">
         <v>5</v>
       </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
       <c r="M28" s="9">
         <v>0</v>
       </c>
@@ -7058,6 +7142,9 @@
       <c r="K29" s="6">
         <v>5.5</v>
       </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
       <c r="M29" s="9">
         <v>0</v>
       </c>
@@ -7096,6 +7183,9 @@
       <c r="K30" s="6">
         <v>6</v>
       </c>
+      <c r="L30">
+        <v>3.9</v>
+      </c>
       <c r="M30" s="9">
         <v>1.25</v>
       </c>
@@ -7133,6 +7223,9 @@
       </c>
       <c r="K31" s="6">
         <v>6</v>
+      </c>
+      <c r="L31">
+        <v>1.8</v>
       </c>
       <c r="M31" s="9">
         <v>0</v>
@@ -7147,16 +7240,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4EC707-71B4-4E8F-AC0E-96DAFCEEB03D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="35.375" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7234,6 +7327,9 @@
       <c r="K2" s="6">
         <v>6</v>
       </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
       <c r="M2" s="9">
         <v>2.25</v>
       </c>
@@ -7272,6 +7368,9 @@
       <c r="K3" s="6">
         <v>4.75</v>
       </c>
+      <c r="L3">
+        <v>1.3</v>
+      </c>
       <c r="M3" s="9">
         <v>0</v>
       </c>
@@ -7310,6 +7409,9 @@
       <c r="K4" s="6">
         <v>5.5</v>
       </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
       <c r="M4" s="9">
         <v>0</v>
       </c>
@@ -7348,6 +7450,9 @@
       <c r="K5" s="6">
         <v>4.75</v>
       </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
       <c r="M5" s="9">
         <v>0</v>
       </c>
@@ -7386,6 +7491,9 @@
       <c r="K6" s="6">
         <v>5.5</v>
       </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
       <c r="M6" s="9">
         <v>0</v>
       </c>
@@ -7424,6 +7532,9 @@
       <c r="K7" s="6">
         <v>5.75</v>
       </c>
+      <c r="L7">
+        <v>2.5</v>
+      </c>
       <c r="M7" s="9">
         <v>0</v>
       </c>
@@ -7462,6 +7573,9 @@
       <c r="K8" s="6">
         <v>6</v>
       </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
       <c r="M8" s="9">
         <v>1.75</v>
       </c>
@@ -7500,6 +7614,9 @@
       <c r="K9" s="6">
         <v>5.5</v>
       </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
       <c r="M9" s="9">
         <v>0</v>
       </c>
@@ -7538,6 +7655,9 @@
       <c r="K10" s="6">
         <v>5.9</v>
       </c>
+      <c r="L10">
+        <v>3.9</v>
+      </c>
       <c r="M10" s="9">
         <v>0</v>
       </c>
@@ -7576,6 +7696,9 @@
       <c r="K11" s="6">
         <v>6</v>
       </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
       <c r="M11" s="9">
         <v>2.5</v>
       </c>
@@ -7614,6 +7737,9 @@
       <c r="K12" s="6">
         <v>6</v>
       </c>
+      <c r="L12">
+        <v>2.5</v>
+      </c>
       <c r="M12" s="9">
         <v>3</v>
       </c>
@@ -7652,6 +7778,9 @@
       <c r="K13" s="6">
         <v>6</v>
       </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
       <c r="M13" s="9">
         <v>1</v>
       </c>
@@ -7690,6 +7819,9 @@
       <c r="K14" s="6">
         <v>5.5</v>
       </c>
+      <c r="L14">
+        <v>3.3</v>
+      </c>
       <c r="M14" s="9">
         <v>0</v>
       </c>
@@ -7720,13 +7852,16 @@
         <v>9</v>
       </c>
       <c r="I15" s="4">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="6">
         <v>8</v>
       </c>
       <c r="K15" s="6">
         <v>4.5</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
       </c>
       <c r="M15" s="9">
         <v>0</v>
@@ -7766,6 +7901,9 @@
       <c r="K16" s="6">
         <v>5.5</v>
       </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
       <c r="M16" s="9">
         <v>0</v>
       </c>
@@ -7804,6 +7942,9 @@
       <c r="K17" s="6">
         <v>5.8</v>
       </c>
+      <c r="L17">
+        <v>2.5</v>
+      </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
@@ -7842,6 +7983,9 @@
       <c r="K18" s="6">
         <v>5.25</v>
       </c>
+      <c r="L18">
+        <v>3.8</v>
+      </c>
       <c r="M18" s="9">
         <v>0</v>
       </c>
@@ -7880,6 +8024,9 @@
       <c r="K19" s="6">
         <v>6</v>
       </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
       <c r="M19" s="9">
         <v>2.5</v>
       </c>
@@ -7918,6 +8065,9 @@
       <c r="K20" s="6">
         <v>5.25</v>
       </c>
+      <c r="L20">
+        <v>3.8</v>
+      </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
@@ -7948,13 +8098,16 @@
         <v>8</v>
       </c>
       <c r="I21" s="4">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J21" s="6">
         <v>6.75</v>
       </c>
       <c r="K21" s="6">
         <v>3.75</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
       </c>
       <c r="M21" s="9">
         <v>0</v>
@@ -7994,6 +8147,9 @@
       <c r="K22" s="6">
         <v>6</v>
       </c>
+      <c r="L22">
+        <v>3.9</v>
+      </c>
       <c r="M22" s="9">
         <v>0</v>
       </c>
@@ -8032,6 +8188,9 @@
       <c r="K23" s="6">
         <v>6</v>
       </c>
+      <c r="L23">
+        <v>3.5</v>
+      </c>
       <c r="M23" s="9">
         <v>0</v>
       </c>
@@ -8070,6 +8229,9 @@
       <c r="K24" s="6">
         <v>6</v>
       </c>
+      <c r="L24">
+        <v>4</v>
+      </c>
       <c r="M24" s="9">
         <v>3.75</v>
       </c>
@@ -8108,6 +8270,9 @@
       <c r="K25" s="6">
         <v>6</v>
       </c>
+      <c r="L25">
+        <v>3.8</v>
+      </c>
       <c r="M25" s="9">
         <v>1.5</v>
       </c>
@@ -8146,6 +8311,9 @@
       <c r="K26" s="6">
         <v>6</v>
       </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
       <c r="M26" s="9">
         <v>0</v>
       </c>
@@ -8176,13 +8344,16 @@
         <v>10</v>
       </c>
       <c r="I27" s="4">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="6">
         <v>9.5</v>
       </c>
       <c r="K27" s="6">
         <v>5</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
       </c>
       <c r="M27" s="9">
         <v>0</v>
@@ -8222,6 +8393,9 @@
       <c r="K28" s="6">
         <v>5.7</v>
       </c>
+      <c r="L28">
+        <v>0.8</v>
+      </c>
       <c r="M28" s="9">
         <v>0</v>
       </c>
@@ -8260,6 +8434,9 @@
       <c r="K29" s="6">
         <v>6</v>
       </c>
+      <c r="L29">
+        <v>3.5</v>
+      </c>
       <c r="M29" s="9">
         <v>0</v>
       </c>
@@ -8298,6 +8475,9 @@
       <c r="K30" s="6">
         <v>6</v>
       </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
       <c r="M30" s="9">
         <v>0.75</v>
       </c>
@@ -8335,6 +8515,9 @@
       </c>
       <c r="K31" s="6">
         <v>5.25</v>
+      </c>
+      <c r="L31">
+        <v>3.5</v>
       </c>
       <c r="M31" s="9">
         <v>0</v>
@@ -8349,17 +8532,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195B8901-376D-4489-8560-7242E57D3B44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
     <col min="8" max="8" width="8" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="8.375" customWidth="1"/>
+    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8437,7 +8620,9 @@
       <c r="K2" s="6">
         <v>5.6</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="2">
+        <v>3.9</v>
+      </c>
       <c r="M2" s="9">
         <v>0</v>
       </c>
@@ -8476,6 +8661,9 @@
       <c r="K3" s="6">
         <v>6</v>
       </c>
+      <c r="L3">
+        <v>3.7</v>
+      </c>
       <c r="M3" s="9">
         <v>1.5</v>
       </c>
@@ -8514,6 +8702,9 @@
       <c r="K4" s="6">
         <v>6</v>
       </c>
+      <c r="L4">
+        <v>3.3</v>
+      </c>
       <c r="M4" s="9">
         <v>2.75</v>
       </c>
@@ -8552,6 +8743,9 @@
       <c r="K5" s="6">
         <v>6</v>
       </c>
+      <c r="L5">
+        <v>2.7</v>
+      </c>
       <c r="M5" s="9">
         <v>0</v>
       </c>
@@ -8590,6 +8784,9 @@
       <c r="K6" s="6">
         <v>5</v>
       </c>
+      <c r="L6">
+        <v>3.9</v>
+      </c>
       <c r="M6" s="9">
         <v>0.25</v>
       </c>
@@ -8628,6 +8825,9 @@
       <c r="K7" s="6">
         <v>4.5</v>
       </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
       <c r="M7" s="9">
         <v>0</v>
       </c>
@@ -8666,6 +8866,9 @@
       <c r="K8" s="6">
         <v>5</v>
       </c>
+      <c r="L8">
+        <v>1.8</v>
+      </c>
       <c r="M8" s="9">
         <v>0</v>
       </c>
@@ -8704,6 +8907,9 @@
       <c r="K9" s="6">
         <v>5.75</v>
       </c>
+      <c r="L9">
+        <v>1.3</v>
+      </c>
       <c r="M9" s="9">
         <v>0</v>
       </c>
@@ -8742,6 +8948,9 @@
       <c r="K10" s="6">
         <v>4.5</v>
       </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
       <c r="M10" s="9">
         <v>0</v>
       </c>
@@ -8780,6 +8989,9 @@
       <c r="K11" s="6">
         <v>6</v>
       </c>
+      <c r="L11">
+        <v>3.9</v>
+      </c>
       <c r="M11" s="9">
         <v>2</v>
       </c>
@@ -8818,6 +9030,9 @@
       <c r="K12" s="6">
         <v>5.75</v>
       </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
       <c r="M12" s="9">
         <v>0</v>
       </c>
@@ -8856,6 +9071,9 @@
       <c r="K13" s="6">
         <v>6</v>
       </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
       <c r="M13" s="9">
         <v>0</v>
       </c>
@@ -8894,6 +9112,9 @@
       <c r="K14" s="6">
         <v>6</v>
       </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
       <c r="M14" s="9">
         <v>0</v>
       </c>
@@ -8932,6 +9153,9 @@
       <c r="K15" s="6">
         <v>6</v>
       </c>
+      <c r="L15">
+        <v>0.3</v>
+      </c>
       <c r="M15" s="9">
         <v>0</v>
       </c>
@@ -8970,6 +9194,9 @@
       <c r="K16" s="6">
         <v>5.5</v>
       </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
       <c r="M16" s="9">
         <v>0</v>
       </c>
@@ -9008,6 +9235,9 @@
       <c r="K17" s="6">
         <v>5</v>
       </c>
+      <c r="L17">
+        <v>2.5</v>
+      </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
@@ -9046,6 +9276,9 @@
       <c r="K18" s="6">
         <v>6</v>
       </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
       <c r="M18" s="9">
         <v>0</v>
       </c>
@@ -9084,6 +9317,9 @@
       <c r="K19" s="6">
         <v>5</v>
       </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
       <c r="M19" s="9">
         <v>0</v>
       </c>
@@ -9122,6 +9358,9 @@
       <c r="K20" s="6">
         <v>6</v>
       </c>
+      <c r="L20">
+        <v>3.8</v>
+      </c>
       <c r="M20" s="9">
         <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>2.75</v>
@@ -9161,6 +9400,9 @@
       <c r="K21" s="6">
         <v>5.5</v>
       </c>
+      <c r="L21">
+        <v>1.5</v>
+      </c>
       <c r="M21" s="9">
         <v>0</v>
       </c>
@@ -9199,6 +9441,9 @@
       <c r="K22" s="6">
         <v>5.5</v>
       </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
       <c r="M22" s="9">
         <v>0</v>
       </c>
@@ -9237,6 +9482,9 @@
       <c r="K23" s="6">
         <v>4.5</v>
       </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
       <c r="M23" s="9">
         <v>0</v>
       </c>
@@ -9275,6 +9523,9 @@
       <c r="K24" s="6">
         <v>6</v>
       </c>
+      <c r="L24">
+        <v>3.9</v>
+      </c>
       <c r="M24" s="9">
         <v>2.75</v>
       </c>
@@ -9313,6 +9564,9 @@
       <c r="K25" s="6">
         <v>6</v>
       </c>
+      <c r="L25">
+        <v>1.8</v>
+      </c>
       <c r="M25" s="9">
         <v>1.25</v>
       </c>
@@ -9351,6 +9605,9 @@
       <c r="K26" s="6">
         <v>5.25</v>
       </c>
+      <c r="L26">
+        <v>3.9</v>
+      </c>
       <c r="M26" s="9">
         <v>0</v>
       </c>
@@ -9389,6 +9646,9 @@
       <c r="K27" s="6">
         <v>5.75</v>
       </c>
+      <c r="L27">
+        <v>4</v>
+      </c>
       <c r="M27" s="9">
         <v>0</v>
       </c>
@@ -9427,6 +9687,9 @@
       <c r="K28" s="6">
         <v>4.75</v>
       </c>
+      <c r="L28">
+        <v>2.5</v>
+      </c>
       <c r="M28" s="9">
         <v>0</v>
       </c>
@@ -9465,6 +9728,9 @@
       <c r="K29" s="6">
         <v>5.5</v>
       </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
       <c r="M29" s="9">
         <v>0</v>
       </c>
@@ -9502,6 +9768,9 @@
       </c>
       <c r="K30" s="6">
         <v>5.9</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
       </c>
       <c r="M30" s="9">
         <v>0</v>
@@ -9516,16 +9785,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC312E2-BFEE-413B-B1C1-039BACF14471}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="13" max="13" width="16.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9603,7 +9872,9 @@
       <c r="K2" s="6">
         <v>5.25</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2">
+        <v>3</v>
+      </c>
       <c r="M2" s="9">
         <v>0</v>
       </c>
@@ -9642,6 +9913,9 @@
       <c r="K3" s="6">
         <v>6</v>
       </c>
+      <c r="L3">
+        <v>2.8</v>
+      </c>
       <c r="M3" s="9">
         <v>0</v>
       </c>
@@ -9680,6 +9954,9 @@
       <c r="K4" s="6">
         <v>6</v>
       </c>
+      <c r="L4">
+        <v>2.8</v>
+      </c>
       <c r="M4" s="9">
         <v>0</v>
       </c>
@@ -9718,6 +9995,9 @@
       <c r="K5" s="6">
         <v>6</v>
       </c>
+      <c r="L5">
+        <v>2.5</v>
+      </c>
       <c r="M5" s="9">
         <v>2.75</v>
       </c>
@@ -9756,6 +10036,9 @@
       <c r="K6" s="6">
         <v>6</v>
       </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
       <c r="M6" s="9">
         <v>0.5</v>
       </c>
@@ -9794,6 +10077,9 @@
       <c r="K7" s="6">
         <v>6</v>
       </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
       <c r="M7" s="9">
         <v>2.5</v>
       </c>
@@ -9832,6 +10118,9 @@
       <c r="K8" s="6">
         <v>5.25</v>
       </c>
+      <c r="L8">
+        <v>3.9</v>
+      </c>
       <c r="M8" s="9">
         <v>0</v>
       </c>
@@ -9870,6 +10159,9 @@
       <c r="K9" s="6">
         <v>6</v>
       </c>
+      <c r="L9">
+        <v>3.3</v>
+      </c>
       <c r="M9" s="9">
         <v>0.5</v>
       </c>
@@ -9908,6 +10200,9 @@
       <c r="K10" s="6">
         <v>5</v>
       </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
       <c r="M10" s="9">
         <v>0</v>
       </c>
@@ -9946,6 +10241,9 @@
       <c r="K11" s="6">
         <v>6</v>
       </c>
+      <c r="L11">
+        <v>3.8</v>
+      </c>
       <c r="M11" s="9">
         <v>1.75</v>
       </c>
@@ -9984,6 +10282,9 @@
       <c r="K12" s="6">
         <v>5</v>
       </c>
+      <c r="L12">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="M12" s="9">
         <v>0</v>
       </c>
@@ -10022,6 +10323,9 @@
       <c r="K13" s="6">
         <v>6</v>
       </c>
+      <c r="L13">
+        <v>2.8</v>
+      </c>
       <c r="M13" s="9">
         <v>0</v>
       </c>
@@ -10060,6 +10364,9 @@
       <c r="K14" s="6">
         <v>6</v>
       </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
       <c r="M14" s="9">
         <v>0.5</v>
       </c>
@@ -10098,6 +10405,9 @@
       <c r="K15" s="6">
         <v>6</v>
       </c>
+      <c r="L15">
+        <v>4</v>
+      </c>
       <c r="M15" s="9">
         <v>0</v>
       </c>
@@ -10136,6 +10446,9 @@
       <c r="K16" s="6">
         <v>5.75</v>
       </c>
+      <c r="L16">
+        <v>3.8</v>
+      </c>
       <c r="M16" s="9">
         <v>0</v>
       </c>
@@ -10174,6 +10487,9 @@
       <c r="K17" s="6">
         <v>5.5</v>
       </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
@@ -10212,6 +10528,9 @@
       <c r="K18" s="6">
         <v>4.5</v>
       </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
       <c r="M18" s="9">
         <v>0</v>
       </c>
@@ -10250,6 +10569,9 @@
       <c r="K19" s="6">
         <v>6</v>
       </c>
+      <c r="L19">
+        <v>3.9</v>
+      </c>
       <c r="M19" s="9">
         <v>3.5</v>
       </c>
@@ -10288,6 +10610,9 @@
       <c r="K20" s="6">
         <v>5</v>
       </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
@@ -10326,6 +10651,9 @@
       <c r="K21" s="6">
         <v>4</v>
       </c>
+      <c r="L21">
+        <v>2.8</v>
+      </c>
       <c r="M21" s="9">
         <v>0</v>
       </c>
@@ -10364,6 +10692,9 @@
       <c r="K22" s="6">
         <v>6</v>
       </c>
+      <c r="L22">
+        <v>3.9</v>
+      </c>
       <c r="M22" s="9">
         <v>3.25</v>
       </c>
@@ -10402,6 +10733,9 @@
       <c r="K23" s="6">
         <v>5.75</v>
       </c>
+      <c r="L23">
+        <v>3.8</v>
+      </c>
       <c r="M23" s="9">
         <v>0</v>
       </c>
@@ -10440,6 +10774,9 @@
       <c r="K24" s="6">
         <v>6</v>
       </c>
+      <c r="L24">
+        <v>3.9</v>
+      </c>
       <c r="M24" s="9">
         <v>0.25</v>
       </c>
@@ -10478,6 +10815,9 @@
       <c r="K25" s="6">
         <v>6</v>
       </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
       <c r="M25" s="9">
         <v>2</v>
       </c>
@@ -10515,6 +10855,9 @@
       </c>
       <c r="K26" s="6">
         <v>6</v>
+      </c>
+      <c r="L26">
+        <v>3.8</v>
       </c>
       <c r="M26" s="9">
         <v>3</v>
@@ -10579,11 +10922,18 @@
       <c r="H28" s="5">
         <v>10</v>
       </c>
-      <c r="I28" s="4"/>
+      <c r="I28" s="4">
+        <v>5</v>
+      </c>
       <c r="J28" s="8">
         <v>8.75</v>
       </c>
-      <c r="K28" s="7"/>
+      <c r="K28" s="7">
+        <v>6</v>
+      </c>
+      <c r="L28" s="3">
+        <v>4</v>
+      </c>
       <c r="M28" s="9">
         <v>0</v>
       </c>
@@ -10621,6 +10971,9 @@
       </c>
       <c r="K29" s="6">
         <v>6</v>
+      </c>
+      <c r="L29">
+        <v>3.9</v>
       </c>
       <c r="M29" s="9">
         <v>0.75</v>
@@ -10635,17 +10988,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD567BBF-FA45-4BB7-A2DB-AA426EC5E0BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="5"/>
-    <col min="11" max="12" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="5"/>
+    <col min="11" max="12" width="9.125" customWidth="1"/>
+    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -12132,6 +12485,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -12140,22 +12501,46 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANKHANG MEDIA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinhthienly-my.sharepoint.com/personal/ict_khangv_lsts_edu_vn/Documents/01. PD/2025 - 2026/SỔ ĐIỂM HK2/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="405" documentId="13_ncr:1_{0DF5AF2B-8EE8-4C11-A3C2-7BA40EC25983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFF161C-459C-4FEF-B9C1-2D237338F141}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -20,7 +21,7 @@
     <sheet name="9H07" sheetId="4" r:id="rId6"/>
     <sheet name="MUL10L3" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2539,11 +2540,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2558,7 +2559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2595,6 +2596,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2608,10 +2615,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -2619,11 +2625,38 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2634,9 +2667,28 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2647,6 +2699,12 @@
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2674,17 +2732,11 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2695,22 +2747,11 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
@@ -2762,160 +2803,160 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table134567" displayName="Table134567" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table134567" displayName="Table134567" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="15" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="17"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="14" name="TX3"/>
-    <tableColumn id="9" name="GKTN"/>
-    <tableColumn id="10" name="GKTH"/>
-    <tableColumn id="11" name="CKTN"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tên lớp"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="TX1" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="TX2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="TX3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="GKTN"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="GKTH"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CKTN"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CKTH"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Điểm cộng/trừ" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1345678" displayName="Table1345678" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1345678" displayName="Table1345678" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="15" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="15"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="14" name="TX3"/>
-    <tableColumn id="9" name="GKTN"/>
-    <tableColumn id="10" name="GKTH"/>
-    <tableColumn id="11" name="CKTN"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Tên lớp"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="TX1" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="TX2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="TX3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="GKTN"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="GKTH"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="CKTN"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="CKTH"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Điểm cộng/trừ" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table13" displayName="Table13" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="14" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="13"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="9" name="GKTN" dataDxfId="12"/>
-    <tableColumn id="11" name="CKTN" dataDxfId="11"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Tên lớp"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TX1" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="TX2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="GKTN" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="CKTN" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="CKTH" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Điểm cộng/trừ" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table1" displayName="Table1" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="14" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="9"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="9" name="GKTN" dataDxfId="8"/>
-    <tableColumn id="11" name="CKTN" dataDxfId="7"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Tên lớp"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="TX1" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="TX2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="GKTN" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CKTN" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="CKTH" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Điểm cộng/trừ" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table134" displayName="Table134" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table134" displayName="Table134" ref="A1:M31" totalsRowShown="0">
+  <autoFilter ref="A1:M31" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="14" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="5"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="9" name="GKTN"/>
-    <tableColumn id="11" name="CKTN"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Tên lớp"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="TX1" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="TX2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="GKTN"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="CKTN"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="CKTH" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Điểm cộng/trừ" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1345" displayName="Table1345" ref="A1:M31" totalsRowShown="0">
-  <autoFilter ref="A1:M31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table1345" displayName="Table1345" ref="A1:M29" totalsRowShown="0">
+  <autoFilter ref="A1:M29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="14" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="3"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="9" name="GKTN"/>
-    <tableColumn id="11" name="CKTN"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Tên lớp"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="TX1" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="TX2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="GKTN"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="CKTN"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="CKTH" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Điểm cộng/trừ" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table13456" displayName="Table13456" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table13456" displayName="Table13456" ref="A1:O31" totalsRowShown="0">
+  <autoFilter ref="A1:O31" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" name="STT"/>
-    <tableColumn id="2" name="Tên lớp"/>
-    <tableColumn id="15" name="Mã định danh"/>
-    <tableColumn id="3" name="MSHS"/>
-    <tableColumn id="4" name="Email"/>
-    <tableColumn id="5" name="Họ và tên"/>
-    <tableColumn id="6" name="Ngày sinh"/>
-    <tableColumn id="7" name="TX1" dataDxfId="1"/>
-    <tableColumn id="8" name="TX2"/>
-    <tableColumn id="14" name="TX3"/>
-    <tableColumn id="9" name="GKTN"/>
-    <tableColumn id="10" name="GKTH"/>
-    <tableColumn id="11" name="CKTN"/>
-    <tableColumn id="12" name="CKTH"/>
-    <tableColumn id="13" name="Điểm cộng/trừ" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="STT"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Tên lớp"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Mã định danh"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="MSHS"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Họ và tên"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Ngày sinh"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TX1" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="TX2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="TX3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="GKTN"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="GKTH"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="CKTN"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="CKTH"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Điểm cộng/trừ" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3237,19 +3278,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3271,7 +3312,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -3292,11 +3333,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3318,7 +3359,7 @@
       <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>9.3000000000000007</v>
       </c>
       <c r="I2">
@@ -3336,12 +3377,12 @@
       <c r="M2">
         <v>6</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3363,7 +3404,7 @@
       <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
@@ -3381,11 +3422,11 @@
       <c r="M3">
         <v>6</v>
       </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -3407,7 +3448,7 @@
       <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
@@ -3425,12 +3466,12 @@
       <c r="M4">
         <v>6</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -3452,7 +3493,7 @@
       <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>10</v>
       </c>
       <c r="I5">
@@ -3467,14 +3508,14 @@
       <c r="L5">
         <v>4</v>
       </c>
-      <c r="M5" s="6">
-        <v>6</v>
-      </c>
-      <c r="O5" s="9">
+      <c r="M5" s="5">
+        <v>6</v>
+      </c>
+      <c r="O5" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -3496,7 +3537,7 @@
       <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
@@ -3514,12 +3555,12 @@
       <c r="M6">
         <v>6</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -3541,7 +3582,7 @@
       <c r="G7" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
       <c r="I7">
@@ -3556,14 +3597,14 @@
       <c r="L7">
         <v>4</v>
       </c>
-      <c r="M7" s="6">
-        <v>6</v>
-      </c>
-      <c r="O7" s="9">
+      <c r="M7" s="5">
+        <v>6</v>
+      </c>
+      <c r="O7" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3585,7 +3626,7 @@
       <c r="G8" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>10</v>
       </c>
       <c r="I8">
@@ -3600,14 +3641,14 @@
       <c r="L8">
         <v>4</v>
       </c>
-      <c r="M8" s="6">
-        <v>6</v>
-      </c>
-      <c r="O8" s="9">
+      <c r="M8" s="5">
+        <v>6</v>
+      </c>
+      <c r="O8" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3629,7 +3670,7 @@
       <c r="G9" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>10</v>
       </c>
       <c r="I9">
@@ -3644,14 +3685,14 @@
       <c r="L9">
         <v>4</v>
       </c>
-      <c r="M9" s="6">
-        <v>6</v>
-      </c>
-      <c r="O9" s="9">
+      <c r="M9" s="5">
+        <v>6</v>
+      </c>
+      <c r="O9" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -3673,7 +3714,7 @@
       <c r="G10" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>10</v>
       </c>
       <c r="I10">
@@ -3688,14 +3729,14 @@
       <c r="L10">
         <v>4</v>
       </c>
-      <c r="M10" s="6">
-        <v>6</v>
-      </c>
-      <c r="O10" s="9">
+      <c r="M10" s="5">
+        <v>6</v>
+      </c>
+      <c r="O10" s="8">
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -3717,7 +3758,7 @@
       <c r="G11" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
@@ -3732,14 +3773,14 @@
       <c r="L11">
         <v>4</v>
       </c>
-      <c r="M11" s="6">
-        <v>6</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="M11" s="5">
+        <v>6</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -3761,7 +3802,7 @@
       <c r="G12" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>10</v>
       </c>
       <c r="I12">
@@ -3779,11 +3820,11 @@
       <c r="M12">
         <v>6</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -3805,7 +3846,7 @@
       <c r="G13" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>10</v>
       </c>
       <c r="I13">
@@ -3823,11 +3864,11 @@
       <c r="M13">
         <v>6</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -3849,7 +3890,7 @@
       <c r="G14" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>9.5</v>
       </c>
       <c r="I14">
@@ -3864,14 +3905,14 @@
       <c r="L14">
         <v>4</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>4.95</v>
       </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3893,7 +3934,7 @@
       <c r="G15" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15">
@@ -3911,11 +3952,11 @@
       <c r="M15">
         <v>5.7</v>
       </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -3937,7 +3978,7 @@
       <c r="G16" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>10</v>
       </c>
       <c r="I16">
@@ -3955,58 +3996,58 @@
       <c r="M16">
         <v>6</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="8">
         <v>1.5</v>
       </c>
       <c r="P16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="3" customFormat="1">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>1906139</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>9</v>
       </c>
-      <c r="I17" s="3">
-        <v>10</v>
-      </c>
-      <c r="J17" s="3">
-        <v>10</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="I17" s="2">
+        <v>10</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2">
         <v>5.7</v>
       </c>
-      <c r="L17" s="3">
-        <v>4</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="L17" s="2">
+        <v>4</v>
+      </c>
+      <c r="M17" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -4028,7 +4069,7 @@
       <c r="G18" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>10</v>
       </c>
       <c r="I18">
@@ -4046,11 +4087,11 @@
       <c r="M18">
         <v>6</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4072,7 +4113,7 @@
       <c r="G19" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>9.8000000000000007</v>
       </c>
       <c r="I19">
@@ -4090,12 +4131,12 @@
       <c r="M19">
         <v>6</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4117,7 +4158,7 @@
       <c r="G20" t="s">
         <v>109</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>10</v>
       </c>
       <c r="I20">
@@ -4132,14 +4173,14 @@
       <c r="L20">
         <v>4</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>4.95</v>
       </c>
-      <c r="O20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -4161,7 +4202,7 @@
       <c r="G21" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>10</v>
       </c>
       <c r="I21">
@@ -4179,14 +4220,14 @@
       <c r="M21">
         <v>6</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="8">
         <v>1</v>
       </c>
       <c r="P21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -4208,7 +4249,7 @@
       <c r="G22" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
@@ -4223,14 +4264,14 @@
       <c r="L22">
         <v>4</v>
       </c>
-      <c r="M22" s="6">
-        <v>6</v>
-      </c>
-      <c r="O22" s="9">
+      <c r="M22" s="5">
+        <v>6</v>
+      </c>
+      <c r="O22" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -4252,7 +4293,7 @@
       <c r="G23" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>8</v>
       </c>
       <c r="I23">
@@ -4270,11 +4311,11 @@
       <c r="M23">
         <v>5.4</v>
       </c>
-      <c r="O23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="O23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -4296,7 +4337,7 @@
       <c r="G24" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>10</v>
       </c>
       <c r="I24">
@@ -4311,14 +4352,14 @@
       <c r="L24">
         <v>4</v>
       </c>
-      <c r="M24" s="6">
-        <v>6</v>
-      </c>
-      <c r="O24" s="9">
+      <c r="M24" s="5">
+        <v>6</v>
+      </c>
+      <c r="O24" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -4340,7 +4381,7 @@
       <c r="G25" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
@@ -4358,7 +4399,7 @@
       <c r="M25">
         <v>6</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
@@ -4366,7 +4407,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -4388,7 +4429,7 @@
       <c r="G26" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>10</v>
       </c>
       <c r="I26">
@@ -4403,14 +4444,14 @@
       <c r="L26">
         <v>4</v>
       </c>
-      <c r="M26" s="6">
-        <v>6</v>
-      </c>
-      <c r="O26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="M26" s="5">
+        <v>6</v>
+      </c>
+      <c r="O26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -4432,7 +4473,7 @@
       <c r="G27" t="s">
         <v>142</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>10</v>
       </c>
       <c r="I27">
@@ -4450,12 +4491,12 @@
       <c r="M27">
         <v>6</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.75</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4477,7 +4518,7 @@
       <c r="G28" t="s">
         <v>147</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>10</v>
       </c>
       <c r="I28">
@@ -4492,14 +4533,14 @@
       <c r="L28">
         <v>4</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>5.25</v>
       </c>
-      <c r="O28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="O28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -4521,7 +4562,7 @@
       <c r="G29" t="s">
         <v>152</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>10</v>
       </c>
       <c r="I29">
@@ -4536,14 +4577,14 @@
       <c r="L29">
         <v>4</v>
       </c>
-      <c r="M29" s="6">
-        <v>6</v>
-      </c>
-      <c r="O29" s="9">
+      <c r="M29" s="5">
+        <v>6</v>
+      </c>
+      <c r="O29" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -4565,7 +4606,7 @@
       <c r="G30" t="s">
         <v>157</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>10</v>
       </c>
       <c r="I30">
@@ -4583,7 +4624,7 @@
       <c r="M30">
         <v>6</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="8">
         <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
         <v>1.25</v>
       </c>
@@ -4600,19 +4641,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4634,7 +4675,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -4655,11 +4696,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4681,7 +4722,7 @@
       <c r="G2" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>10</v>
       </c>
       <c r="I2">
@@ -4699,11 +4740,11 @@
       <c r="M2">
         <v>6</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4725,7 +4766,7 @@
       <c r="G3" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
@@ -4743,11 +4784,11 @@
       <c r="M3">
         <v>5.4</v>
       </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -4769,7 +4810,7 @@
       <c r="G4" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
@@ -4787,11 +4828,11 @@
       <c r="M4">
         <v>6</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="8">
         <v>2.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4813,7 +4854,7 @@
       <c r="G5" t="s">
         <v>174</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>10</v>
       </c>
       <c r="I5">
@@ -4831,11 +4872,11 @@
       <c r="M5">
         <v>6</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4857,7 +4898,7 @@
       <c r="G6" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>8.5</v>
       </c>
       <c r="I6">
@@ -4875,11 +4916,11 @@
       <c r="M6">
         <v>6</v>
       </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4901,7 +4942,7 @@
       <c r="G7" t="s">
         <v>182</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
       <c r="I7">
@@ -4919,11 +4960,11 @@
       <c r="M7">
         <v>5.7</v>
       </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4945,13 +4986,13 @@
       <c r="G8" t="s">
         <v>186</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>9.5</v>
       </c>
       <c r="I8">
         <v>9.8000000000000007</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8">
@@ -4963,11 +5004,11 @@
       <c r="M8">
         <v>5</v>
       </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -4989,7 +5030,7 @@
       <c r="G9" t="s">
         <v>190</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>10</v>
       </c>
       <c r="I9">
@@ -5007,53 +5048,53 @@
       <c r="M9">
         <v>6</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="3" customFormat="1">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>1910003</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="5">
-        <v>10</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="J10" s="3">
-        <v>10</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J10" s="2">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2">
         <v>5.4</v>
       </c>
-      <c r="L10" s="3">
-        <v>4</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -5075,7 +5116,7 @@
       <c r="G11" t="s">
         <v>170</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
@@ -5093,11 +5134,11 @@
       <c r="M11">
         <v>6</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5119,7 +5160,7 @@
       <c r="G12" t="s">
         <v>201</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>10</v>
       </c>
       <c r="I12">
@@ -5137,11 +5178,11 @@
       <c r="M12">
         <v>6</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="8">
         <v>1.25</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -5163,7 +5204,7 @@
       <c r="G13" t="s">
         <v>205</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>10</v>
       </c>
       <c r="I13">
@@ -5181,14 +5222,14 @@
       <c r="M13">
         <v>6</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>1.25</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -5210,7 +5251,7 @@
       <c r="G14" t="s">
         <v>209</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>10</v>
       </c>
       <c r="I14">
@@ -5228,11 +5269,11 @@
       <c r="M14">
         <v>6</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <v>1.25</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -5254,7 +5295,7 @@
       <c r="G15" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15">
@@ -5272,11 +5313,11 @@
       <c r="M15">
         <v>6</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -5298,7 +5339,7 @@
       <c r="G16" t="s">
         <v>217</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>10</v>
       </c>
       <c r="I16">
@@ -5316,11 +5357,11 @@
       <c r="M16">
         <v>6</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -5342,7 +5383,7 @@
       <c r="G17" t="s">
         <v>221</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>10</v>
       </c>
       <c r="I17">
@@ -5360,11 +5401,11 @@
       <c r="M17">
         <v>6</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="8">
         <v>2.25</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -5386,7 +5427,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>10</v>
       </c>
       <c r="I18">
@@ -5404,14 +5445,14 @@
       <c r="M18">
         <v>6</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="8">
         <v>1.5</v>
       </c>
       <c r="P18">
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5433,7 +5474,7 @@
       <c r="G19" t="s">
         <v>229</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>10</v>
       </c>
       <c r="I19">
@@ -5451,11 +5492,11 @@
       <c r="M19">
         <v>6</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="8">
         <v>1.25</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -5477,7 +5518,7 @@
       <c r="G20" t="s">
         <v>233</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>10</v>
       </c>
       <c r="I20">
@@ -5495,11 +5536,11 @@
       <c r="M20">
         <v>6</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5521,7 +5562,7 @@
       <c r="G21" t="s">
         <v>237</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>9.5</v>
       </c>
       <c r="I21">
@@ -5539,11 +5580,11 @@
       <c r="M21">
         <v>5.8</v>
       </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -5565,7 +5606,7 @@
       <c r="G22" t="s">
         <v>241</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
@@ -5583,11 +5624,11 @@
       <c r="M22">
         <v>5.8</v>
       </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -5609,7 +5650,7 @@
       <c r="G23" t="s">
         <v>245</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>10</v>
       </c>
       <c r="I23">
@@ -5627,11 +5668,11 @@
       <c r="M23">
         <v>5.6</v>
       </c>
-      <c r="O23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="O23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5653,7 +5694,7 @@
       <c r="G24" t="s">
         <v>249</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>9.5</v>
       </c>
       <c r="I24">
@@ -5671,11 +5712,11 @@
       <c r="M24">
         <v>6</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -5697,7 +5738,7 @@
       <c r="G25" t="s">
         <v>253</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
@@ -5715,11 +5756,11 @@
       <c r="M25">
         <v>6</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="8">
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -5741,7 +5782,7 @@
       <c r="G26" t="s">
         <v>249</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>10</v>
       </c>
       <c r="I26">
@@ -5759,11 +5800,11 @@
       <c r="M26">
         <v>5.9</v>
       </c>
-      <c r="O26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="O26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -5785,7 +5826,7 @@
       <c r="G27" t="s">
         <v>225</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>10</v>
       </c>
       <c r="I27">
@@ -5803,11 +5844,11 @@
       <c r="M27">
         <v>6</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -5829,7 +5870,7 @@
       <c r="G28" t="s">
         <v>263</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>10</v>
       </c>
       <c r="I28">
@@ -5847,11 +5888,11 @@
       <c r="M28">
         <v>5.5</v>
       </c>
-      <c r="O28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="O28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -5873,7 +5914,7 @@
       <c r="G29" t="s">
         <v>217</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>10</v>
       </c>
       <c r="I29">
@@ -5891,11 +5932,11 @@
       <c r="M29">
         <v>6</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="8">
         <v>1.25</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5917,7 +5958,7 @@
       <c r="G30" t="s">
         <v>270</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>10</v>
       </c>
       <c r="I30">
@@ -5935,7 +5976,7 @@
       <c r="M30">
         <v>6</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5948,19 +5989,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="24.25" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5982,7 +6023,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -5997,11 +6038,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -6023,26 +6064,26 @@
       <c r="G2" t="s">
         <v>275</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="6">
-        <v>10</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="J2" s="5">
+        <v>10</v>
+      </c>
+      <c r="K2" s="5">
         <v>5.7</v>
       </c>
-      <c r="L2">
-        <v>2.5</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="L2" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -6064,26 +6105,26 @@
       <c r="G3" t="s">
         <v>279</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
-        <v>10</v>
-      </c>
-      <c r="K3" s="6">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="J3" s="5">
+        <v>10</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="10">
+        <v>3</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -6105,26 +6146,26 @@
       <c r="G4" t="s">
         <v>283</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>3.5</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6146,26 +6187,26 @@
       <c r="G5" t="s">
         <v>287</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="6">
-        <v>10</v>
-      </c>
-      <c r="K5" s="6">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>3.5</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="J5" s="5">
+        <v>10</v>
+      </c>
+      <c r="K5" s="5">
+        <v>6</v>
+      </c>
+      <c r="L5" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -6187,67 +6228,67 @@
       <c r="G6" t="s">
         <v>291</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6" s="6">
-        <v>10</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="J6" s="5">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5">
         <v>5.7</v>
       </c>
-      <c r="L6">
-        <v>2.5</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="3" customFormat="1">
-      <c r="A7" s="3" t="s">
+      <c r="L6" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>2006111</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>8</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="9">
         <v>8.5</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>4.5</v>
       </c>
-      <c r="L7" s="3">
-        <v>3</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -6269,26 +6310,26 @@
       <c r="G8" t="s">
         <v>299</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>10</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="6">
-        <v>10</v>
-      </c>
-      <c r="K8" s="6">
+      <c r="J8" s="5">
+        <v>10</v>
+      </c>
+      <c r="K8" s="5">
         <v>5.2</v>
       </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="L8" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -6310,26 +6351,26 @@
       <c r="G9" t="s">
         <v>303</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>10</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" s="6">
-        <v>10</v>
-      </c>
-      <c r="K9" s="6">
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <v>3.5</v>
-      </c>
-      <c r="M9" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="J9" s="5">
+        <v>10</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="10">
+        <v>4</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -6351,26 +6392,26 @@
       <c r="G10" t="s">
         <v>307</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>9.3000000000000007</v>
       </c>
       <c r="I10">
-        <v>9.5</v>
-      </c>
-      <c r="J10" s="6">
+        <v>10</v>
+      </c>
+      <c r="J10" s="5">
         <v>9.75</v>
       </c>
-      <c r="K10" s="6">
-        <v>6</v>
-      </c>
-      <c r="L10">
-        <v>3.8</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="K10" s="5">
+        <v>6</v>
+      </c>
+      <c r="L10" s="10">
+        <v>4</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -6392,26 +6433,26 @@
       <c r="G11" t="s">
         <v>311</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="6">
-        <v>10</v>
-      </c>
-      <c r="K11" s="6">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>6</v>
+      </c>
+      <c r="L11" s="10">
+        <v>4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -6433,26 +6474,26 @@
       <c r="G12" t="s">
         <v>315</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
-        <v>10</v>
-      </c>
-      <c r="K12" s="6">
-        <v>6</v>
-      </c>
-      <c r="L12">
-        <v>3.3</v>
-      </c>
-      <c r="M12" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="J12" s="5">
+        <v>10</v>
+      </c>
+      <c r="K12" s="5">
+        <v>6</v>
+      </c>
+      <c r="L12" s="10">
+        <v>4</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -6474,26 +6515,26 @@
       <c r="G13" t="s">
         <v>319</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>10</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13" s="6">
-        <v>10</v>
-      </c>
-      <c r="K13" s="6">
+      <c r="J13" s="5">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5">
         <v>5.5</v>
       </c>
-      <c r="L13">
-        <v>3.9</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="L13" s="10">
+        <v>4</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -6515,26 +6556,26 @@
       <c r="G14" t="s">
         <v>323</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>10</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14" s="6">
-        <v>10</v>
-      </c>
-      <c r="K14" s="6">
+      <c r="J14" s="5">
+        <v>10</v>
+      </c>
+      <c r="K14" s="5">
         <v>5.5</v>
       </c>
-      <c r="L14">
-        <v>3.8</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="L14" s="10">
+        <v>4</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -6556,26 +6597,26 @@
       <c r="G15" t="s">
         <v>327</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>9.3000000000000007</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>4.75</v>
       </c>
-      <c r="L15">
-        <v>1.5</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="10">
+        <v>2</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -6597,26 +6638,26 @@
       <c r="G16" t="s">
         <v>331</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>8.5</v>
       </c>
-      <c r="I16" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="J16" s="6">
+      <c r="I16" s="1">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
         <v>8.5</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>4.5</v>
       </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="L16" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -6638,26 +6679,26 @@
       <c r="G17" t="s">
         <v>335</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
       </c>
-      <c r="J17" s="6">
-        <v>10</v>
-      </c>
-      <c r="K17" s="6">
-        <v>6</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="J17" s="5">
+        <v>10</v>
+      </c>
+      <c r="K17" s="5">
+        <v>6</v>
+      </c>
+      <c r="L17" s="10">
+        <v>4</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -6679,26 +6720,26 @@
       <c r="G18" t="s">
         <v>339</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>10</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18" s="6">
-        <v>10</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="J18" s="5">
+        <v>10</v>
+      </c>
+      <c r="K18" s="5">
         <v>5.5</v>
       </c>
-      <c r="L18">
-        <v>3.5</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="L18" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -6720,26 +6761,26 @@
       <c r="G19" t="s">
         <v>343</v>
       </c>
-      <c r="H19" s="5">
-        <v>10</v>
-      </c>
-      <c r="I19" s="4">
-        <v>6.25</v>
-      </c>
-      <c r="J19" s="6">
-        <v>9.75</v>
-      </c>
-      <c r="K19" s="6">
-        <v>6</v>
-      </c>
-      <c r="L19">
-        <v>3.9</v>
-      </c>
-      <c r="M19" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="5">
+        <v>10</v>
+      </c>
+      <c r="K19" s="5">
+        <v>6</v>
+      </c>
+      <c r="L19" s="10">
+        <v>4</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -6761,26 +6802,26 @@
       <c r="G20" t="s">
         <v>347</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="5">
         <v>9.3000000000000007</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>5.5</v>
       </c>
-      <c r="L20">
-        <v>3.8</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="L20" s="10">
+        <v>4</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6802,26 +6843,26 @@
       <c r="G21" t="s">
         <v>351</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>10</v>
       </c>
       <c r="I21">
         <v>10</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>9.9</v>
       </c>
-      <c r="K21" s="6">
-        <v>6</v>
-      </c>
-      <c r="L21">
-        <v>3</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="K21" s="5">
+        <v>6</v>
+      </c>
+      <c r="L21" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -6843,26 +6884,26 @@
       <c r="G22" t="s">
         <v>355</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
-      <c r="J22" s="6">
-        <v>10</v>
-      </c>
-      <c r="K22" s="6">
-        <v>6</v>
-      </c>
-      <c r="L22">
-        <v>3.8</v>
-      </c>
-      <c r="M22" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="J22" s="5">
+        <v>10</v>
+      </c>
+      <c r="K22" s="5">
+        <v>6</v>
+      </c>
+      <c r="L22" s="10">
+        <v>4</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -6884,26 +6925,26 @@
       <c r="G23" t="s">
         <v>279</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23" s="6">
-        <v>10</v>
-      </c>
-      <c r="K23" s="6">
-        <v>6</v>
-      </c>
-      <c r="L23">
-        <v>3.9</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="J23" s="5">
+        <v>10</v>
+      </c>
+      <c r="K23" s="5">
+        <v>6</v>
+      </c>
+      <c r="L23" s="10">
+        <v>4</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -6925,26 +6966,26 @@
       <c r="G24" t="s">
         <v>362</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>9.5</v>
       </c>
-      <c r="I24" s="4">
-        <v>6.25</v>
-      </c>
-      <c r="J24" s="6">
+      <c r="I24" s="1">
+        <v>8</v>
+      </c>
+      <c r="J24" s="5">
         <v>9.25</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>5.5</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="L24" s="10">
+        <v>4</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -6966,26 +7007,26 @@
       <c r="G25" t="s">
         <v>366</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25" s="6">
-        <v>10</v>
-      </c>
-      <c r="K25" s="6">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>4</v>
-      </c>
-      <c r="M25" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="J25" s="5">
+        <v>10</v>
+      </c>
+      <c r="K25" s="5">
+        <v>6</v>
+      </c>
+      <c r="L25" s="10">
+        <v>4</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -7007,26 +7048,26 @@
       <c r="G26" t="s">
         <v>370</v>
       </c>
-      <c r="H26" s="5">
-        <v>10</v>
-      </c>
-      <c r="I26" s="4">
-        <v>7</v>
-      </c>
-      <c r="J26" s="6">
+      <c r="H26" s="4">
+        <v>10</v>
+      </c>
+      <c r="I26" s="1">
+        <v>8</v>
+      </c>
+      <c r="J26" s="5">
         <v>8.5</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>5.75</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="L26" s="10">
+        <v>4</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -7048,26 +7089,26 @@
       <c r="G27" t="s">
         <v>374</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
       </c>
-      <c r="J27" s="6">
-        <v>10</v>
-      </c>
-      <c r="K27" s="6">
-        <v>6</v>
-      </c>
-      <c r="L27">
-        <v>3.9</v>
-      </c>
-      <c r="M27" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="J27" s="5">
+        <v>10</v>
+      </c>
+      <c r="K27" s="5">
+        <v>6</v>
+      </c>
+      <c r="L27" s="10">
+        <v>4</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -7089,26 +7130,26 @@
       <c r="G28" t="s">
         <v>378</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>5</v>
       </c>
-      <c r="L28">
-        <v>3</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="L28" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -7130,26 +7171,26 @@
       <c r="G29" t="s">
         <v>382</v>
       </c>
-      <c r="H29" s="5">
-        <v>10</v>
-      </c>
-      <c r="I29" s="4">
-        <v>5.75</v>
-      </c>
-      <c r="J29" s="6">
-        <v>10</v>
-      </c>
-      <c r="K29" s="6">
+      <c r="H29" s="4">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1">
+        <v>8</v>
+      </c>
+      <c r="J29" s="5">
+        <v>10</v>
+      </c>
+      <c r="K29" s="5">
         <v>5.5</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="L29" s="10">
+        <v>4</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -7171,26 +7212,26 @@
       <c r="G30" t="s">
         <v>386</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>10</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
-      <c r="J30" s="6">
-        <v>10</v>
-      </c>
-      <c r="K30" s="6">
-        <v>6</v>
-      </c>
-      <c r="L30">
-        <v>3.9</v>
-      </c>
-      <c r="M30" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="J30" s="5">
+        <v>10</v>
+      </c>
+      <c r="K30" s="5">
+        <v>6</v>
+      </c>
+      <c r="L30" s="10">
+        <v>4</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -7212,26 +7253,27 @@
       <c r="G31" t="s">
         <v>391</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="4">
         <v>10</v>
       </c>
       <c r="I31">
         <v>10</v>
       </c>
-      <c r="J31" s="6">
-        <v>10</v>
-      </c>
-      <c r="K31" s="6">
-        <v>6</v>
-      </c>
-      <c r="L31">
-        <v>1.8</v>
-      </c>
-      <c r="M31" s="9">
+      <c r="J31" s="5">
+        <v>10</v>
+      </c>
+      <c r="K31" s="5">
+        <v>6</v>
+      </c>
+      <c r="L31" s="10">
+        <v>2</v>
+      </c>
+      <c r="M31" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -7240,19 +7282,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="35.375" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7274,7 +7316,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -7289,11 +7331,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -7315,26 +7357,26 @@
       <c r="G2" t="s">
         <v>396</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="6">
-        <v>10</v>
-      </c>
-      <c r="K2" s="6">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2" s="9">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="J2" s="5">
+        <v>10</v>
+      </c>
+      <c r="K2" s="5">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10">
+        <v>4</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -7356,26 +7398,26 @@
       <c r="G3" t="s">
         <v>400</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>9.6</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>4.75</v>
       </c>
-      <c r="L3">
-        <v>1.3</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -7397,26 +7439,26 @@
       <c r="G4" t="s">
         <v>404</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6">
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
         <v>5.5</v>
       </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="L4" s="10">
+        <v>4</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -7438,26 +7480,26 @@
       <c r="G5" t="s">
         <v>408</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>9</v>
       </c>
-      <c r="I5" s="4">
-        <v>6</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="1">
+        <v>8</v>
+      </c>
+      <c r="J5" s="5">
         <v>7.75</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>4.75</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="L5" s="10">
+        <v>4</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -7479,26 +7521,26 @@
       <c r="G6" t="s">
         <v>412</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6" s="6">
-        <v>10</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="J6" s="5">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5">
         <v>5.5</v>
       </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="L6" s="10">
+        <v>4</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -7520,26 +7562,26 @@
       <c r="G7" t="s">
         <v>416</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7" s="6">
-        <v>10</v>
-      </c>
-      <c r="K7" s="6">
+      <c r="J7" s="5">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5">
         <v>5.75</v>
       </c>
-      <c r="L7">
-        <v>2.5</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -7561,26 +7603,26 @@
       <c r="G8" t="s">
         <v>420</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>10</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="6">
-        <v>10</v>
-      </c>
-      <c r="K8" s="6">
-        <v>6</v>
-      </c>
-      <c r="L8">
-        <v>4</v>
-      </c>
-      <c r="M8" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="J8" s="5">
+        <v>10</v>
+      </c>
+      <c r="K8" s="5">
+        <v>6</v>
+      </c>
+      <c r="L8" s="10">
+        <v>4</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -7602,26 +7644,26 @@
       <c r="G9" t="s">
         <v>424</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>9</v>
       </c>
       <c r="I9">
         <v>9</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>8.75</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>5.5</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="L9" s="10">
+        <v>3</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -7643,26 +7685,26 @@
       <c r="G10" t="s">
         <v>428</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>10</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10" s="6">
-        <v>10</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="J10" s="5">
+        <v>10</v>
+      </c>
+      <c r="K10" s="5">
         <v>5.9</v>
       </c>
-      <c r="L10">
-        <v>3.9</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="L10" s="10">
+        <v>4</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -7684,26 +7726,26 @@
       <c r="G11" t="s">
         <v>323</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="6">
-        <v>10</v>
-      </c>
-      <c r="K11" s="6">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>6</v>
+      </c>
+      <c r="L11" s="10">
+        <v>4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -7725,26 +7767,26 @@
       <c r="G12" t="s">
         <v>435</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
-        <v>10</v>
-      </c>
-      <c r="K12" s="6">
-        <v>6</v>
-      </c>
-      <c r="L12">
-        <v>2.5</v>
-      </c>
-      <c r="M12" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="J12" s="5">
+        <v>10</v>
+      </c>
+      <c r="K12" s="5">
+        <v>6</v>
+      </c>
+      <c r="L12" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -7766,26 +7808,26 @@
       <c r="G13" t="s">
         <v>435</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>10</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13" s="6">
-        <v>10</v>
-      </c>
-      <c r="K13" s="6">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="J13" s="5">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5">
+        <v>6</v>
+      </c>
+      <c r="L13" s="10">
+        <v>3</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7807,26 +7849,26 @@
       <c r="G14" t="s">
         <v>442</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>10</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>8.9</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>5.5</v>
       </c>
-      <c r="L14">
-        <v>3.3</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="L14" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -7848,26 +7890,26 @@
       <c r="G15" t="s">
         <v>446</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>9</v>
       </c>
-      <c r="I15" s="4">
-        <v>7</v>
-      </c>
-      <c r="J15" s="6">
+      <c r="I15" s="1">
         <v>8</v>
       </c>
-      <c r="K15" s="6">
+      <c r="J15" s="5">
+        <v>8</v>
+      </c>
+      <c r="K15" s="5">
         <v>4.5</v>
       </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -7889,26 +7931,26 @@
       <c r="G16" t="s">
         <v>362</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>10</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>9.1</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>5.5</v>
       </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="L16" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -7930,26 +7972,26 @@
       <c r="G17" t="s">
         <v>453</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
       </c>
-      <c r="J17" s="6">
-        <v>10</v>
-      </c>
-      <c r="K17" s="6">
+      <c r="J17" s="5">
+        <v>10</v>
+      </c>
+      <c r="K17" s="5">
         <v>5.8</v>
       </c>
-      <c r="L17">
-        <v>2.5</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="L17" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -7971,26 +8013,26 @@
       <c r="G18" t="s">
         <v>457</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>9</v>
       </c>
-      <c r="I18" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="J18" s="6">
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="5">
         <v>9.25</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>5.25</v>
       </c>
-      <c r="L18">
-        <v>3.8</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="L18" s="10">
+        <v>4</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -8012,26 +8054,26 @@
       <c r="G19" t="s">
         <v>461</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
-      <c r="J19" s="6">
-        <v>10</v>
-      </c>
-      <c r="K19" s="6">
-        <v>6</v>
-      </c>
-      <c r="L19">
-        <v>4</v>
-      </c>
-      <c r="M19" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="J19" s="5">
+        <v>10</v>
+      </c>
+      <c r="K19" s="5">
+        <v>6</v>
+      </c>
+      <c r="L19" s="10">
+        <v>4</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -8053,26 +8095,26 @@
       <c r="G20" t="s">
         <v>382</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>9</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="5">
         <v>9</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>5.25</v>
       </c>
-      <c r="L20">
-        <v>3.8</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="L20" s="10">
+        <v>4</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8094,26 +8136,26 @@
       <c r="G21" t="s">
         <v>468</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>8</v>
       </c>
-      <c r="I21" s="4">
-        <v>7</v>
-      </c>
-      <c r="J21" s="6">
+      <c r="I21" s="1">
+        <v>8</v>
+      </c>
+      <c r="J21" s="5">
         <v>6.75</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>3.75</v>
       </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="L21" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -8135,26 +8177,26 @@
       <c r="G22" t="s">
         <v>472</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
-      <c r="J22" s="6">
-        <v>10</v>
-      </c>
-      <c r="K22" s="6">
-        <v>6</v>
-      </c>
-      <c r="L22">
-        <v>3.9</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="J22" s="5">
+        <v>10</v>
+      </c>
+      <c r="K22" s="5">
+        <v>6</v>
+      </c>
+      <c r="L22" s="10">
+        <v>4</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -8176,26 +8218,26 @@
       <c r="G23" t="s">
         <v>370</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23" s="6">
-        <v>10</v>
-      </c>
-      <c r="K23" s="6">
-        <v>6</v>
-      </c>
-      <c r="L23">
-        <v>3.5</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="J23" s="5">
+        <v>10</v>
+      </c>
+      <c r="K23" s="5">
+        <v>6</v>
+      </c>
+      <c r="L23" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -8217,26 +8259,26 @@
       <c r="G24" t="s">
         <v>479</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24" s="6">
-        <v>10</v>
-      </c>
-      <c r="K24" s="6">
-        <v>6</v>
-      </c>
-      <c r="L24">
-        <v>4</v>
-      </c>
-      <c r="M24" s="9">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="J24" s="5">
+        <v>10</v>
+      </c>
+      <c r="K24" s="5">
+        <v>6</v>
+      </c>
+      <c r="L24" s="10">
+        <v>4</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8258,26 +8300,26 @@
       <c r="G25" t="s">
         <v>483</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25" s="6">
-        <v>10</v>
-      </c>
-      <c r="K25" s="6">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>3.8</v>
-      </c>
-      <c r="M25" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="J25" s="5">
+        <v>10</v>
+      </c>
+      <c r="K25" s="5">
+        <v>6</v>
+      </c>
+      <c r="L25" s="10">
+        <v>4</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -8299,26 +8341,26 @@
       <c r="G26" t="s">
         <v>487</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>10</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
-      <c r="J26" s="6">
-        <v>10</v>
-      </c>
-      <c r="K26" s="6">
-        <v>6</v>
-      </c>
-      <c r="L26">
-        <v>4</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="J26" s="5">
+        <v>10</v>
+      </c>
+      <c r="K26" s="5">
+        <v>6</v>
+      </c>
+      <c r="L26" s="10">
+        <v>4</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -8340,26 +8382,26 @@
       <c r="G27" t="s">
         <v>491</v>
       </c>
-      <c r="H27" s="5">
-        <v>10</v>
-      </c>
-      <c r="I27" s="4">
-        <v>7</v>
-      </c>
-      <c r="J27" s="6">
+      <c r="H27" s="4">
+        <v>10</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
+      <c r="J27" s="5">
         <v>9.5</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>5</v>
       </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="L27" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -8381,26 +8423,26 @@
       <c r="G28" t="s">
         <v>495</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
-      <c r="J28" s="6">
-        <v>10</v>
-      </c>
-      <c r="K28" s="6">
+      <c r="J28" s="5">
+        <v>10</v>
+      </c>
+      <c r="K28" s="5">
         <v>5.7</v>
       </c>
-      <c r="L28">
-        <v>0.8</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="L28" s="10">
+        <v>1</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -8422,26 +8464,26 @@
       <c r="G29" t="s">
         <v>499</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>9.5</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
-      <c r="J29" s="6">
-        <v>10</v>
-      </c>
-      <c r="K29" s="6">
-        <v>6</v>
-      </c>
-      <c r="L29">
-        <v>3.5</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="J29" s="5">
+        <v>10</v>
+      </c>
+      <c r="K29" s="5">
+        <v>6</v>
+      </c>
+      <c r="L29" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -8463,26 +8505,26 @@
       <c r="G30" t="s">
         <v>503</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>10</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
-      <c r="J30" s="6">
-        <v>10</v>
-      </c>
-      <c r="K30" s="6">
-        <v>6</v>
-      </c>
-      <c r="L30">
-        <v>3</v>
-      </c>
-      <c r="M30" s="9">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="J30" s="5">
+        <v>10</v>
+      </c>
+      <c r="K30" s="5">
+        <v>6</v>
+      </c>
+      <c r="L30" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -8504,22 +8546,22 @@
       <c r="G31" t="s">
         <v>507</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="4">
         <v>7</v>
       </c>
       <c r="I31">
         <v>10</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="5">
         <v>9.5</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>5.25</v>
       </c>
-      <c r="L31">
-        <v>3.5</v>
-      </c>
-      <c r="M31" s="9">
+      <c r="L31" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M31" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8532,20 +8574,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="16.75" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="8" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.375" customWidth="1"/>
-    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8567,7 +8609,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -8582,11 +8624,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -8608,26 +8650,26 @@
       <c r="G2" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="6">
-        <v>10</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="J2" s="5">
+        <v>10</v>
+      </c>
+      <c r="K2" s="5">
         <v>5.6</v>
       </c>
-      <c r="L2" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="L2" s="11">
+        <v>4</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -8649,26 +8691,26 @@
       <c r="G3" t="s">
         <v>515</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
-        <v>10</v>
-      </c>
-      <c r="K3" s="6">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>3.7</v>
-      </c>
-      <c r="M3" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="J3" s="5">
+        <v>10</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="10">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -8690,26 +8732,26 @@
       <c r="G4" t="s">
         <v>519</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>3.3</v>
-      </c>
-      <c r="M4" s="9">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="10">
+        <v>4</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -8731,26 +8773,26 @@
       <c r="G5" t="s">
         <v>523</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>9</v>
       </c>
-      <c r="K5" s="6">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2.7</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="K5" s="5">
+        <v>6</v>
+      </c>
+      <c r="L5" s="10">
+        <v>3</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -8772,26 +8814,26 @@
       <c r="G6" t="s">
         <v>527</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6" s="6">
-        <v>10</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="J6" s="5">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5">
         <v>5</v>
       </c>
-      <c r="L6">
-        <v>3.9</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="L6" s="10">
+        <v>4</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -8813,26 +8855,26 @@
       <c r="G7" t="s">
         <v>531</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>8</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>8.5</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>4.5</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -8854,26 +8896,26 @@
       <c r="G8" t="s">
         <v>535</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>9.3000000000000007</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>9.4</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>5</v>
       </c>
-      <c r="L8">
-        <v>1.8</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="L8" s="10">
+        <v>2</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -8895,26 +8937,26 @@
       <c r="G9" t="s">
         <v>539</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>9</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>9.6</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>5.75</v>
       </c>
-      <c r="L9">
-        <v>1.3</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="L9" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -8936,26 +8978,26 @@
       <c r="G10" t="s">
         <v>543</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>10</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>6.8</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>4.5</v>
       </c>
-      <c r="L10">
-        <v>3</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="L10" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -8977,26 +9019,26 @@
       <c r="G11" t="s">
         <v>547</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="6">
-        <v>10</v>
-      </c>
-      <c r="K11" s="6">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>3.9</v>
-      </c>
-      <c r="M11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>6</v>
+      </c>
+      <c r="L11" s="10">
+        <v>4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -9018,26 +9060,26 @@
       <c r="G12" t="s">
         <v>442</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>8.5</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>9.5</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>5.75</v>
       </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="L12" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -9059,26 +9101,26 @@
       <c r="G13" t="s">
         <v>554</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>9.5</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13" s="6">
-        <v>10</v>
-      </c>
-      <c r="K13" s="6">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="J13" s="5">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5">
+        <v>6</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -9100,26 +9142,26 @@
       <c r="G14" t="s">
         <v>558</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>8.5</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>9</v>
       </c>
-      <c r="K14" s="6">
-        <v>6</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="K14" s="5">
+        <v>6</v>
+      </c>
+      <c r="L14" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -9141,26 +9183,26 @@
       <c r="G15" t="s">
         <v>562</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>9.5</v>
       </c>
-      <c r="K15" s="6">
-        <v>6</v>
-      </c>
-      <c r="L15">
-        <v>0.3</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="K15" s="5">
+        <v>6</v>
+      </c>
+      <c r="L15" s="10">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -9182,26 +9224,26 @@
       <c r="G16" t="s">
         <v>535</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>9.5</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>8.6</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>5.5</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="L16" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -9223,26 +9265,26 @@
       <c r="G17" t="s">
         <v>569</v>
       </c>
-      <c r="H17" s="5">
-        <v>10</v>
-      </c>
-      <c r="I17" s="4">
-        <v>9.25</v>
-      </c>
-      <c r="J17" s="6">
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
+      <c r="I17" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J17" s="5">
         <v>8.75</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>5</v>
       </c>
-      <c r="L17">
-        <v>2.5</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="L17" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -9264,26 +9306,26 @@
       <c r="G18" t="s">
         <v>573</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>10</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18" s="6">
-        <v>10</v>
-      </c>
-      <c r="K18" s="6">
-        <v>6</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="J18" s="5">
+        <v>10</v>
+      </c>
+      <c r="K18" s="5">
+        <v>6</v>
+      </c>
+      <c r="L18" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -9305,26 +9347,26 @@
       <c r="G19" t="s">
         <v>577</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
-      <c r="J19" s="6">
-        <v>10</v>
-      </c>
-      <c r="K19" s="6">
+      <c r="J19" s="5">
+        <v>10</v>
+      </c>
+      <c r="K19" s="5">
         <v>5</v>
       </c>
-      <c r="L19">
-        <v>4</v>
-      </c>
-      <c r="M19" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="L19" s="10">
+        <v>4</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -9346,27 +9388,26 @@
       <c r="G20" t="s">
         <v>581</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
-      <c r="J20" s="6">
-        <v>10</v>
-      </c>
-      <c r="K20" s="6">
-        <v>6</v>
-      </c>
-      <c r="L20">
-        <v>3.8</v>
-      </c>
-      <c r="M20" s="9">
-        <f ca="1">Table134[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="J20" s="5">
+        <v>10</v>
+      </c>
+      <c r="K20" s="5">
+        <v>6</v>
+      </c>
+      <c r="L20" s="10">
+        <v>4</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9388,26 +9429,26 @@
       <c r="G21" t="s">
         <v>585</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>9.5</v>
       </c>
-      <c r="I21" s="4">
-        <v>8.75</v>
-      </c>
-      <c r="J21" s="6">
+      <c r="I21" s="1">
+        <v>9</v>
+      </c>
+      <c r="J21" s="5">
         <v>9.25</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>5.5</v>
       </c>
-      <c r="L21">
-        <v>1.5</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="L21" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -9429,26 +9470,26 @@
       <c r="G22" t="s">
         <v>303</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="5">
         <v>9.75</v>
       </c>
-      <c r="J22" s="6">
-        <v>9.75</v>
-      </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>5.5</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="L22" s="10">
+        <v>3</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -9470,26 +9511,26 @@
       <c r="G23" t="s">
         <v>592</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>9</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23" s="6">
-        <v>10</v>
-      </c>
-      <c r="K23" s="6">
+      <c r="J23" s="5">
+        <v>10</v>
+      </c>
+      <c r="K23" s="5">
         <v>4.5</v>
       </c>
-      <c r="L23">
-        <v>2</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="L23" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -9511,26 +9552,26 @@
       <c r="G24" t="s">
         <v>366</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24" s="6">
-        <v>10</v>
-      </c>
-      <c r="K24" s="6">
-        <v>6</v>
-      </c>
-      <c r="L24">
-        <v>3.9</v>
-      </c>
-      <c r="M24" s="9">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="J24" s="5">
+        <v>10</v>
+      </c>
+      <c r="K24" s="5">
+        <v>6</v>
+      </c>
+      <c r="L24" s="10">
+        <v>4</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -9552,26 +9593,26 @@
       <c r="G25" t="s">
         <v>424</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25" s="6">
-        <v>10</v>
-      </c>
-      <c r="K25" s="6">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>1.8</v>
-      </c>
-      <c r="M25" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="J25" s="5">
+        <v>10</v>
+      </c>
+      <c r="K25" s="5">
+        <v>6</v>
+      </c>
+      <c r="L25" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -9593,26 +9634,26 @@
       <c r="G26" t="s">
         <v>446</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>9.8000000000000007</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="5">
         <v>8.8000000000000007</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>5.25</v>
       </c>
-      <c r="L26">
-        <v>3.9</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="L26" s="10">
+        <v>4</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -9634,26 +9675,26 @@
       <c r="G27" t="s">
         <v>605</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>9</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="5">
         <v>9.5</v>
       </c>
-      <c r="J27" s="6">
-        <v>9.5</v>
-      </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>5.75</v>
       </c>
-      <c r="L27">
-        <v>4</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="L27" s="10">
+        <v>4</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -9675,26 +9716,26 @@
       <c r="G28" t="s">
         <v>569</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="5">
         <v>9.5</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>4.75</v>
       </c>
-      <c r="L28">
-        <v>2.5</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="L28" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -9716,26 +9757,26 @@
       <c r="G29" t="s">
         <v>378</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="5">
         <v>9.6999999999999993</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>5.5</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="L29" s="10">
+        <v>3</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -9757,24 +9798,27 @@
       <c r="G30" t="s">
         <v>615</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>10</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
-      <c r="J30" s="6">
-        <v>10</v>
-      </c>
-      <c r="K30" s="6">
+      <c r="J30" s="5">
+        <v>10</v>
+      </c>
+      <c r="K30" s="5">
         <v>5.9</v>
       </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" s="9">
-        <v>0</v>
-      </c>
+      <c r="L30" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L31" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9785,19 +9829,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="13" max="13" width="16.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="12" max="12" width="9.140625" style="10"/>
+    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9819,7 +9864,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -9831,14 +9876,14 @@
       <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9860,26 +9905,26 @@
       <c r="G2" t="s">
         <v>620</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>9.3000000000000007</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>9</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>5.25</v>
       </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="L2" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -9901,26 +9946,26 @@
       <c r="G3" t="s">
         <v>355</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>9.9</v>
       </c>
-      <c r="K3" s="6">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>2.8</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="10">
+        <v>3</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -9942,26 +9987,26 @@
       <c r="G4" t="s">
         <v>627</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>9.75</v>
       </c>
-      <c r="K4" s="6">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>2.8</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="10">
+        <v>3</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -9983,26 +10028,26 @@
       <c r="G5" t="s">
         <v>382</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5" s="6">
-        <v>10</v>
-      </c>
-      <c r="K5" s="6">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2.5</v>
-      </c>
-      <c r="M5" s="9">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="J5" s="5">
+        <v>10</v>
+      </c>
+      <c r="K5" s="5">
+        <v>6</v>
+      </c>
+      <c r="L5" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -10024,26 +10069,26 @@
       <c r="G6" t="s">
         <v>634</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6" s="6">
-        <v>10</v>
-      </c>
-      <c r="K6" s="6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="J6" s="5">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5">
+        <v>6</v>
+      </c>
+      <c r="L6" s="10">
+        <v>4</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -10065,26 +10110,26 @@
       <c r="G7" t="s">
         <v>638</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7" s="6">
-        <v>10</v>
-      </c>
-      <c r="K7" s="6">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="J7" s="5">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5">
+        <v>6</v>
+      </c>
+      <c r="L7" s="10">
+        <v>4</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -10106,26 +10151,26 @@
       <c r="G8" t="s">
         <v>642</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>9.5</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>5.25</v>
       </c>
-      <c r="L8">
-        <v>3.9</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="L8" s="10">
+        <v>4</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -10147,26 +10192,26 @@
       <c r="G9" t="s">
         <v>646</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>10</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" s="6">
-        <v>10</v>
-      </c>
-      <c r="K9" s="6">
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <v>3.3</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="J9" s="5">
+        <v>10</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -10188,26 +10233,26 @@
       <c r="G10" t="s">
         <v>650</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>9.5</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>5</v>
       </c>
-      <c r="L10">
-        <v>4</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="L10" s="10">
+        <v>4</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -10229,26 +10274,26 @@
       <c r="G11" t="s">
         <v>654</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="6">
-        <v>10</v>
-      </c>
-      <c r="K11" s="6">
-        <v>6</v>
-      </c>
-      <c r="L11">
-        <v>3.8</v>
-      </c>
-      <c r="M11" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>6</v>
+      </c>
+      <c r="L11" s="10">
+        <v>4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -10270,26 +10315,26 @@
       <c r="G12" t="s">
         <v>658</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>9.5</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
-        <v>10</v>
-      </c>
-      <c r="K12" s="6">
+      <c r="J12" s="5">
+        <v>10</v>
+      </c>
+      <c r="K12" s="5">
         <v>5</v>
       </c>
-      <c r="L12">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="L12" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -10311,26 +10356,26 @@
       <c r="G13" t="s">
         <v>662</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>10</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K13" s="6">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>2.8</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="K13" s="5">
+        <v>6</v>
+      </c>
+      <c r="L13" s="10">
+        <v>3</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -10352,26 +10397,26 @@
       <c r="G14" t="s">
         <v>666</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>9.5</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14" s="6">
-        <v>10</v>
-      </c>
-      <c r="K14" s="6">
-        <v>6</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="J14" s="5">
+        <v>10</v>
+      </c>
+      <c r="K14" s="5">
+        <v>6</v>
+      </c>
+      <c r="L14" s="10">
+        <v>4</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -10393,26 +10438,26 @@
       <c r="G15" t="s">
         <v>491</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>9.5</v>
       </c>
-      <c r="K15" s="6">
-        <v>6</v>
-      </c>
-      <c r="L15">
-        <v>4</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="K15" s="5">
+        <v>6</v>
+      </c>
+      <c r="L15" s="10">
+        <v>4</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -10434,26 +10479,26 @@
       <c r="G16" t="s">
         <v>673</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>9.5</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="1">
+        <v>10</v>
+      </c>
+      <c r="J16" s="5">
         <v>9.5</v>
       </c>
-      <c r="J16" s="6">
-        <v>9.5</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>5.75</v>
       </c>
-      <c r="L16">
-        <v>3.8</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="L16" s="10">
+        <v>4</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -10475,26 +10520,26 @@
       <c r="G17" t="s">
         <v>677</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>9</v>
       </c>
-      <c r="I17" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="J17" s="6">
+      <c r="I17" s="1">
+        <v>7</v>
+      </c>
+      <c r="J17" s="5">
         <v>7.75</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>5.5</v>
       </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="L17" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -10516,26 +10561,26 @@
       <c r="G18" t="s">
         <v>331</v>
       </c>
-      <c r="H18" s="5">
-        <v>10</v>
-      </c>
-      <c r="I18" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="J18" s="6">
+      <c r="H18" s="4">
+        <v>10</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="5">
         <v>8.25</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>4.5</v>
       </c>
-      <c r="L18">
-        <v>3</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="L18" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -10557,26 +10602,26 @@
       <c r="G19" t="s">
         <v>684</v>
       </c>
-      <c r="H19" s="5">
-        <v>10</v>
-      </c>
-      <c r="I19">
-        <v>10</v>
-      </c>
-      <c r="J19" s="6">
-        <v>10</v>
-      </c>
-      <c r="K19" s="6">
-        <v>6</v>
-      </c>
-      <c r="L19">
-        <v>3.9</v>
-      </c>
-      <c r="M19" s="9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="5">
+        <v>10</v>
+      </c>
+      <c r="K19" s="5">
+        <v>6</v>
+      </c>
+      <c r="L19" s="10">
+        <v>4</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -10598,26 +10643,26 @@
       <c r="G20" t="s">
         <v>688</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>9.5</v>
       </c>
-      <c r="I20">
-        <v>10</v>
-      </c>
-      <c r="J20" s="6">
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="5">
         <v>8.75</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>5</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -10639,26 +10684,26 @@
       <c r="G21" t="s">
         <v>692</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>9.5</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="1">
         <v>8</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>8.5</v>
       </c>
-      <c r="K21" s="6">
-        <v>4</v>
-      </c>
-      <c r="L21">
-        <v>2.8</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="K21" s="5">
+        <v>4</v>
+      </c>
+      <c r="L21" s="10">
+        <v>3</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -10680,26 +10725,26 @@
       <c r="G22" t="s">
         <v>627</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
-      <c r="J22" s="6">
-        <v>10</v>
-      </c>
-      <c r="K22" s="6">
-        <v>6</v>
-      </c>
-      <c r="L22">
-        <v>3.9</v>
-      </c>
-      <c r="M22" s="9">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="J22" s="5">
+        <v>10</v>
+      </c>
+      <c r="K22" s="5">
+        <v>6</v>
+      </c>
+      <c r="L22" s="10">
+        <v>4</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -10721,26 +10766,26 @@
       <c r="G23" t="s">
         <v>491</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <v>9.6999999999999993</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>5.75</v>
       </c>
-      <c r="L23">
-        <v>3.8</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="L23" s="10">
+        <v>4</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -10762,26 +10807,26 @@
       <c r="G24" t="s">
         <v>702</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
-      <c r="J24" s="6">
-        <v>10</v>
-      </c>
-      <c r="K24" s="6">
-        <v>6</v>
-      </c>
-      <c r="L24">
-        <v>3.9</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="J24" s="5">
+        <v>10</v>
+      </c>
+      <c r="K24" s="5">
+        <v>6</v>
+      </c>
+      <c r="L24" s="10">
+        <v>4</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -10803,26 +10848,26 @@
       <c r="G25" t="s">
         <v>706</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
-      <c r="J25" s="6">
-        <v>10</v>
-      </c>
-      <c r="K25" s="6">
-        <v>6</v>
-      </c>
-      <c r="L25">
-        <v>4</v>
-      </c>
-      <c r="M25" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="J25" s="5">
+        <v>10</v>
+      </c>
+      <c r="K25" s="5">
+        <v>6</v>
+      </c>
+      <c r="L25" s="10">
+        <v>4</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -10844,101 +10889,102 @@
       <c r="G26" t="s">
         <v>573</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>10</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
-      <c r="J26" s="6">
-        <v>10</v>
-      </c>
-      <c r="K26" s="6">
-        <v>6</v>
-      </c>
-      <c r="L26">
-        <v>3.8</v>
-      </c>
-      <c r="M26" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1">
-      <c r="A27" s="4" t="s">
+      <c r="J26" s="5">
+        <v>10</v>
+      </c>
+      <c r="K26" s="5">
+        <v>6</v>
+      </c>
+      <c r="L26" s="10">
+        <v>4</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>2206254</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>8</v>
       </c>
-      <c r="I27" s="4">
-        <v>10</v>
-      </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="M27" s="9">
+      <c r="I27" s="3">
+        <v>10</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="3" customFormat="1">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>2206058</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="H28" s="5">
-        <v>10</v>
-      </c>
-      <c r="I28" s="4">
+      <c r="H28" s="4">
+        <v>10</v>
+      </c>
+      <c r="I28" s="3">
         <v>5</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="7">
         <v>8.75</v>
       </c>
-      <c r="K28" s="7">
-        <v>6</v>
-      </c>
-      <c r="L28" s="3">
-        <v>4</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="K28" s="6">
+        <v>6</v>
+      </c>
+      <c r="L28" s="10">
+        <v>4</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -10960,23 +11006,23 @@
       <c r="G29" t="s">
         <v>446</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>10</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
-      <c r="J29" s="6">
-        <v>10</v>
-      </c>
-      <c r="K29" s="6">
-        <v>6</v>
-      </c>
-      <c r="L29">
-        <v>3.9</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0.75</v>
+      <c r="J29" s="5">
+        <v>10</v>
+      </c>
+      <c r="K29" s="5">
+        <v>6</v>
+      </c>
+      <c r="L29" s="10">
+        <v>4</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10988,20 +11034,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="5"/>
-    <col min="11" max="12" width="9.125" customWidth="1"/>
-    <col min="15" max="15" width="16.125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
+    <col min="11" max="12" width="9.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11023,7 +11069,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -11044,11 +11090,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -11070,7 +11116,7 @@
       <c r="G2" t="s">
         <v>724</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>10</v>
       </c>
       <c r="I2">
@@ -11082,17 +11128,17 @@
       <c r="K2">
         <v>6</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>4</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -11114,7 +11160,7 @@
       <c r="G3" t="s">
         <v>728</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>10</v>
       </c>
       <c r="I3">
@@ -11126,17 +11172,17 @@
       <c r="K3">
         <v>6</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>4</v>
       </c>
       <c r="M3">
         <v>5.9</v>
       </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -11158,10 +11204,10 @@
       <c r="G4" t="s">
         <v>732</v>
       </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2">
         <v>10</v>
       </c>
       <c r="J4">
@@ -11170,17 +11216,17 @@
       <c r="K4">
         <v>5.8</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>3.8</v>
       </c>
       <c r="M4">
         <v>5.9</v>
       </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -11202,10 +11248,10 @@
       <c r="G5" t="s">
         <v>737</v>
       </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2">
         <v>10</v>
       </c>
       <c r="J5">
@@ -11214,17 +11260,17 @@
       <c r="K5">
         <v>6</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>4</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -11246,7 +11292,7 @@
       <c r="G6" t="s">
         <v>741</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>10</v>
       </c>
       <c r="I6">
@@ -11258,17 +11304,17 @@
       <c r="K6">
         <v>5.7</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>4</v>
       </c>
       <c r="M6">
         <v>5.6</v>
       </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -11290,7 +11336,7 @@
       <c r="G7" t="s">
         <v>745</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
       <c r="I7">
@@ -11302,17 +11348,17 @@
       <c r="K7">
         <v>6</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>4</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="8">
         <v>1.75</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -11334,7 +11380,7 @@
       <c r="G8" t="s">
         <v>750</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>10</v>
       </c>
       <c r="I8">
@@ -11346,17 +11392,17 @@
       <c r="K8">
         <v>6</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>4</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -11378,10 +11424,10 @@
       <c r="G9" t="s">
         <v>754</v>
       </c>
-      <c r="H9" s="5">
-        <v>10</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2">
         <v>9.3000000000000007</v>
       </c>
       <c r="J9">
@@ -11390,17 +11436,17 @@
       <c r="K9">
         <v>6</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>3.2</v>
       </c>
       <c r="M9">
         <v>5.7</v>
       </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="O9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -11422,10 +11468,10 @@
       <c r="G10" t="s">
         <v>758</v>
       </c>
-      <c r="H10" s="5">
-        <v>10</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2">
         <v>10</v>
       </c>
       <c r="J10">
@@ -11434,17 +11480,17 @@
       <c r="K10">
         <v>5.4</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>3.3</v>
       </c>
       <c r="M10">
         <v>5.6</v>
       </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -11466,10 +11512,10 @@
       <c r="G11" t="s">
         <v>762</v>
       </c>
-      <c r="H11" s="5">
-        <v>10</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="2">
         <v>9.3000000000000007</v>
       </c>
       <c r="J11">
@@ -11478,17 +11524,17 @@
       <c r="K11">
         <v>5.5</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>3.2</v>
       </c>
       <c r="M11">
         <v>5.7</v>
       </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -11510,10 +11556,10 @@
       <c r="G12" t="s">
         <v>766</v>
       </c>
-      <c r="H12" s="5">
-        <v>10</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2">
         <v>9.3000000000000007</v>
       </c>
       <c r="J12">
@@ -11522,17 +11568,17 @@
       <c r="K12">
         <v>5.7</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <v>3.2</v>
       </c>
       <c r="M12">
         <v>6</v>
       </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -11554,10 +11600,10 @@
       <c r="G13" t="s">
         <v>770</v>
       </c>
-      <c r="H13" s="5">
-        <v>10</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
+      <c r="I13" s="2">
         <v>9.3000000000000007</v>
       </c>
       <c r="J13">
@@ -11566,17 +11612,17 @@
       <c r="K13">
         <v>5.7</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <v>3.2</v>
       </c>
       <c r="M13">
         <v>5.7</v>
       </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -11598,10 +11644,10 @@
       <c r="G14" t="s">
         <v>775</v>
       </c>
-      <c r="H14" s="5">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="4">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2">
         <v>10</v>
       </c>
       <c r="J14">
@@ -11610,17 +11656,17 @@
       <c r="K14">
         <v>6</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <v>3.8</v>
       </c>
       <c r="M14">
         <v>6</v>
       </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -11642,10 +11688,10 @@
       <c r="G15" t="s">
         <v>779</v>
       </c>
-      <c r="H15" s="5">
-        <v>10</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
         <v>10</v>
       </c>
       <c r="J15">
@@ -11654,17 +11700,17 @@
       <c r="K15">
         <v>6</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <v>3.7</v>
       </c>
       <c r="M15">
         <v>5.7</v>
       </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -11686,10 +11732,10 @@
       <c r="G16" t="s">
         <v>783</v>
       </c>
-      <c r="H16" s="5">
-        <v>10</v>
-      </c>
-      <c r="I16" s="3">
+      <c r="H16" s="4">
+        <v>10</v>
+      </c>
+      <c r="I16" s="2">
         <v>10</v>
       </c>
       <c r="J16">
@@ -11698,17 +11744,17 @@
       <c r="K16">
         <v>5.7</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <v>3.8</v>
       </c>
       <c r="M16">
         <v>5.8</v>
       </c>
-      <c r="O16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="O16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -11730,29 +11776,29 @@
       <c r="G17" t="s">
         <v>787</v>
       </c>
-      <c r="H17" s="5">
-        <v>10</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10</v>
+      </c>
+      <c r="J17" s="2">
         <v>8.5</v>
       </c>
       <c r="K17">
         <v>5.6</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <v>3</v>
       </c>
       <c r="M17">
         <v>5.8</v>
       </c>
-      <c r="O17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -11774,10 +11820,10 @@
       <c r="G18" t="s">
         <v>791</v>
       </c>
-      <c r="H18" s="5">
-        <v>10</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="H18" s="4">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2">
         <v>10</v>
       </c>
       <c r="J18">
@@ -11786,17 +11832,17 @@
       <c r="K18">
         <v>6</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="2">
         <v>3.8</v>
       </c>
       <c r="M18">
         <v>5.6</v>
       </c>
-      <c r="O18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -11818,10 +11864,10 @@
       <c r="G19" t="s">
         <v>795</v>
       </c>
-      <c r="H19" s="5">
-        <v>10</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
+      <c r="I19" s="2">
         <v>10</v>
       </c>
       <c r="J19">
@@ -11830,17 +11876,17 @@
       <c r="K19">
         <v>5.9</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="2">
         <v>3.8</v>
       </c>
       <c r="M19">
         <v>5.9</v>
       </c>
-      <c r="O19" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="O19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -11862,10 +11908,10 @@
       <c r="G20" t="s">
         <v>799</v>
       </c>
-      <c r="H20" s="5">
-        <v>10</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="4">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2">
         <v>10</v>
       </c>
       <c r="J20">
@@ -11874,17 +11920,17 @@
       <c r="K20">
         <v>6</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="2">
         <v>3.8</v>
       </c>
       <c r="M20">
         <v>6</v>
       </c>
-      <c r="O20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="O20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -11906,29 +11952,29 @@
       <c r="G21" t="s">
         <v>803</v>
       </c>
-      <c r="H21" s="5">
-        <v>10</v>
-      </c>
-      <c r="I21" s="3">
-        <v>10</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="H21" s="4">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10</v>
+      </c>
+      <c r="J21" s="2">
         <v>8.5</v>
       </c>
       <c r="K21">
         <v>5.7</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="2">
         <v>3</v>
       </c>
       <c r="M21">
         <v>5.5</v>
       </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -11950,7 +11996,7 @@
       <c r="G22" t="s">
         <v>807</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>10</v>
       </c>
       <c r="I22">
@@ -11962,17 +12008,17 @@
       <c r="K22" s="1">
         <v>5.6</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="2">
         <v>3.9</v>
       </c>
       <c r="M22">
         <v>5.6</v>
       </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -11994,10 +12040,10 @@
       <c r="G23" t="s">
         <v>811</v>
       </c>
-      <c r="H23" s="5">
-        <v>10</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="H23" s="4">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2">
         <v>10</v>
       </c>
       <c r="J23">
@@ -12006,17 +12052,17 @@
       <c r="K23">
         <v>6</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="2">
         <v>3.3</v>
       </c>
       <c r="M23">
         <v>5.7</v>
       </c>
-      <c r="O23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="O23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -12038,7 +12084,7 @@
       <c r="G24" t="s">
         <v>815</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>10</v>
       </c>
       <c r="I24">
@@ -12050,17 +12096,17 @@
       <c r="K24">
         <v>6</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="2">
         <v>4</v>
       </c>
       <c r="M24">
         <v>6</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -12082,10 +12128,10 @@
       <c r="G25" t="s">
         <v>818</v>
       </c>
-      <c r="H25" s="5">
-        <v>10</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="H25" s="4">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2">
         <v>10</v>
       </c>
       <c r="J25">
@@ -12094,17 +12140,17 @@
       <c r="K25">
         <v>6</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="2">
         <v>4</v>
       </c>
       <c r="M25">
         <v>5.8</v>
       </c>
-      <c r="O25" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="O25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -12126,7 +12172,7 @@
       <c r="G26" t="s">
         <v>822</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>10</v>
       </c>
       <c r="I26">
@@ -12138,17 +12184,17 @@
       <c r="K26">
         <v>6</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="2">
         <v>4</v>
       </c>
       <c r="M26">
         <v>6</v>
       </c>
-      <c r="O26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="O26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -12170,10 +12216,10 @@
       <c r="G27" t="s">
         <v>826</v>
       </c>
-      <c r="H27" s="5">
-        <v>10</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="H27" s="4">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2">
         <v>10</v>
       </c>
       <c r="J27">
@@ -12182,17 +12228,17 @@
       <c r="K27">
         <v>6</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="2">
         <v>4</v>
       </c>
       <c r="M27">
         <v>6</v>
       </c>
-      <c r="O27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="O27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -12214,25 +12260,25 @@
       <c r="G28" t="s">
         <v>830</v>
       </c>
-      <c r="H28" s="5">
-        <v>10</v>
-      </c>
-      <c r="I28" s="3">
-        <v>10</v>
-      </c>
-      <c r="J28" s="3">
+      <c r="H28" s="4">
+        <v>10</v>
+      </c>
+      <c r="I28" s="2">
+        <v>10</v>
+      </c>
+      <c r="J28" s="2">
         <v>8.5</v>
       </c>
       <c r="K28">
         <v>5.7</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="2">
         <v>3</v>
       </c>
       <c r="M28">
         <v>5.6</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12246,6 +12292,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -12484,24 +12547,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12518,29 +12589,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2173007-016A-4A81-9620-65BD135EA778}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinhthienly-my.sharepoint.com/personal/ict_khangv_lsts_edu_vn/Documents/01. PD/2025 - 2026/SỔ ĐIỂM HK2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khangv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="405" documentId="13_ncr:1_{0DF5AF2B-8EE8-4C11-A3C2-7BA40EC25983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFF161C-459C-4FEF-B9C1-2D237338F141}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36091599-C009-4660-906D-777235C34CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -2630,14 +2630,22 @@
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2654,6 +2662,14 @@
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2677,39 +2693,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
@@ -2724,27 +2707,14 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -2789,6 +2759,36 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2813,14 +2813,14 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="TX1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="TX1" dataDxfId="16"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Điểm cộng/trừ" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Điểm cộng/trừ" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2837,14 +2837,14 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="TX1" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="TX1" dataDxfId="14"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Điểm cộng/trừ" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Điểm cộng/trừ" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2861,12 +2861,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TX1" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TX1" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="GKTN" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="CKTN" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="CKTH" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Điểm cộng/trừ" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="GKTN" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="CKTN" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="CKTH" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Điểm cộng/trừ" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2883,12 +2883,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="TX1" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="TX1" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="GKTN" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CKTN" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="CKTH" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Điểm cộng/trừ" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="GKTN" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CKTN" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="CKTH" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Điểm cộng/trừ" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2905,12 +2905,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="TX1" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="TX1" dataDxfId="7"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="CKTH" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Điểm cộng/trừ" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="CKTH" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Điểm cộng/trừ" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2927,12 +2927,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="TX1" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="TX1" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="CKTH" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Điểm cộng/trừ" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="CKTH" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Điểm cộng/trừ" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2949,14 +2949,14 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TX1" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TX1" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Điểm cộng/trừ" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Điểm cộng/trừ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3280,17 +3280,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="15" max="15" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -4643,17 +4643,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14.265625" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="15" max="15" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5991,17 +5991,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" customWidth="1"/>
+    <col min="6" max="6" width="24.265625" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="13" max="13" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -7284,17 +7284,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="6" max="6" width="35.3984375" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="13" max="13" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -7581,7 +7581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>387</v>
       </c>
@@ -8576,18 +8576,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="16.73046875" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
     <col min="8" max="8" width="8" style="4" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="8.3984375" customWidth="1"/>
+    <col min="13" max="13" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="L31" s="10"/>
     </row>
   </sheetData>
@@ -9831,18 +9831,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="12" max="12" width="9.140625" style="10"/>
-    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="12" max="12" width="9.1328125" style="10"/>
+    <col min="13" max="13" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
         <v>138</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>143</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -11036,18 +11036,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" customWidth="1"/>
+    <col min="3" max="3" width="15.73046875" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="4"/>
-    <col min="11" max="12" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="4"/>
+    <col min="11" max="12" width="9.1328125" customWidth="1"/>
+    <col min="15" max="15" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -11134,11 +11134,14 @@
       <c r="M2">
         <v>6</v>
       </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
       <c r="O2" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -11178,11 +11181,14 @@
       <c r="M3">
         <v>5.9</v>
       </c>
+      <c r="N3">
+        <v>3.9</v>
+      </c>
       <c r="O3" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -11222,11 +11228,14 @@
       <c r="M4">
         <v>5.9</v>
       </c>
+      <c r="N4">
+        <v>3.8</v>
+      </c>
       <c r="O4" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -11266,11 +11275,14 @@
       <c r="M5">
         <v>6</v>
       </c>
+      <c r="N5">
+        <v>3.8</v>
+      </c>
       <c r="O5" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -11310,11 +11322,14 @@
       <c r="M6">
         <v>5.6</v>
       </c>
+      <c r="N6">
+        <v>3.9</v>
+      </c>
       <c r="O6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -11354,11 +11369,14 @@
       <c r="M7">
         <v>6</v>
       </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
       <c r="O7" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -11398,11 +11416,14 @@
       <c r="M8">
         <v>6</v>
       </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
       <c r="O8" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -11442,11 +11463,14 @@
       <c r="M9">
         <v>5.7</v>
       </c>
+      <c r="N9">
+        <v>3.3</v>
+      </c>
       <c r="O9" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -11486,11 +11510,14 @@
       <c r="M10">
         <v>5.6</v>
       </c>
+      <c r="N10">
+        <v>3.8</v>
+      </c>
       <c r="O10" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -11530,11 +11557,14 @@
       <c r="M11">
         <v>5.7</v>
       </c>
+      <c r="N11">
+        <v>3.3</v>
+      </c>
       <c r="O11" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -11574,11 +11604,14 @@
       <c r="M12">
         <v>6</v>
       </c>
+      <c r="N12">
+        <v>3.3</v>
+      </c>
       <c r="O12" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -11618,11 +11651,14 @@
       <c r="M13">
         <v>5.7</v>
       </c>
+      <c r="N13">
+        <v>3.3</v>
+      </c>
       <c r="O13" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -11662,11 +11698,14 @@
       <c r="M14">
         <v>6</v>
       </c>
+      <c r="N14">
+        <v>3.8</v>
+      </c>
       <c r="O14" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -11706,11 +11745,14 @@
       <c r="M15">
         <v>5.7</v>
       </c>
+      <c r="N15">
+        <v>3.8</v>
+      </c>
       <c r="O15" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -11750,11 +11792,14 @@
       <c r="M16">
         <v>5.8</v>
       </c>
+      <c r="N16">
+        <v>3.8</v>
+      </c>
       <c r="O16" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -11794,11 +11839,14 @@
       <c r="M17">
         <v>5.8</v>
       </c>
+      <c r="N17">
+        <v>3.8</v>
+      </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -11838,11 +11886,14 @@
       <c r="M18">
         <v>5.6</v>
       </c>
+      <c r="N18">
+        <v>3.8</v>
+      </c>
       <c r="O18" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -11882,11 +11933,14 @@
       <c r="M19">
         <v>5.9</v>
       </c>
+      <c r="N19">
+        <v>3.8</v>
+      </c>
       <c r="O19" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -11926,11 +11980,14 @@
       <c r="M20">
         <v>6</v>
       </c>
+      <c r="N20">
+        <v>3.8</v>
+      </c>
       <c r="O20" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -11970,11 +12027,14 @@
       <c r="M21">
         <v>5.5</v>
       </c>
+      <c r="N21">
+        <v>3.8</v>
+      </c>
       <c r="O21" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -12014,11 +12074,14 @@
       <c r="M22">
         <v>5.6</v>
       </c>
+      <c r="N22">
+        <v>3.9</v>
+      </c>
       <c r="O22" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -12058,11 +12121,14 @@
       <c r="M23">
         <v>5.7</v>
       </c>
+      <c r="N23">
+        <v>3.8</v>
+      </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -12102,11 +12168,14 @@
       <c r="M24">
         <v>6</v>
       </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
       <c r="O24" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -12146,11 +12215,14 @@
       <c r="M25">
         <v>5.8</v>
       </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
       <c r="O25" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -12190,11 +12262,14 @@
       <c r="M26">
         <v>6</v>
       </c>
+      <c r="N26">
+        <v>3.9</v>
+      </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -12234,11 +12309,14 @@
       <c r="M27">
         <v>6</v>
       </c>
+      <c r="N27">
+        <v>3.8</v>
+      </c>
       <c r="O27" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -12277,6 +12355,9 @@
       </c>
       <c r="M28">
         <v>5.6</v>
+      </c>
+      <c r="N28">
+        <v>3.8</v>
       </c>
       <c r="O28" s="8">
         <v>0</v>
@@ -12292,23 +12373,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x01010069F5FA6F5E99D64B892633AF1293AFE9" ma:contentTypeVersion="16" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="d2d5385ae45fc0df6c563476e54477bc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="64e27462-61f7-439c-88b3-7ca10cd645ec" xmlns:ns4="4329cf8b-2919-4c61-9f30-6ea716fa69c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b90872c2c5aa4b2a61f2c9ac5966a13" ns3:_="" ns4:_="">
     <xsd:import namespace="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
@@ -12547,10 +12611,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="64e27462-61f7-439c-88b3-7ca10cd645ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
+    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12573,20 +12665,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C04A264A-B108-430A-B3AF-4CD6D510722A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB00F7F1-EDF3-4F0C-9299-8D2EDB28E76E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="64e27462-61f7-439c-88b3-7ca10cd645ec"/>
-    <ds:schemaRef ds:uri="4329cf8b-2919-4c61-9f30-6ea716fa69c3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/so-diem.xlsx
+++ b/data/so-diem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khangv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36091599-C009-4660-906D-777235C34CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28190965-0841-4C4B-8A61-F41956637999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12T1" sheetId="6" r:id="rId1"/>
@@ -2635,22 +2635,6 @@
   <dxfs count="22">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.79998168889431442"/>
@@ -2739,6 +2723,20 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
@@ -2771,19 +2769,21 @@
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
@@ -2813,22 +2813,22 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="TX1" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="TX1" dataDxfId="19"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Điểm cộng/trừ" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Điểm cộng/trừ" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1345678" displayName="Table1345678" ref="A1:O31" totalsRowShown="0">
-  <autoFilter ref="A1:O31" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1345678" displayName="Table1345678" ref="A1:O30" totalsRowShown="0">
+  <autoFilter ref="A1:O30" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="STT"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Tên lớp"/>
@@ -2837,14 +2837,14 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="TX1" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="TX1" dataDxfId="17"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Điểm cộng/trừ" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Điểm cộng/trừ" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2861,12 +2861,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TX1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TX1" dataDxfId="15"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="GKTN" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="CKTN" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="CKTH" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Điểm cộng/trừ" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="GKTN" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="CKTN" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="CKTH" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Điểm cộng/trừ" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2883,12 +2883,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="TX1" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="TX1" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="TX2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="GKTN" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CKTN" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="CKTH" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Điểm cộng/trừ" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="GKTN" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="CKTN" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="CKTH" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Điểm cộng/trừ" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2905,12 +2905,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="TX1" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="TX1" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="CKTH" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Điểm cộng/trừ" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="CKTH" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Điểm cộng/trừ" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2927,12 +2927,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="TX1" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="TX1" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="TX2"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="GKTN"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="CKTN"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="CKTH" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Điểm cộng/trừ" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="CKTH" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Điểm cộng/trừ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2949,14 +2949,14 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Email"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Họ và tên"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Ngày sinh"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TX1" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TX1" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="TX2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="TX3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="GKTN"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="GKTH"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="CKTN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="CKTH"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Điểm cộng/trừ" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Điểm cộng/trừ" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3279,7 +3279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.73046875" customWidth="1"/>
@@ -3290,7 +3290,7 @@
     <col min="15" max="15" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3377,12 +3377,14 @@
       <c r="M2">
         <v>6</v>
       </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
       <c r="O2" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3422,11 +3424,14 @@
       <c r="M3">
         <v>6</v>
       </c>
+      <c r="N3">
+        <v>3.8</v>
+      </c>
       <c r="O3" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -3466,12 +3471,14 @@
       <c r="M4">
         <v>6</v>
       </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
       <c r="O4" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -3511,11 +3518,14 @@
       <c r="M5" s="5">
         <v>6</v>
       </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
       <c r="O5" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -3555,12 +3565,14 @@
       <c r="M6">
         <v>6</v>
       </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
       <c r="O6" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -3600,11 +3612,14 @@
       <c r="M7" s="5">
         <v>6</v>
       </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
       <c r="O7" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3644,11 +3659,14 @@
       <c r="M8" s="5">
         <v>6</v>
       </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
       <c r="O8" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3688,11 +3706,14 @@
       <c r="M9" s="5">
         <v>6</v>
       </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
       <c r="O9" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -3732,11 +3753,14 @@
       <c r="M10" s="5">
         <v>6</v>
       </c>
+      <c r="N10">
+        <v>3.9</v>
+      </c>
       <c r="O10" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -3776,11 +3800,14 @@
       <c r="M11" s="5">
         <v>6</v>
       </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
       <c r="O11" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -3820,11 +3847,14 @@
       <c r="M12">
         <v>6</v>
       </c>
+      <c r="N12">
+        <v>4</v>
+      </c>
       <c r="O12" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -3864,11 +3894,14 @@
       <c r="M13">
         <v>6</v>
       </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
       <c r="O13" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -3908,11 +3941,14 @@
       <c r="M14" s="5">
         <v>4.95</v>
       </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
       <c r="O14" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3952,11 +3988,14 @@
       <c r="M15">
         <v>5.7</v>
       </c>
+      <c r="N15">
+        <v>3.8</v>
+      </c>
       <c r="O15" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -3996,14 +4035,14 @@
       <c r="M16">
         <v>6</v>
       </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
       <c r="O16" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="P16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
@@ -4043,11 +4082,14 @@
       <c r="M17" s="2">
         <v>5.0999999999999996</v>
       </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -4087,11 +4129,14 @@
       <c r="M18">
         <v>6</v>
       </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
       <c r="O18" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4131,12 +4176,14 @@
       <c r="M19">
         <v>6</v>
       </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
       <c r="O19" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4176,11 +4223,14 @@
       <c r="M20" s="5">
         <v>4.95</v>
       </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
       <c r="O20" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -4220,14 +4270,14 @@
       <c r="M21">
         <v>6</v>
       </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
       <c r="O21" s="8">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -4267,11 +4317,14 @@
       <c r="M22" s="5">
         <v>6</v>
       </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
       <c r="O22" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -4311,11 +4364,14 @@
       <c r="M23">
         <v>5.4</v>
       </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -4355,11 +4411,14 @@
       <c r="M24" s="5">
         <v>6</v>
       </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
       <c r="O24" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -4399,15 +4458,14 @@
       <c r="M25">
         <v>6</v>
       </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
       <c r="O25" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-      <c r="P25">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -4447,11 +4505,14 @@
       <c r="M26" s="5">
         <v>6</v>
       </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -4491,12 +4552,14 @@
       <c r="M27">
         <v>6</v>
       </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
       <c r="O27" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -4536,11 +4599,14 @@
       <c r="M28" s="5">
         <v>5.25</v>
       </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
       <c r="O28" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -4580,11 +4646,14 @@
       <c r="M29" s="5">
         <v>6</v>
       </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
       <c r="O29" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -4624,12 +4693,11 @@
       <c r="M30">
         <v>6</v>
       </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
       <c r="O30" s="8">
-        <f ca="1">Table134567[[#This Row],[Điểm cộng/trừ]]+1</f>
-        <v>1.25</v>
-      </c>
-      <c r="P30">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4642,7 +4710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.73046875" customWidth="1"/>
@@ -4653,7 +4721,7 @@
     <col min="15" max="15" width="16.1328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4700,7 +4768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4740,11 +4808,14 @@
       <c r="M2">
         <v>6</v>
       </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
       <c r="O2" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4784,11 +4855,14 @@
       <c r="M3">
         <v>5.4</v>
       </c>
+      <c r="N3">
+        <v>3.8</v>
+      </c>
       <c r="O3" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -4828,11 +4902,14 @@
       <c r="M4">
         <v>6</v>
       </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
       <c r="O4" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4872,11 +4949,14 @@
       <c r="M5">
         <v>6</v>
       </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
       <c r="O5" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4916,11 +4996,14 @@
       <c r="M6">
         <v>6</v>
       </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
       <c r="O6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -4960,11 +5043,14 @@
       <c r="M7">
         <v>5.7</v>
       </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
       <c r="O7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -5004,11 +5090,14 @@
       <c r="M8">
         <v>5</v>
       </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
       <c r="O8" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -5048,11 +5137,14 @@
       <c r="M9">
         <v>6</v>
       </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
       <c r="O9" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
@@ -5090,11 +5182,14 @@
         <v>4</v>
       </c>
       <c r="M10" s="3"/>
+      <c r="N10">
+        <v>3.9</v>
+      </c>
       <c r="O10" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -5134,11 +5229,14 @@
       <c r="M11">
         <v>6</v>
       </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
       <c r="O11" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5178,11 +5276,14 @@
       <c r="M12">
         <v>6</v>
       </c>
+      <c r="N12">
+        <v>4</v>
+      </c>
       <c r="O12" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -5222,14 +5323,14 @@
       <c r="M13">
         <v>6</v>
       </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
       <c r="O13" s="8">
-        <v>1.25</v>
-      </c>
-      <c r="P13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -5269,11 +5370,14 @@
       <c r="M14">
         <v>6</v>
       </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
       <c r="O14" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -5313,11 +5417,14 @@
       <c r="M15">
         <v>6</v>
       </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
       <c r="O15" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -5357,11 +5464,14 @@
       <c r="M16">
         <v>6</v>
       </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
       <c r="O16" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -5401,11 +5511,14 @@
       <c r="M17">
         <v>6</v>
       </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
       <c r="O17" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -5445,14 +5558,14 @@
       <c r="M18">
         <v>6</v>
       </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
       <c r="O18" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="P18">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -5492,11 +5605,14 @@
       <c r="M19">
         <v>6</v>
       </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
       <c r="O19" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -5536,11 +5652,14 @@
       <c r="M20">
         <v>6</v>
       </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
       <c r="O20" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5580,11 +5699,14 @@
       <c r="M21">
         <v>5.8</v>
       </c>
+      <c r="N21">
+        <v>3.7</v>
+      </c>
       <c r="O21" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -5624,11 +5746,14 @@
       <c r="M22">
         <v>5.8</v>
       </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
       <c r="O22" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -5668,11 +5793,14 @@
       <c r="M23">
         <v>5.6</v>
       </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -5712,11 +5840,14 @@
       <c r="M24">
         <v>6</v>
       </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
       <c r="O24" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -5756,11 +5887,14 @@
       <c r="M25">
         <v>6</v>
       </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
       <c r="O25" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -5800,11 +5934,14 @@
       <c r="M26">
         <v>5.9</v>
       </c>
+      <c r="N26">
+        <v>3.9</v>
+      </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -5844,11 +5981,14 @@
       <c r="M27">
         <v>6</v>
       </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
       <c r="O27" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -5888,11 +6028,14 @@
       <c r="M28">
         <v>5.5</v>
       </c>
+      <c r="N28">
+        <v>3.7</v>
+      </c>
       <c r="O28" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>148</v>
       </c>
@@ -5932,11 +6075,14 @@
       <c r="M29">
         <v>6</v>
       </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
       <c r="O29" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5975,6 +6121,9 @@
       </c>
       <c r="M30">
         <v>6</v>
+      </c>
+      <c r="N30">
+        <v>3.7</v>
       </c>
       <c r="O30" s="8">
         <v>0</v>
